--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,7 +473,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,98 +488,98 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>265500</v>
+        <v>247000</v>
       </c>
       <c r="F2" t="n">
-        <v>123.2792</v>
+        <v>33.5026</v>
       </c>
       <c r="G2" t="n">
-        <v>32730640.59686133</v>
+        <v>8275143.9</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>116300</v>
+        <v>48400</v>
       </c>
       <c r="F3" t="n">
-        <v>332.3224</v>
+        <v>31.4253</v>
       </c>
       <c r="G3" t="n">
-        <v>38649096.95964394</v>
+        <v>1520986.1</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>152400</v>
+        <v>142700</v>
       </c>
       <c r="F4" t="n">
-        <v>272.9638</v>
+        <v>64.8394</v>
       </c>
       <c r="G4" t="n">
-        <v>41599689.38070278</v>
+        <v>9252589.1</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,694 +588,670 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44950</v>
+        <v>36800</v>
       </c>
       <c r="F5" t="n">
-        <v>931.6319999999999</v>
+        <v>1048.963</v>
       </c>
       <c r="G5" t="n">
-        <v>41876856.8952711</v>
+        <v>38601838.9</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>48700</v>
+        <v>46000</v>
       </c>
       <c r="F6" t="n">
-        <v>854.2030999999999</v>
+        <v>8.958600000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>41599689.38070278</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6.1</v>
-      </c>
+        <v>412095.1</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>125000</v>
+        <v>47650</v>
       </c>
       <c r="F7" t="n">
-        <v>335.0149</v>
+        <v>159.7361</v>
       </c>
       <c r="G7" t="n">
-        <v>41876856.8952711</v>
-      </c>
-      <c r="H7" t="n">
-        <v>8.32</v>
-      </c>
+        <v>7611423.9</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>51300</v>
+        <v>143600</v>
       </c>
       <c r="F8" t="n">
-        <v>638.0242</v>
+        <v>18.9174</v>
       </c>
       <c r="G8" t="n">
-        <v>32730640.59686133</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-14.21</v>
-      </c>
+        <v>2716534.1</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>145400</v>
+        <v>216500</v>
       </c>
       <c r="F9" t="n">
-        <v>265.8122</v>
+        <v>21.1655</v>
       </c>
       <c r="G9" t="n">
-        <v>38649096.95964394</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.83</v>
-      </c>
+        <v>4582327.9</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>663000</v>
+        <v>166800</v>
       </c>
       <c r="F10" t="n">
-        <v>59.097</v>
+        <v>41.8652</v>
       </c>
       <c r="G10" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>6983122.1</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>236500</v>
+        <v>58000</v>
       </c>
       <c r="F11" t="n">
-        <v>165.6714</v>
+        <v>5.9271</v>
       </c>
       <c r="G11" t="n">
-        <v>39181280.69736513</v>
+        <v>343773.9</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>117900</v>
+        <v>50300</v>
       </c>
       <c r="F12" t="n">
-        <v>268.003</v>
+        <v>75.29649999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>31597552.38168333</v>
+        <v>3787415.1</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>190600</v>
+        <v>199600</v>
       </c>
       <c r="F13" t="n">
-        <v>165.7794</v>
+        <v>12.1097</v>
       </c>
       <c r="G13" t="n">
-        <v>31597552.38168333</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-11.96</v>
-      </c>
+        <v>2417091.1</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>665000</v>
+        <v>111400</v>
       </c>
       <c r="F14" t="n">
-        <v>59.097</v>
+        <v>16.3438</v>
       </c>
       <c r="G14" t="n">
-        <v>39299474.60595447</v>
+        <v>1820696.1</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>94200</v>
+        <v>137200</v>
       </c>
       <c r="F15" t="n">
-        <v>390.423</v>
+        <v>25.5948</v>
       </c>
       <c r="G15" t="n">
-        <v>36777850.25730231</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-7.83</v>
-      </c>
+        <v>3511613.1</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>240000</v>
+        <v>32250</v>
       </c>
       <c r="F16" t="n">
-        <v>153.241</v>
+        <v>73.12130000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>36777850.25730231</v>
+        <v>2358161.1</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>78200</v>
+        <v>136900</v>
       </c>
       <c r="F17" t="n">
-        <v>502.5508</v>
+        <v>281.9711</v>
       </c>
       <c r="G17" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
+        <v>38601838.9</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>10970</v>
+        <v>47450</v>
       </c>
       <c r="F18" t="n">
-        <v>3600.36</v>
+        <v>11.7985</v>
       </c>
       <c r="G18" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-1.26</v>
-      </c>
+        <v>559838.1</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>80800</v>
+        <v>243000</v>
       </c>
       <c r="F19" t="n">
-        <v>493.8272</v>
+        <v>5.7934</v>
       </c>
       <c r="G19" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.25</v>
-      </c>
+        <v>1407799.1</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>11880</v>
+        <v>150200</v>
       </c>
       <c r="F20" t="n">
-        <v>3021.148</v>
+        <v>22.6436</v>
       </c>
       <c r="G20" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-10.27</v>
-      </c>
+        <v>3401064.1</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102200</v>
+        <v>53300</v>
       </c>
       <c r="F21" t="n">
-        <v>390.423</v>
+        <v>148.0773</v>
       </c>
       <c r="G21" t="n">
-        <v>39901234.56790123</v>
+        <v>7892520.9</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>45150</v>
+        <v>280500</v>
       </c>
       <c r="F22" t="n">
-        <v>832.4662</v>
+        <v>0.1361</v>
       </c>
       <c r="G22" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-6.04</v>
-      </c>
+        <v>38166.1</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>194500</v>
+        <v>327500</v>
       </c>
       <c r="F23" t="n">
-        <v>203.064</v>
+        <v>17.7362</v>
       </c>
       <c r="G23" t="n">
-        <v>39495949.5949595</v>
+        <v>5808609.9</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>128800</v>
+        <v>129200</v>
       </c>
       <c r="F24" t="n">
-        <v>306.2796</v>
+        <v>35.7512</v>
       </c>
       <c r="G24" t="n">
-        <v>39448818.8976378</v>
+        <v>4619059.9</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>45900</v>
+        <v>16590</v>
       </c>
       <c r="F25" t="n">
-        <v>854.2030999999999</v>
+        <v>513.0315000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>39207920.79207921</v>
+        <v>8511192.1</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1284,30 +1260,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>78200</v>
+        <v>42450</v>
       </c>
       <c r="F26" t="n">
-        <v>502.5508</v>
+        <v>909.3484</v>
       </c>
       <c r="G26" t="n">
-        <v>39299474.60595447</v>
+        <v>38601838.9</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1316,98 +1292,94 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>115400</v>
+        <v>265500</v>
       </c>
       <c r="F27" t="n">
-        <v>335.0149</v>
+        <v>123.2792</v>
       </c>
       <c r="G27" t="n">
-        <v>38660714.28571428</v>
+        <v>32730640.59686133</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>9740</v>
+        <v>116300</v>
       </c>
       <c r="F28" t="n">
-        <v>3875.969</v>
+        <v>332.3224</v>
       </c>
       <c r="G28" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-5.62</v>
-      </c>
+        <v>38649096.95964394</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>21650</v>
+        <v>152400</v>
       </c>
       <c r="F29" t="n">
-        <v>1785.7143</v>
+        <v>272.9638</v>
       </c>
       <c r="G29" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>41599689.38070278</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1416,30 +1388,30 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>271000</v>
+        <v>44950</v>
       </c>
       <c r="F30" t="n">
-        <v>141.0219</v>
+        <v>931.6319999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>38216939.07875186</v>
+        <v>41876856.8952711</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1448,32 +1420,32 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>64300</v>
+        <v>48700</v>
       </c>
       <c r="F31" t="n">
-        <v>594.3536</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>38216939.07875186</v>
+        <v>41599689.38070278</v>
       </c>
       <c r="H31" t="n">
-        <v>-4.46</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1482,196 +1454,198 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>56100</v>
+        <v>125000</v>
       </c>
       <c r="F32" t="n">
-        <v>700.5254</v>
+        <v>335.0149</v>
       </c>
       <c r="G32" t="n">
-        <v>39299474.60595447</v>
+        <v>41876856.8952711</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.75</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>137300</v>
+        <v>51300</v>
       </c>
       <c r="F33" t="n">
-        <v>274.9595</v>
+        <v>638.0242</v>
       </c>
       <c r="G33" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>32730640.59686133</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-14.21</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>59800</v>
+        <v>145400</v>
       </c>
       <c r="F34" t="n">
-        <v>638.0242</v>
+        <v>265.8122</v>
       </c>
       <c r="G34" t="n">
-        <v>38153846.15384615</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>38649096.95964394</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.83</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>141400</v>
+        <v>663000</v>
       </c>
       <c r="F35" t="n">
-        <v>265.8122</v>
+        <v>59.097</v>
       </c>
       <c r="G35" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>10020</v>
+        <v>236500</v>
       </c>
       <c r="F36" t="n">
-        <v>3937.0079</v>
+        <v>165.6714</v>
       </c>
       <c r="G36" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-1.38</v>
-      </c>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>29700</v>
+        <v>117900</v>
       </c>
       <c r="F37" t="n">
-        <v>1320.132</v>
+        <v>268.003</v>
       </c>
       <c r="G37" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-1.98</v>
-      </c>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1680,32 +1654,32 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6820</v>
+        <v>190600</v>
       </c>
       <c r="F38" t="n">
-        <v>5594.4056</v>
+        <v>165.7794</v>
       </c>
       <c r="G38" t="n">
-        <v>38153846.15384615</v>
+        <v>31597552.38168333</v>
       </c>
       <c r="H38" t="n">
-        <v>-4.62</v>
+        <v>-11.96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1714,62 +1688,64 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>216500</v>
+        <v>665000</v>
       </c>
       <c r="F39" t="n">
-        <v>165.7794</v>
+        <v>59.097</v>
       </c>
       <c r="G39" t="n">
-        <v>35891238.67069487</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>48850</v>
+        <v>94200</v>
       </c>
       <c r="F40" t="n">
-        <v>818.8332</v>
+        <v>390.423</v>
       </c>
       <c r="G40" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-7.83</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1778,158 +1754,166 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>11110</v>
+        <v>240000</v>
       </c>
       <c r="F41" t="n">
-        <v>3600.36</v>
+        <v>153.241</v>
       </c>
       <c r="G41" t="n">
-        <v>40000000</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>81000</v>
+        <v>78200</v>
       </c>
       <c r="F42" t="n">
-        <v>493.8272</v>
+        <v>502.5508</v>
       </c>
       <c r="G42" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>13240</v>
+        <v>10970</v>
       </c>
       <c r="F43" t="n">
-        <v>3021.148</v>
+        <v>3600.36</v>
       </c>
       <c r="G43" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>39495949.5949595</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-1.26</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>14530</v>
+        <v>80800</v>
       </c>
       <c r="F44" t="n">
-        <v>2752.925</v>
+        <v>493.8272</v>
       </c>
       <c r="G44" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>46650</v>
+        <v>11880</v>
       </c>
       <c r="F45" t="n">
-        <v>857.4491</v>
+        <v>3021.148</v>
       </c>
       <c r="G45" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>35891238.67069487</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-10.27</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1938,62 +1922,64 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>62600</v>
+        <v>102200</v>
       </c>
       <c r="F46" t="n">
-        <v>638.9776000000001</v>
+        <v>390.423</v>
       </c>
       <c r="G46" t="n">
-        <v>40000000</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>142600</v>
+        <v>45150</v>
       </c>
       <c r="F47" t="n">
-        <v>280.5049</v>
+        <v>832.4662</v>
       </c>
       <c r="G47" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-6.04</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2002,30 +1988,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>48050</v>
+        <v>194500</v>
       </c>
       <c r="F48" t="n">
-        <v>832.4662</v>
+        <v>203.064</v>
       </c>
       <c r="G48" t="n">
-        <v>40000000</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2034,30 +2020,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>62000</v>
+        <v>128800</v>
       </c>
       <c r="F49" t="n">
-        <v>645.1613</v>
+        <v>306.2796</v>
       </c>
       <c r="G49" t="n">
-        <v>40000000</v>
+        <v>39448818.8976378</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2066,30 +2052,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>113600</v>
+        <v>45900</v>
       </c>
       <c r="F50" t="n">
-        <v>352.1127</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>40000000</v>
+        <v>39207920.79207921</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2098,30 +2084,30 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>31250</v>
+        <v>78200</v>
       </c>
       <c r="F51" t="n">
-        <v>1280</v>
+        <v>502.5508</v>
       </c>
       <c r="G51" t="n">
-        <v>40000000</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2130,20 +2116,20 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>50100</v>
+        <v>115400</v>
       </c>
       <c r="F52" t="n">
-        <v>798.4032</v>
+        <v>335.0149</v>
       </c>
       <c r="G52" t="n">
-        <v>40000000</v>
+        <v>38660714.28571428</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2158,24 +2144,26 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>10320</v>
+        <v>9740</v>
       </c>
       <c r="F53" t="n">
         <v>3875.969</v>
       </c>
       <c r="G53" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>37751937.98449613</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-5.62</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2190,34 +2178,36 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>22400</v>
+        <v>21650</v>
       </c>
       <c r="F54" t="n">
         <v>1785.7143</v>
       </c>
       <c r="G54" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-3.35</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2226,94 +2216,98 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>137800</v>
+        <v>271000</v>
       </c>
       <c r="F55" t="n">
-        <v>290.2758</v>
+        <v>141.0219</v>
       </c>
       <c r="G55" t="n">
-        <v>40000000</v>
+        <v>38216939.07875186</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>71900</v>
+        <v>64300</v>
       </c>
       <c r="F56" t="n">
-        <v>556.3282</v>
+        <v>594.3536</v>
       </c>
       <c r="G56" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>413500</v>
+        <v>56100</v>
       </c>
       <c r="F57" t="n">
-        <v>96.73520000000001</v>
+        <v>700.5254</v>
       </c>
       <c r="G57" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-1.75</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2322,30 +2316,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>67300</v>
+        <v>137300</v>
       </c>
       <c r="F58" t="n">
-        <v>594.3536</v>
+        <v>274.9595</v>
       </c>
       <c r="G58" t="n">
-        <v>40000000</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2354,30 +2348,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>57100</v>
+        <v>59800</v>
       </c>
       <c r="F59" t="n">
-        <v>700.5254</v>
+        <v>638.0242</v>
       </c>
       <c r="G59" t="n">
-        <v>40000000</v>
+        <v>38153846.15384615</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2386,20 +2380,20 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>13890</v>
+        <v>141400</v>
       </c>
       <c r="F60" t="n">
-        <v>2879.7696</v>
+        <v>265.8122</v>
       </c>
       <c r="G60" t="n">
-        <v>40000000</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2414,24 +2408,26 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>10160</v>
+        <v>10020</v>
       </c>
       <c r="F61" t="n">
         <v>3937.0079</v>
       </c>
       <c r="G61" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2446,24 +2442,26 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>30300</v>
+        <v>29700</v>
       </c>
       <c r="F62" t="n">
         <v>1320.132</v>
       </c>
       <c r="G62" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2478,51 +2476,853 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>7150</v>
+        <v>6820</v>
       </c>
       <c r="F63" t="n">
         <v>5594.4056</v>
       </c>
       <c r="G63" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>달바글로벌</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>483650</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>216500</v>
+      </c>
+      <c r="F64" t="n">
+        <v>165.7794</v>
+      </c>
+      <c r="G64" t="n">
+        <v>35891238.67069487</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>001450</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>48850</v>
+      </c>
+      <c r="F65" t="n">
+        <v>818.8332</v>
+      </c>
+      <c r="G65" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>송원산업</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>004430</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>11110</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3600.36</v>
+      </c>
+      <c r="G66" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>한국공항</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>005430</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>81000</v>
+      </c>
+      <c r="F67" t="n">
+        <v>493.8272</v>
+      </c>
+      <c r="G67" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>이수화학</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>005950</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>13240</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3021.148</v>
+      </c>
+      <c r="G68" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>대원전선</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>006340</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>14530</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2752.925</v>
+      </c>
+      <c r="G69" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DN오토모티브</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>007340</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>46650</v>
+      </c>
+      <c r="F70" t="n">
+        <v>857.4491</v>
+      </c>
+      <c r="G70" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>009420</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>62600</v>
+      </c>
+      <c r="F71" t="n">
+        <v>638.9776000000001</v>
+      </c>
+      <c r="G71" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>010950</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>142600</v>
+      </c>
+      <c r="F72" t="n">
+        <v>280.5049</v>
+      </c>
+      <c r="G72" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>48050</v>
+      </c>
+      <c r="F73" t="n">
+        <v>832.4662</v>
+      </c>
+      <c r="G73" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>인바디</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>041830</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>62000</v>
+      </c>
+      <c r="F74" t="n">
+        <v>645.1613</v>
+      </c>
+      <c r="G74" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>078930</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>113600</v>
+      </c>
+      <c r="F75" t="n">
+        <v>352.1127</v>
+      </c>
+      <c r="G75" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>씨젠</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>096530</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>31250</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1280</v>
+      </c>
+      <c r="G76" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>119850</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>50100</v>
+      </c>
+      <c r="F77" t="n">
+        <v>798.4032</v>
+      </c>
+      <c r="G77" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>뉴파워프라즈마</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>144960</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>10320</v>
+      </c>
+      <c r="F78" t="n">
+        <v>3875.969</v>
+      </c>
+      <c r="G78" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>22400</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1785.7143</v>
+      </c>
+      <c r="G79" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>161890</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>137800</v>
+      </c>
+      <c r="F80" t="n">
+        <v>290.2758</v>
+      </c>
+      <c r="G80" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NHN</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>181710</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>71900</v>
+      </c>
+      <c r="F81" t="n">
+        <v>556.3282</v>
+      </c>
+      <c r="G81" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>413500</v>
+      </c>
+      <c r="F82" t="n">
+        <v>96.73520000000001</v>
+      </c>
+      <c r="G82" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>타이거일렉</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>219130</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>67300</v>
+      </c>
+      <c r="F83" t="n">
+        <v>594.3536</v>
+      </c>
+      <c r="G83" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>슈프리마</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>236200</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>57100</v>
+      </c>
+      <c r="F84" t="n">
+        <v>700.5254</v>
+      </c>
+      <c r="G84" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2879.7696</v>
+      </c>
+      <c r="G85" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>자이에스앤디</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>317400</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>10160</v>
+      </c>
+      <c r="F86" t="n">
+        <v>3937.0079</v>
+      </c>
+      <c r="G86" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G87" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F88" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G88" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>SK이터닉스</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>475150</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
         <v>56000</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F89" t="n">
         <v>714.2857</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G89" t="n">
         <v>40000000</v>
       </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,29 +574,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36800</v>
+        <v>12770</v>
       </c>
       <c r="F5" t="n">
-        <v>1048.963</v>
+        <v>2752.925</v>
       </c>
       <c r="G5" t="n">
-        <v>38601838.9</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>35154852.03</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-12.11</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -606,27 +608,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>46000</v>
+        <v>36800</v>
       </c>
       <c r="F6" t="n">
-        <v>8.958600000000001</v>
+        <v>1048.963</v>
       </c>
       <c r="G6" t="n">
-        <v>412095.1</v>
+        <v>38601838.9</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -638,27 +640,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>47650</v>
+        <v>46000</v>
       </c>
       <c r="F7" t="n">
-        <v>159.7361</v>
+        <v>8.958600000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>7611423.9</v>
+        <v>412095.1</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -670,27 +672,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>143600</v>
+        <v>47650</v>
       </c>
       <c r="F8" t="n">
-        <v>18.9174</v>
+        <v>159.7361</v>
       </c>
       <c r="G8" t="n">
-        <v>2716534.1</v>
+        <v>7611423.9</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -702,27 +704,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>216500</v>
+        <v>143600</v>
       </c>
       <c r="F9" t="n">
-        <v>21.1655</v>
+        <v>18.9174</v>
       </c>
       <c r="G9" t="n">
-        <v>4582327.9</v>
+        <v>2716534.1</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -734,27 +736,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>166800</v>
+        <v>216500</v>
       </c>
       <c r="F10" t="n">
-        <v>41.8652</v>
+        <v>21.1655</v>
       </c>
       <c r="G10" t="n">
-        <v>6983122.1</v>
+        <v>4582327.9</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -766,27 +768,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>58000</v>
+        <v>166800</v>
       </c>
       <c r="F11" t="n">
-        <v>5.9271</v>
+        <v>41.8652</v>
       </c>
       <c r="G11" t="n">
-        <v>343773.9</v>
+        <v>6983122.1</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -798,27 +800,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>50300</v>
+        <v>58000</v>
       </c>
       <c r="F12" t="n">
-        <v>75.29649999999999</v>
+        <v>5.9271</v>
       </c>
       <c r="G12" t="n">
-        <v>3787415.1</v>
+        <v>343773.9</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -830,12 +832,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -844,13 +846,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>199600</v>
+        <v>50300</v>
       </c>
       <c r="F13" t="n">
-        <v>12.1097</v>
+        <v>75.29649999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>2417091.1</v>
+        <v>3787415.1</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -862,12 +864,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,13 +878,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>111400</v>
+        <v>199600</v>
       </c>
       <c r="F14" t="n">
-        <v>16.3438</v>
+        <v>12.1097</v>
       </c>
       <c r="G14" t="n">
-        <v>1820696.1</v>
+        <v>2417091.1</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -894,12 +896,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -908,13 +910,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>137200</v>
+        <v>111400</v>
       </c>
       <c r="F15" t="n">
-        <v>25.5948</v>
+        <v>16.3438</v>
       </c>
       <c r="G15" t="n">
-        <v>3511613.1</v>
+        <v>1820696.1</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -926,12 +928,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -940,13 +942,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>32250</v>
+        <v>137200</v>
       </c>
       <c r="F16" t="n">
-        <v>73.12130000000001</v>
+        <v>25.5948</v>
       </c>
       <c r="G16" t="n">
-        <v>2358161.1</v>
+        <v>3511613.1</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -958,27 +960,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>136900</v>
+        <v>32250</v>
       </c>
       <c r="F17" t="n">
-        <v>281.9711</v>
+        <v>73.12130000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>38601838.9</v>
+        <v>2358161.1</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -990,27 +992,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>47450</v>
+        <v>136900</v>
       </c>
       <c r="F18" t="n">
-        <v>11.7985</v>
+        <v>281.9711</v>
       </c>
       <c r="G18" t="n">
-        <v>559838.1</v>
+        <v>38601838.9</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1022,12 +1024,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1036,13 +1038,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>243000</v>
+        <v>47450</v>
       </c>
       <c r="F19" t="n">
-        <v>5.7934</v>
+        <v>11.7985</v>
       </c>
       <c r="G19" t="n">
-        <v>1407799.1</v>
+        <v>559838.1</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1054,12 +1056,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1068,13 +1070,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>150200</v>
+        <v>243000</v>
       </c>
       <c r="F20" t="n">
-        <v>22.6436</v>
+        <v>5.7934</v>
       </c>
       <c r="G20" t="n">
-        <v>3401064.1</v>
+        <v>1407799.1</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1086,27 +1088,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53300</v>
+        <v>150200</v>
       </c>
       <c r="F21" t="n">
-        <v>148.0773</v>
+        <v>22.6436</v>
       </c>
       <c r="G21" t="n">
-        <v>7892520.9</v>
+        <v>3401064.1</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1118,27 +1120,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>280500</v>
+        <v>53300</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1361</v>
+        <v>148.0773</v>
       </c>
       <c r="G22" t="n">
-        <v>38166.1</v>
+        <v>7892520.9</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1150,27 +1152,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>327500</v>
+        <v>280500</v>
       </c>
       <c r="F23" t="n">
-        <v>17.7362</v>
+        <v>0.1361</v>
       </c>
       <c r="G23" t="n">
-        <v>5808609.9</v>
+        <v>38166.1</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1182,12 +1184,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1196,13 +1198,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>129200</v>
+        <v>327500</v>
       </c>
       <c r="F24" t="n">
-        <v>35.7512</v>
+        <v>17.7362</v>
       </c>
       <c r="G24" t="n">
-        <v>4619059.9</v>
+        <v>5808609.9</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1214,27 +1216,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>16590</v>
+        <v>129200</v>
       </c>
       <c r="F25" t="n">
-        <v>513.0315000000001</v>
+        <v>35.7512</v>
       </c>
       <c r="G25" t="n">
-        <v>8511192.1</v>
+        <v>4619059.9</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1246,76 +1248,78 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>42450</v>
+        <v>136600</v>
       </c>
       <c r="F26" t="n">
-        <v>909.3484</v>
+        <v>274.9595</v>
       </c>
       <c r="G26" t="n">
-        <v>38601838.9</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>37559466.34</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.51</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>265500</v>
+        <v>16590</v>
       </c>
       <c r="F27" t="n">
-        <v>123.2792</v>
+        <v>513.0315000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>32730640.59686133</v>
+        <v>8511192.1</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1324,47 +1328,49 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>116300</v>
+        <v>42450</v>
       </c>
       <c r="F28" t="n">
-        <v>332.3224</v>
+        <v>909.3484</v>
       </c>
       <c r="G28" t="n">
-        <v>38649096.95964394</v>
+        <v>38601838.9</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>475150</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>152400</v>
+        <v>49100</v>
       </c>
       <c r="F29" t="n">
-        <v>272.9638</v>
+        <v>714.2857</v>
       </c>
       <c r="G29" t="n">
-        <v>41599689.38070278</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>35071428.57</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-12.32</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1374,12 +1380,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1388,13 +1394,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>44950</v>
+        <v>265500</v>
       </c>
       <c r="F30" t="n">
-        <v>931.6319999999999</v>
+        <v>123.2792</v>
       </c>
       <c r="G30" t="n">
-        <v>41876856.8952711</v>
+        <v>32730640.59686133</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1406,31 +1412,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>48700</v>
+        <v>116300</v>
       </c>
       <c r="F31" t="n">
-        <v>854.2030999999999</v>
+        <v>332.3224</v>
       </c>
       <c r="G31" t="n">
-        <v>41599689.38070278</v>
-      </c>
-      <c r="H31" t="n">
-        <v>6.1</v>
-      </c>
+        <v>38649096.95964394</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1440,31 +1444,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>125000</v>
+        <v>152400</v>
       </c>
       <c r="F32" t="n">
-        <v>335.0149</v>
+        <v>272.9638</v>
       </c>
       <c r="G32" t="n">
-        <v>41876856.8952711</v>
-      </c>
-      <c r="H32" t="n">
-        <v>8.32</v>
-      </c>
+        <v>41599689.38070278</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1474,31 +1476,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>51300</v>
+        <v>44950</v>
       </c>
       <c r="F33" t="n">
-        <v>638.0242</v>
+        <v>931.6319999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>32730640.59686133</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-14.21</v>
-      </c>
+        <v>41876856.8952711</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1522,32 +1522,32 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>145400</v>
+        <v>48700</v>
       </c>
       <c r="F34" t="n">
-        <v>265.8122</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>38649096.95964394</v>
+        <v>41599689.38070278</v>
       </c>
       <c r="H34" t="n">
-        <v>2.83</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1556,81 +1556,85 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>663000</v>
+        <v>125000</v>
       </c>
       <c r="F35" t="n">
-        <v>59.097</v>
+        <v>335.0149</v>
       </c>
       <c r="G35" t="n">
-        <v>39181280.69736513</v>
+        <v>41876856.8952711</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.3</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>236500</v>
+        <v>51300</v>
       </c>
       <c r="F36" t="n">
-        <v>165.6714</v>
+        <v>638.0242</v>
       </c>
       <c r="G36" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>32730640.59686133</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-14.21</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>117900</v>
+        <v>145400</v>
       </c>
       <c r="F37" t="n">
-        <v>268.003</v>
+        <v>265.8122</v>
       </c>
       <c r="G37" t="n">
-        <v>31597552.38168333</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>38649096.95964394</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.83</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1640,12 +1644,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1654,32 +1658,32 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>190600</v>
+        <v>663000</v>
       </c>
       <c r="F38" t="n">
-        <v>165.7794</v>
+        <v>59.097</v>
       </c>
       <c r="G38" t="n">
-        <v>31597552.38168333</v>
+        <v>39181280.69736513</v>
       </c>
       <c r="H38" t="n">
-        <v>-11.96</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1688,81 +1692,81 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>665000</v>
+        <v>236500</v>
       </c>
       <c r="F39" t="n">
-        <v>59.097</v>
+        <v>165.6714</v>
       </c>
       <c r="G39" t="n">
-        <v>39299474.60595447</v>
+        <v>39181280.69736513</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>94200</v>
+        <v>117900</v>
       </c>
       <c r="F40" t="n">
-        <v>390.423</v>
+        <v>268.003</v>
       </c>
       <c r="G40" t="n">
-        <v>36777850.25730231</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-7.83</v>
-      </c>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>240000</v>
+        <v>190600</v>
       </c>
       <c r="F41" t="n">
-        <v>153.241</v>
+        <v>165.7794</v>
       </c>
       <c r="G41" t="n">
-        <v>36777850.25730231</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-11.96</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1772,46 +1776,44 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>78200</v>
+        <v>665000</v>
       </c>
       <c r="F42" t="n">
-        <v>502.5508</v>
+        <v>59.097</v>
       </c>
       <c r="G42" t="n">
         <v>39299474.60595447</v>
       </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1820,66 +1822,64 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>10970</v>
+        <v>94200</v>
       </c>
       <c r="F43" t="n">
-        <v>3600.36</v>
+        <v>390.423</v>
       </c>
       <c r="G43" t="n">
-        <v>39495949.5949595</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.26</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>80800</v>
+        <v>240000</v>
       </c>
       <c r="F44" t="n">
-        <v>493.8272</v>
+        <v>153.241</v>
       </c>
       <c r="G44" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-0.25</v>
-      </c>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1888,16 +1888,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>11880</v>
+        <v>78200</v>
       </c>
       <c r="F45" t="n">
-        <v>3021.148</v>
+        <v>502.5508</v>
       </c>
       <c r="G45" t="n">
-        <v>35891238.67069487</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H45" t="n">
-        <v>-10.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1908,29 +1908,31 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102200</v>
+        <v>10970</v>
       </c>
       <c r="F46" t="n">
-        <v>390.423</v>
+        <v>3600.36</v>
       </c>
       <c r="G46" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>39495949.5949595</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-1.26</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1940,12 +1942,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1954,16 +1956,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>45150</v>
+        <v>80800</v>
       </c>
       <c r="F47" t="n">
-        <v>832.4662</v>
+        <v>493.8272</v>
       </c>
       <c r="G47" t="n">
-        <v>37585848.07492196</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H47" t="n">
-        <v>-6.04</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="48">
@@ -1974,29 +1976,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>194500</v>
+        <v>11880</v>
       </c>
       <c r="F48" t="n">
-        <v>203.064</v>
+        <v>3021.148</v>
       </c>
       <c r="G48" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>35891238.67069487</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-10.27</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2006,12 +2010,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2020,13 +2024,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>128800</v>
+        <v>102200</v>
       </c>
       <c r="F49" t="n">
-        <v>306.2796</v>
+        <v>390.423</v>
       </c>
       <c r="G49" t="n">
-        <v>39448818.8976378</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2038,29 +2042,31 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>45900</v>
+        <v>45150</v>
       </c>
       <c r="F50" t="n">
-        <v>854.2030999999999</v>
+        <v>832.4662</v>
       </c>
       <c r="G50" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-6.04</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2070,12 +2076,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2084,13 +2090,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>78200</v>
+        <v>194500</v>
       </c>
       <c r="F51" t="n">
-        <v>502.5508</v>
+        <v>203.064</v>
       </c>
       <c r="G51" t="n">
-        <v>39299474.60595447</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2102,12 +2108,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2116,13 +2122,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>115400</v>
+        <v>128800</v>
       </c>
       <c r="F52" t="n">
-        <v>335.0149</v>
+        <v>306.2796</v>
       </c>
       <c r="G52" t="n">
-        <v>38660714.28571428</v>
+        <v>39448818.8976378</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2134,31 +2140,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>9740</v>
+        <v>45900</v>
       </c>
       <c r="F53" t="n">
-        <v>3875.969</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-5.62</v>
-      </c>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2168,31 +2172,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>21650</v>
+        <v>78200</v>
       </c>
       <c r="F54" t="n">
-        <v>1785.7143</v>
+        <v>502.5508</v>
       </c>
       <c r="G54" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2202,12 +2204,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2216,13 +2218,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>271000</v>
+        <v>115400</v>
       </c>
       <c r="F55" t="n">
-        <v>141.0219</v>
+        <v>335.0149</v>
       </c>
       <c r="G55" t="n">
-        <v>38216939.07875186</v>
+        <v>38660714.28571428</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2234,12 +2236,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2248,16 +2250,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>64300</v>
+        <v>9740</v>
       </c>
       <c r="F56" t="n">
-        <v>594.3536</v>
+        <v>3875.969</v>
       </c>
       <c r="G56" t="n">
-        <v>38216939.07875186</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H56" t="n">
-        <v>-4.46</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="57">
@@ -2268,12 +2270,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2282,16 +2284,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>56100</v>
+        <v>21650</v>
       </c>
       <c r="F57" t="n">
-        <v>700.5254</v>
+        <v>1785.7143</v>
       </c>
       <c r="G57" t="n">
-        <v>39299474.60595447</v>
+        <v>38660714.28571428</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.75</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="58">
@@ -2302,12 +2304,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2316,13 +2318,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>137300</v>
+        <v>271000</v>
       </c>
       <c r="F58" t="n">
-        <v>274.9595</v>
+        <v>141.0219</v>
       </c>
       <c r="G58" t="n">
-        <v>37751937.98449613</v>
+        <v>38216939.07875186</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2334,29 +2336,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>59800</v>
+        <v>64300</v>
       </c>
       <c r="F59" t="n">
-        <v>638.0242</v>
+        <v>594.3536</v>
       </c>
       <c r="G59" t="n">
-        <v>38153846.15384615</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2366,29 +2370,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>141400</v>
+        <v>56100</v>
       </c>
       <c r="F60" t="n">
-        <v>265.8122</v>
+        <v>700.5254</v>
       </c>
       <c r="G60" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-1.75</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2398,31 +2404,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>10020</v>
+        <v>137300</v>
       </c>
       <c r="F61" t="n">
-        <v>3937.0079</v>
+        <v>274.9595</v>
       </c>
       <c r="G61" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-1.38</v>
-      </c>
+        <v>37751937.98449613</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2432,31 +2436,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>29700</v>
+        <v>59800</v>
       </c>
       <c r="F62" t="n">
-        <v>1320.132</v>
+        <v>638.0242</v>
       </c>
       <c r="G62" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-1.98</v>
-      </c>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2466,31 +2468,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6820</v>
+        <v>141400</v>
       </c>
       <c r="F63" t="n">
-        <v>5594.4056</v>
+        <v>265.8122</v>
       </c>
       <c r="G63" t="n">
-        <v>38153846.15384615</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-4.62</v>
-      </c>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2500,108 +2500,114 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>216500</v>
+        <v>10020</v>
       </c>
       <c r="F64" t="n">
-        <v>165.7794</v>
+        <v>3937.0079</v>
       </c>
       <c r="G64" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>48850</v>
+        <v>29700</v>
       </c>
       <c r="F65" t="n">
-        <v>818.8332</v>
+        <v>1320.132</v>
       </c>
       <c r="G65" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>11110</v>
+        <v>6820</v>
       </c>
       <c r="F66" t="n">
-        <v>3600.36</v>
+        <v>5594.4056</v>
       </c>
       <c r="G66" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2610,13 +2616,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>81000</v>
+        <v>216500</v>
       </c>
       <c r="F67" t="n">
-        <v>493.8272</v>
+        <v>165.7794</v>
       </c>
       <c r="G67" t="n">
-        <v>40000000</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2628,12 +2634,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2642,10 +2648,10 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>13240</v>
+        <v>48850</v>
       </c>
       <c r="F68" t="n">
-        <v>3021.148</v>
+        <v>818.8332</v>
       </c>
       <c r="G68" t="n">
         <v>40000000</v>
@@ -2660,12 +2666,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2674,10 +2680,10 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>14530</v>
+        <v>11110</v>
       </c>
       <c r="F69" t="n">
-        <v>2752.925</v>
+        <v>3600.36</v>
       </c>
       <c r="G69" t="n">
         <v>40000000</v>
@@ -2692,12 +2698,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2706,10 +2712,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>46650</v>
+        <v>81000</v>
       </c>
       <c r="F70" t="n">
-        <v>857.4491</v>
+        <v>493.8272</v>
       </c>
       <c r="G70" t="n">
         <v>40000000</v>
@@ -2724,12 +2730,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2738,10 +2744,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>62600</v>
+        <v>13240</v>
       </c>
       <c r="F71" t="n">
-        <v>638.9776000000001</v>
+        <v>3021.148</v>
       </c>
       <c r="G71" t="n">
         <v>40000000</v>
@@ -2756,12 +2762,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2770,10 +2776,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>142600</v>
+        <v>14530</v>
       </c>
       <c r="F72" t="n">
-        <v>280.5049</v>
+        <v>2752.925</v>
       </c>
       <c r="G72" t="n">
         <v>40000000</v>
@@ -2788,12 +2794,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2802,10 +2808,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>48050</v>
+        <v>46650</v>
       </c>
       <c r="F73" t="n">
-        <v>832.4662</v>
+        <v>857.4491</v>
       </c>
       <c r="G73" t="n">
         <v>40000000</v>
@@ -2820,12 +2826,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2834,10 +2840,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>62000</v>
+        <v>62600</v>
       </c>
       <c r="F74" t="n">
-        <v>645.1613</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G74" t="n">
         <v>40000000</v>
@@ -2852,12 +2858,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2866,10 +2872,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>113600</v>
+        <v>142600</v>
       </c>
       <c r="F75" t="n">
-        <v>352.1127</v>
+        <v>280.5049</v>
       </c>
       <c r="G75" t="n">
         <v>40000000</v>
@@ -2884,12 +2890,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2898,10 +2904,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>31250</v>
+        <v>48050</v>
       </c>
       <c r="F76" t="n">
-        <v>1280</v>
+        <v>832.4662</v>
       </c>
       <c r="G76" t="n">
         <v>40000000</v>
@@ -2916,12 +2922,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2930,10 +2936,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>50100</v>
+        <v>62000</v>
       </c>
       <c r="F77" t="n">
-        <v>798.4032</v>
+        <v>645.1613</v>
       </c>
       <c r="G77" t="n">
         <v>40000000</v>
@@ -2948,12 +2954,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2962,10 +2968,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>10320</v>
+        <v>113600</v>
       </c>
       <c r="F78" t="n">
-        <v>3875.969</v>
+        <v>352.1127</v>
       </c>
       <c r="G78" t="n">
         <v>40000000</v>
@@ -2980,12 +2986,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2994,10 +3000,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>22400</v>
+        <v>31250</v>
       </c>
       <c r="F79" t="n">
-        <v>1785.7143</v>
+        <v>1280</v>
       </c>
       <c r="G79" t="n">
         <v>40000000</v>
@@ -3012,12 +3018,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3026,10 +3032,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>137800</v>
+        <v>50100</v>
       </c>
       <c r="F80" t="n">
-        <v>290.2758</v>
+        <v>798.4032</v>
       </c>
       <c r="G80" t="n">
         <v>40000000</v>
@@ -3044,12 +3050,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3058,10 +3064,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>71900</v>
+        <v>10320</v>
       </c>
       <c r="F81" t="n">
-        <v>556.3282</v>
+        <v>3875.969</v>
       </c>
       <c r="G81" t="n">
         <v>40000000</v>
@@ -3076,12 +3082,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3090,10 +3096,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>413500</v>
+        <v>22400</v>
       </c>
       <c r="F82" t="n">
-        <v>96.73520000000001</v>
+        <v>1785.7143</v>
       </c>
       <c r="G82" t="n">
         <v>40000000</v>
@@ -3108,12 +3114,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3122,10 +3128,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>67300</v>
+        <v>137800</v>
       </c>
       <c r="F83" t="n">
-        <v>594.3536</v>
+        <v>290.2758</v>
       </c>
       <c r="G83" t="n">
         <v>40000000</v>
@@ -3140,12 +3146,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3154,10 +3160,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>57100</v>
+        <v>71900</v>
       </c>
       <c r="F84" t="n">
-        <v>700.5254</v>
+        <v>556.3282</v>
       </c>
       <c r="G84" t="n">
         <v>40000000</v>
@@ -3172,12 +3178,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3186,10 +3192,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>13890</v>
+        <v>413500</v>
       </c>
       <c r="F85" t="n">
-        <v>2879.7696</v>
+        <v>96.73520000000001</v>
       </c>
       <c r="G85" t="n">
         <v>40000000</v>
@@ -3204,12 +3210,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3218,10 +3224,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10160</v>
+        <v>67300</v>
       </c>
       <c r="F86" t="n">
-        <v>3937.0079</v>
+        <v>594.3536</v>
       </c>
       <c r="G86" t="n">
         <v>40000000</v>
@@ -3236,12 +3242,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3250,10 +3256,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>30300</v>
+        <v>57100</v>
       </c>
       <c r="F87" t="n">
-        <v>1320.132</v>
+        <v>700.5254</v>
       </c>
       <c r="G87" t="n">
         <v>40000000</v>
@@ -3268,12 +3274,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3282,10 +3288,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>7150</v>
+        <v>13890</v>
       </c>
       <c r="F88" t="n">
-        <v>5594.4056</v>
+        <v>2879.7696</v>
       </c>
       <c r="G88" t="n">
         <v>40000000</v>
@@ -3300,12 +3306,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3314,15 +3320,111 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>56000</v>
+        <v>10160</v>
       </c>
       <c r="F89" t="n">
-        <v>714.2857</v>
+        <v>3937.0079</v>
       </c>
       <c r="G89" t="n">
         <v>40000000</v>
       </c>
       <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G90" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F91" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G91" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>475150</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>56000</v>
+      </c>
+      <c r="F92" t="n">
+        <v>714.2857</v>
+      </c>
+      <c r="G92" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,64 +473,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>247000</v>
+        <v>225000</v>
       </c>
       <c r="F2" t="n">
-        <v>33.5026</v>
+        <v>174.4065</v>
       </c>
       <c r="G2" t="n">
-        <v>8275143.9</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>39241469.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-5.12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48400</v>
+        <v>59800</v>
       </c>
       <c r="F3" t="n">
-        <v>31.4253</v>
+        <v>656.2119</v>
       </c>
       <c r="G3" t="n">
-        <v>1520986.1</v>
+        <v>39241469.2</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -542,27 +544,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>142700</v>
+        <v>247000</v>
       </c>
       <c r="F4" t="n">
-        <v>64.8394</v>
+        <v>33.5026</v>
       </c>
       <c r="G4" t="n">
-        <v>9252589.1</v>
+        <v>8275143.9</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,31 +576,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12770</v>
+        <v>48400</v>
       </c>
       <c r="F5" t="n">
-        <v>2752.925</v>
+        <v>31.4253</v>
       </c>
       <c r="G5" t="n">
-        <v>35154852.03</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-12.11</v>
-      </c>
+        <v>1520986.1</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,27 +608,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>36800</v>
+        <v>142700</v>
       </c>
       <c r="F6" t="n">
-        <v>1048.963</v>
+        <v>64.8394</v>
       </c>
       <c r="G6" t="n">
-        <v>38601838.9</v>
+        <v>9252589.1</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,29 +640,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>46000</v>
+        <v>12770</v>
       </c>
       <c r="F7" t="n">
-        <v>8.958600000000001</v>
+        <v>2752.925</v>
       </c>
       <c r="G7" t="n">
-        <v>412095.1</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>35154852.03</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-12.11</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -672,27 +674,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>47650</v>
+        <v>36800</v>
       </c>
       <c r="F8" t="n">
-        <v>159.7361</v>
+        <v>1048.963</v>
       </c>
       <c r="G8" t="n">
-        <v>7611423.9</v>
+        <v>38601838.9</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -704,12 +706,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,13 +720,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>143600</v>
+        <v>46000</v>
       </c>
       <c r="F9" t="n">
-        <v>18.9174</v>
+        <v>8.958600000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>2716534.1</v>
+        <v>412095.1</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,12 +738,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,13 +752,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>216500</v>
+        <v>47650</v>
       </c>
       <c r="F10" t="n">
-        <v>21.1655</v>
+        <v>159.7361</v>
       </c>
       <c r="G10" t="n">
-        <v>4582327.9</v>
+        <v>7611423.9</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,12 +770,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -782,13 +784,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>166800</v>
+        <v>143600</v>
       </c>
       <c r="F11" t="n">
-        <v>41.8652</v>
+        <v>18.9174</v>
       </c>
       <c r="G11" t="n">
-        <v>6983122.1</v>
+        <v>2716534.1</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -800,12 +802,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -814,13 +816,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>58000</v>
+        <v>216500</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9271</v>
+        <v>21.1655</v>
       </c>
       <c r="G12" t="n">
-        <v>343773.9</v>
+        <v>4582327.9</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,13 +848,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>50300</v>
+        <v>166800</v>
       </c>
       <c r="F13" t="n">
-        <v>75.29649999999999</v>
+        <v>41.8652</v>
       </c>
       <c r="G13" t="n">
-        <v>3787415.1</v>
+        <v>6983122.1</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -864,27 +866,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>199600</v>
+        <v>58000</v>
       </c>
       <c r="F14" t="n">
-        <v>12.1097</v>
+        <v>5.9271</v>
       </c>
       <c r="G14" t="n">
-        <v>2417091.1</v>
+        <v>343773.9</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -896,12 +898,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -910,13 +912,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>111400</v>
+        <v>50300</v>
       </c>
       <c r="F15" t="n">
-        <v>16.3438</v>
+        <v>75.29649999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1820696.1</v>
+        <v>3787415.1</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -928,12 +930,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -942,13 +944,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>137200</v>
+        <v>199600</v>
       </c>
       <c r="F16" t="n">
-        <v>25.5948</v>
+        <v>12.1097</v>
       </c>
       <c r="G16" t="n">
-        <v>3511613.1</v>
+        <v>2417091.1</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,12 +962,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -974,13 +976,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>32250</v>
+        <v>111400</v>
       </c>
       <c r="F17" t="n">
-        <v>73.12130000000001</v>
+        <v>16.3438</v>
       </c>
       <c r="G17" t="n">
-        <v>2358161.1</v>
+        <v>1820696.1</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -992,27 +994,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>136900</v>
+        <v>137200</v>
       </c>
       <c r="F18" t="n">
-        <v>281.9711</v>
+        <v>25.5948</v>
       </c>
       <c r="G18" t="n">
-        <v>38601838.9</v>
+        <v>3511613.1</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1024,12 +1026,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1038,13 +1040,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>47450</v>
+        <v>32250</v>
       </c>
       <c r="F19" t="n">
-        <v>11.7985</v>
+        <v>73.12130000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>559838.1</v>
+        <v>2358161.1</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1056,27 +1058,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>243000</v>
+        <v>136900</v>
       </c>
       <c r="F20" t="n">
-        <v>5.7934</v>
+        <v>281.9711</v>
       </c>
       <c r="G20" t="n">
-        <v>1407799.1</v>
+        <v>38601838.9</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1088,12 +1090,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1102,13 +1104,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>150200</v>
+        <v>47450</v>
       </c>
       <c r="F21" t="n">
-        <v>22.6436</v>
+        <v>11.7985</v>
       </c>
       <c r="G21" t="n">
-        <v>3401064.1</v>
+        <v>559838.1</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1120,27 +1122,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53300</v>
+        <v>243000</v>
       </c>
       <c r="F22" t="n">
-        <v>148.0773</v>
+        <v>5.7934</v>
       </c>
       <c r="G22" t="n">
-        <v>7892520.9</v>
+        <v>1407799.1</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1152,12 +1154,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1166,13 +1168,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>280500</v>
+        <v>150200</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1361</v>
+        <v>22.6436</v>
       </c>
       <c r="G23" t="n">
-        <v>38166.1</v>
+        <v>3401064.1</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1184,12 +1186,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1198,13 +1200,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>327500</v>
+        <v>53300</v>
       </c>
       <c r="F24" t="n">
-        <v>17.7362</v>
+        <v>148.0773</v>
       </c>
       <c r="G24" t="n">
-        <v>5808609.9</v>
+        <v>7892520.9</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1216,27 +1218,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>129200</v>
+        <v>280500</v>
       </c>
       <c r="F25" t="n">
-        <v>35.7512</v>
+        <v>0.1361</v>
       </c>
       <c r="G25" t="n">
-        <v>4619059.9</v>
+        <v>38166.1</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1248,31 +1250,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>136600</v>
+        <v>327500</v>
       </c>
       <c r="F26" t="n">
-        <v>274.9595</v>
+        <v>17.7362</v>
       </c>
       <c r="G26" t="n">
-        <v>37559466.34</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-0.51</v>
-      </c>
+        <v>5808609.9</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1282,27 +1282,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>16590</v>
+        <v>129200</v>
       </c>
       <c r="F27" t="n">
-        <v>513.0315000000001</v>
+        <v>35.7512</v>
       </c>
       <c r="G27" t="n">
-        <v>8511192.1</v>
+        <v>4619059.9</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1314,29 +1314,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>42450</v>
+        <v>136600</v>
       </c>
       <c r="F28" t="n">
-        <v>909.3484</v>
+        <v>274.9595</v>
       </c>
       <c r="G28" t="n">
-        <v>38601838.9</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>37559466.34</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-0.51</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1346,46 +1348,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>49100</v>
+        <v>16590</v>
       </c>
       <c r="F29" t="n">
-        <v>714.2857</v>
+        <v>513.0315000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>35071428.57</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-12.32</v>
-      </c>
+        <v>8511192.1</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1394,47 +1394,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>265500</v>
+        <v>42450</v>
       </c>
       <c r="F30" t="n">
-        <v>123.2792</v>
+        <v>909.3484</v>
       </c>
       <c r="G30" t="n">
-        <v>32730640.59686133</v>
+        <v>38601838.9</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>475150</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>116300</v>
+        <v>49100</v>
       </c>
       <c r="F31" t="n">
-        <v>332.3224</v>
+        <v>714.2857</v>
       </c>
       <c r="G31" t="n">
-        <v>38649096.95964394</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>35071428.57</v>
+      </c>
+      <c r="H31" t="n">
+        <v>-12.32</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1444,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1458,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>152400</v>
+        <v>265500</v>
       </c>
       <c r="F32" t="n">
-        <v>272.9638</v>
+        <v>123.2792</v>
       </c>
       <c r="G32" t="n">
-        <v>41599689.38070278</v>
+        <v>32730640.59686133</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1476,12 +1478,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1490,13 +1492,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>44950</v>
+        <v>116300</v>
       </c>
       <c r="F33" t="n">
-        <v>931.6319999999999</v>
+        <v>332.3224</v>
       </c>
       <c r="G33" t="n">
-        <v>41876856.8952711</v>
+        <v>38649096.95964394</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1508,31 +1510,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>48700</v>
+        <v>152400</v>
       </c>
       <c r="F34" t="n">
-        <v>854.2030999999999</v>
+        <v>272.9638</v>
       </c>
       <c r="G34" t="n">
         <v>41599689.38070278</v>
       </c>
-      <c r="H34" t="n">
-        <v>6.1</v>
-      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1542,31 +1542,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>125000</v>
+        <v>44950</v>
       </c>
       <c r="F35" t="n">
-        <v>335.0149</v>
+        <v>931.6319999999999</v>
       </c>
       <c r="G35" t="n">
         <v>41876856.8952711</v>
       </c>
-      <c r="H35" t="n">
-        <v>8.32</v>
-      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1576,12 +1574,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1590,16 +1588,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>51300</v>
+        <v>48700</v>
       </c>
       <c r="F36" t="n">
-        <v>638.0242</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>32730640.59686133</v>
+        <v>41599689.38070278</v>
       </c>
       <c r="H36" t="n">
-        <v>-14.21</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="37">
@@ -1610,12 +1608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1624,32 +1622,32 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>145400</v>
+        <v>125000</v>
       </c>
       <c r="F37" t="n">
-        <v>265.8122</v>
+        <v>335.0149</v>
       </c>
       <c r="G37" t="n">
-        <v>38649096.95964394</v>
+        <v>41876856.8952711</v>
       </c>
       <c r="H37" t="n">
-        <v>2.83</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1658,49 +1656,51 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>663000</v>
+        <v>51300</v>
       </c>
       <c r="F38" t="n">
-        <v>59.097</v>
+        <v>638.0242</v>
       </c>
       <c r="G38" t="n">
-        <v>39181280.69736513</v>
+        <v>32730640.59686133</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.3</v>
+        <v>-14.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>236500</v>
+        <v>145400</v>
       </c>
       <c r="F39" t="n">
-        <v>165.6714</v>
+        <v>265.8122</v>
       </c>
       <c r="G39" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>38649096.95964394</v>
+      </c>
+      <c r="H39" t="n">
+        <v>2.83</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1710,29 +1710,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>117900</v>
+        <v>663000</v>
       </c>
       <c r="F40" t="n">
-        <v>268.003</v>
+        <v>59.097</v>
       </c>
       <c r="G40" t="n">
-        <v>31597552.38168333</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1742,46 +1744,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>190600</v>
+        <v>236500</v>
       </c>
       <c r="F41" t="n">
-        <v>165.7794</v>
+        <v>165.6714</v>
       </c>
       <c r="G41" t="n">
-        <v>31597552.38168333</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-11.96</v>
-      </c>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1790,30 +1790,30 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>665000</v>
+        <v>117900</v>
       </c>
       <c r="F42" t="n">
-        <v>59.097</v>
+        <v>268.003</v>
       </c>
       <c r="G42" t="n">
-        <v>39299474.60595447</v>
+        <v>31597552.38168333</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>94200</v>
+        <v>190600</v>
       </c>
       <c r="F43" t="n">
-        <v>390.423</v>
+        <v>165.7794</v>
       </c>
       <c r="G43" t="n">
-        <v>36777850.25730231</v>
+        <v>31597552.38168333</v>
       </c>
       <c r="H43" t="n">
-        <v>-7.83</v>
+        <v>-11.96</v>
       </c>
     </row>
     <row r="44">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1856,13 +1856,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>240000</v>
+        <v>665000</v>
       </c>
       <c r="F44" t="n">
-        <v>153.241</v>
+        <v>59.097</v>
       </c>
       <c r="G44" t="n">
-        <v>36777850.25730231</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1888,66 +1888,64 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>78200</v>
+        <v>94200</v>
       </c>
       <c r="F45" t="n">
-        <v>502.5508</v>
+        <v>390.423</v>
       </c>
       <c r="G45" t="n">
-        <v>39299474.60595447</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>10970</v>
+        <v>240000</v>
       </c>
       <c r="F46" t="n">
-        <v>3600.36</v>
+        <v>153.241</v>
       </c>
       <c r="G46" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-1.26</v>
-      </c>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1956,16 +1954,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>80800</v>
+        <v>78200</v>
       </c>
       <c r="F47" t="n">
-        <v>493.8272</v>
+        <v>502.5508</v>
       </c>
       <c r="G47" t="n">
-        <v>39901234.56790123</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1976,12 +1974,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1990,16 +1988,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>11880</v>
+        <v>10970</v>
       </c>
       <c r="F48" t="n">
-        <v>3021.148</v>
+        <v>3600.36</v>
       </c>
       <c r="G48" t="n">
-        <v>35891238.67069487</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H48" t="n">
-        <v>-10.27</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="49">
@@ -2010,29 +2008,31 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102200</v>
+        <v>80800</v>
       </c>
       <c r="F49" t="n">
-        <v>390.423</v>
+        <v>493.8272</v>
       </c>
       <c r="G49" t="n">
         <v>39901234.56790123</v>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2056,16 +2056,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>45150</v>
+        <v>11880</v>
       </c>
       <c r="F50" t="n">
-        <v>832.4662</v>
+        <v>3021.148</v>
       </c>
       <c r="G50" t="n">
-        <v>37585848.07492196</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H50" t="n">
-        <v>-6.04</v>
+        <v>-10.27</v>
       </c>
     </row>
     <row r="51">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>194500</v>
+        <v>102200</v>
       </c>
       <c r="F51" t="n">
-        <v>203.064</v>
+        <v>390.423</v>
       </c>
       <c r="G51" t="n">
-        <v>39495949.5949595</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2108,29 +2108,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>128800</v>
+        <v>45150</v>
       </c>
       <c r="F52" t="n">
-        <v>306.2796</v>
+        <v>832.4662</v>
       </c>
       <c r="G52" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-6.04</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2140,12 +2142,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2154,13 +2156,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>45900</v>
+        <v>194500</v>
       </c>
       <c r="F53" t="n">
-        <v>854.2030999999999</v>
+        <v>203.064</v>
       </c>
       <c r="G53" t="n">
-        <v>39207920.79207921</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2172,12 +2174,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2186,13 +2188,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>78200</v>
+        <v>128800</v>
       </c>
       <c r="F54" t="n">
-        <v>502.5508</v>
+        <v>306.2796</v>
       </c>
       <c r="G54" t="n">
-        <v>39299474.60595447</v>
+        <v>39448818.8976378</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2204,12 +2206,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2218,13 +2220,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>115400</v>
+        <v>45900</v>
       </c>
       <c r="F55" t="n">
-        <v>335.0149</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>38660714.28571428</v>
+        <v>39207920.79207921</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2236,31 +2238,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>9740</v>
+        <v>78200</v>
       </c>
       <c r="F56" t="n">
-        <v>3875.969</v>
+        <v>502.5508</v>
       </c>
       <c r="G56" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-5.62</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2270,31 +2270,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>21650</v>
+        <v>115400</v>
       </c>
       <c r="F57" t="n">
-        <v>1785.7143</v>
+        <v>335.0149</v>
       </c>
       <c r="G57" t="n">
         <v>38660714.28571428</v>
       </c>
-      <c r="H57" t="n">
-        <v>-3.35</v>
-      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2304,29 +2302,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>271000</v>
+        <v>9740</v>
       </c>
       <c r="F58" t="n">
-        <v>141.0219</v>
+        <v>3875.969</v>
       </c>
       <c r="G58" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>37751937.98449613</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-5.62</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2350,16 +2350,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>64300</v>
+        <v>21650</v>
       </c>
       <c r="F59" t="n">
-        <v>594.3536</v>
+        <v>1785.7143</v>
       </c>
       <c r="G59" t="n">
-        <v>38216939.07875186</v>
+        <v>38660714.28571428</v>
       </c>
       <c r="H59" t="n">
-        <v>-4.46</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="60">
@@ -2370,31 +2370,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>56100</v>
+        <v>271000</v>
       </c>
       <c r="F60" t="n">
-        <v>700.5254</v>
+        <v>141.0219</v>
       </c>
       <c r="G60" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-1.75</v>
-      </c>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2404,29 +2402,31 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>137300</v>
+        <v>64300</v>
       </c>
       <c r="F61" t="n">
-        <v>274.9595</v>
+        <v>594.3536</v>
       </c>
       <c r="G61" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2436,29 +2436,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>59800</v>
+        <v>56100</v>
       </c>
       <c r="F62" t="n">
-        <v>638.0242</v>
+        <v>700.5254</v>
       </c>
       <c r="G62" t="n">
-        <v>38153846.15384615</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-1.75</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2468,12 +2470,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2482,13 +2484,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>141400</v>
+        <v>137300</v>
       </c>
       <c r="F63" t="n">
-        <v>265.8122</v>
+        <v>274.9595</v>
       </c>
       <c r="G63" t="n">
-        <v>37585848.07492196</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2500,31 +2502,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>10020</v>
+        <v>59800</v>
       </c>
       <c r="F64" t="n">
-        <v>3937.0079</v>
+        <v>638.0242</v>
       </c>
       <c r="G64" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-1.38</v>
-      </c>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2534,31 +2534,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>29700</v>
+        <v>141400</v>
       </c>
       <c r="F65" t="n">
-        <v>1320.132</v>
+        <v>265.8122</v>
       </c>
       <c r="G65" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-1.98</v>
-      </c>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2568,12 +2566,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2582,16 +2580,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6820</v>
+        <v>10020</v>
       </c>
       <c r="F66" t="n">
-        <v>5594.4056</v>
+        <v>3937.0079</v>
       </c>
       <c r="G66" t="n">
-        <v>38153846.15384615</v>
+        <v>39448818.8976378</v>
       </c>
       <c r="H66" t="n">
-        <v>-4.62</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="67">
@@ -2602,76 +2600,80 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>216500</v>
+        <v>29700</v>
       </c>
       <c r="F67" t="n">
-        <v>165.7794</v>
+        <v>1320.132</v>
       </c>
       <c r="G67" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>48850</v>
+        <v>6820</v>
       </c>
       <c r="F68" t="n">
-        <v>818.8332</v>
+        <v>5594.4056</v>
       </c>
       <c r="G68" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2680,13 +2682,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>11110</v>
+        <v>216500</v>
       </c>
       <c r="F69" t="n">
-        <v>3600.36</v>
+        <v>165.7794</v>
       </c>
       <c r="G69" t="n">
-        <v>40000000</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2698,12 +2700,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2712,10 +2714,10 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>81000</v>
+        <v>48850</v>
       </c>
       <c r="F70" t="n">
-        <v>493.8272</v>
+        <v>818.8332</v>
       </c>
       <c r="G70" t="n">
         <v>40000000</v>
@@ -2730,12 +2732,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2744,10 +2746,10 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>13240</v>
+        <v>11110</v>
       </c>
       <c r="F71" t="n">
-        <v>3021.148</v>
+        <v>3600.36</v>
       </c>
       <c r="G71" t="n">
         <v>40000000</v>
@@ -2762,12 +2764,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2776,10 +2778,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>14530</v>
+        <v>81000</v>
       </c>
       <c r="F72" t="n">
-        <v>2752.925</v>
+        <v>493.8272</v>
       </c>
       <c r="G72" t="n">
         <v>40000000</v>
@@ -2794,12 +2796,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2808,10 +2810,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>46650</v>
+        <v>13240</v>
       </c>
       <c r="F73" t="n">
-        <v>857.4491</v>
+        <v>3021.148</v>
       </c>
       <c r="G73" t="n">
         <v>40000000</v>
@@ -2826,12 +2828,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2840,10 +2842,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>62600</v>
+        <v>14530</v>
       </c>
       <c r="F74" t="n">
-        <v>638.9776000000001</v>
+        <v>2752.925</v>
       </c>
       <c r="G74" t="n">
         <v>40000000</v>
@@ -2858,12 +2860,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2872,10 +2874,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>142600</v>
+        <v>46650</v>
       </c>
       <c r="F75" t="n">
-        <v>280.5049</v>
+        <v>857.4491</v>
       </c>
       <c r="G75" t="n">
         <v>40000000</v>
@@ -2890,12 +2892,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2904,10 +2906,10 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>48050</v>
+        <v>62600</v>
       </c>
       <c r="F76" t="n">
-        <v>832.4662</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G76" t="n">
         <v>40000000</v>
@@ -2922,12 +2924,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2936,10 +2938,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>62000</v>
+        <v>142600</v>
       </c>
       <c r="F77" t="n">
-        <v>645.1613</v>
+        <v>280.5049</v>
       </c>
       <c r="G77" t="n">
         <v>40000000</v>
@@ -2954,12 +2956,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2968,10 +2970,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>113600</v>
+        <v>48050</v>
       </c>
       <c r="F78" t="n">
-        <v>352.1127</v>
+        <v>832.4662</v>
       </c>
       <c r="G78" t="n">
         <v>40000000</v>
@@ -2986,12 +2988,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3000,10 +3002,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>31250</v>
+        <v>62000</v>
       </c>
       <c r="F79" t="n">
-        <v>1280</v>
+        <v>645.1613</v>
       </c>
       <c r="G79" t="n">
         <v>40000000</v>
@@ -3018,12 +3020,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3032,10 +3034,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>50100</v>
+        <v>113600</v>
       </c>
       <c r="F80" t="n">
-        <v>798.4032</v>
+        <v>352.1127</v>
       </c>
       <c r="G80" t="n">
         <v>40000000</v>
@@ -3050,12 +3052,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3064,10 +3066,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>10320</v>
+        <v>31250</v>
       </c>
       <c r="F81" t="n">
-        <v>3875.969</v>
+        <v>1280</v>
       </c>
       <c r="G81" t="n">
         <v>40000000</v>
@@ -3082,12 +3084,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3096,10 +3098,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>22400</v>
+        <v>50100</v>
       </c>
       <c r="F82" t="n">
-        <v>1785.7143</v>
+        <v>798.4032</v>
       </c>
       <c r="G82" t="n">
         <v>40000000</v>
@@ -3114,12 +3116,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3128,10 +3130,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>137800</v>
+        <v>10320</v>
       </c>
       <c r="F83" t="n">
-        <v>290.2758</v>
+        <v>3875.969</v>
       </c>
       <c r="G83" t="n">
         <v>40000000</v>
@@ -3146,12 +3148,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3160,10 +3162,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>71900</v>
+        <v>22400</v>
       </c>
       <c r="F84" t="n">
-        <v>556.3282</v>
+        <v>1785.7143</v>
       </c>
       <c r="G84" t="n">
         <v>40000000</v>
@@ -3178,12 +3180,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3192,10 +3194,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>413500</v>
+        <v>137800</v>
       </c>
       <c r="F85" t="n">
-        <v>96.73520000000001</v>
+        <v>290.2758</v>
       </c>
       <c r="G85" t="n">
         <v>40000000</v>
@@ -3210,12 +3212,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3224,10 +3226,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>67300</v>
+        <v>71900</v>
       </c>
       <c r="F86" t="n">
-        <v>594.3536</v>
+        <v>556.3282</v>
       </c>
       <c r="G86" t="n">
         <v>40000000</v>
@@ -3242,12 +3244,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3256,10 +3258,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>57100</v>
+        <v>413500</v>
       </c>
       <c r="F87" t="n">
-        <v>700.5254</v>
+        <v>96.73520000000001</v>
       </c>
       <c r="G87" t="n">
         <v>40000000</v>
@@ -3274,12 +3276,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3288,10 +3290,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>13890</v>
+        <v>67300</v>
       </c>
       <c r="F88" t="n">
-        <v>2879.7696</v>
+        <v>594.3536</v>
       </c>
       <c r="G88" t="n">
         <v>40000000</v>
@@ -3306,12 +3308,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3320,10 +3322,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>10160</v>
+        <v>57100</v>
       </c>
       <c r="F89" t="n">
-        <v>3937.0079</v>
+        <v>700.5254</v>
       </c>
       <c r="G89" t="n">
         <v>40000000</v>
@@ -3338,12 +3340,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3352,10 +3354,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>30300</v>
+        <v>13890</v>
       </c>
       <c r="F90" t="n">
-        <v>1320.132</v>
+        <v>2879.7696</v>
       </c>
       <c r="G90" t="n">
         <v>40000000</v>
@@ -3370,12 +3372,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3384,10 +3386,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>7150</v>
+        <v>10160</v>
       </c>
       <c r="F91" t="n">
-        <v>5594.4056</v>
+        <v>3937.0079</v>
       </c>
       <c r="G91" t="n">
         <v>40000000</v>
@@ -3402,12 +3404,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3416,15 +3418,79 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>56000</v>
+        <v>30300</v>
       </c>
       <c r="F92" t="n">
-        <v>714.2857</v>
+        <v>1320.132</v>
       </c>
       <c r="G92" t="n">
         <v>40000000</v>
       </c>
       <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F93" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G93" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>475150</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>56000</v>
+      </c>
+      <c r="F94" t="n">
+        <v>714.2857</v>
+      </c>
+      <c r="G94" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,31 +478,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>008930</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>225000</v>
+        <v>50600</v>
       </c>
       <c r="F2" t="n">
-        <v>174.4065</v>
+        <v>743.4666999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>39241469.2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-5.12</v>
-      </c>
+        <v>37619415.7</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,285 +510,293 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>59800</v>
+        <v>47100</v>
       </c>
       <c r="F3" t="n">
-        <v>656.2119</v>
+        <v>798.7137</v>
       </c>
       <c r="G3" t="n">
-        <v>39241469.2</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>37619415.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-20.99</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>247000</v>
+        <v>225000</v>
       </c>
       <c r="F4" t="n">
-        <v>33.5026</v>
+        <v>174.4065</v>
       </c>
       <c r="G4" t="n">
-        <v>8275143.9</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>39241469.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-5.12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48400</v>
+        <v>208500</v>
       </c>
       <c r="F5" t="n">
-        <v>31.4253</v>
+        <v>178.9817</v>
       </c>
       <c r="G5" t="n">
-        <v>1520986.1</v>
+        <v>37317676.7</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>142700</v>
+        <v>135700</v>
       </c>
       <c r="F6" t="n">
-        <v>64.8394</v>
+        <v>280.6848</v>
       </c>
       <c r="G6" t="n">
-        <v>9252589.1</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>38088927.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.36</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12770</v>
+        <v>144700</v>
       </c>
       <c r="F7" t="n">
-        <v>2752.925</v>
+        <v>263.2269</v>
       </c>
       <c r="G7" t="n">
-        <v>35154852.03</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-12.11</v>
-      </c>
+        <v>38088927.7</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>36800</v>
+        <v>269500</v>
       </c>
       <c r="F8" t="n">
-        <v>1048.963</v>
+        <v>159.878</v>
       </c>
       <c r="G8" t="n">
-        <v>38601838.9</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>43087111.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>13.95</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>46000</v>
+        <v>25300</v>
       </c>
       <c r="F9" t="n">
-        <v>8.958600000000001</v>
+        <v>1703.0479</v>
       </c>
       <c r="G9" t="n">
-        <v>412095.1</v>
+        <v>43087111.6</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>47650</v>
+        <v>326000</v>
       </c>
       <c r="F10" t="n">
-        <v>159.7361</v>
+        <v>114.4714</v>
       </c>
       <c r="G10" t="n">
-        <v>7611423.9</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>37317676.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-18.54</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>143600</v>
+        <v>59800</v>
       </c>
       <c r="F11" t="n">
-        <v>18.9174</v>
+        <v>656.2119</v>
       </c>
       <c r="G11" t="n">
-        <v>2716534.1</v>
+        <v>39241469.2</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,12 +808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -816,13 +822,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>216500</v>
+        <v>247000</v>
       </c>
       <c r="F12" t="n">
-        <v>21.1655</v>
+        <v>33.5026</v>
       </c>
       <c r="G12" t="n">
-        <v>4582327.9</v>
+        <v>8275143.9</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,12 +840,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,13 +854,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>166800</v>
+        <v>48400</v>
       </c>
       <c r="F13" t="n">
-        <v>41.8652</v>
+        <v>31.4253</v>
       </c>
       <c r="G13" t="n">
-        <v>6983122.1</v>
+        <v>1520986.1</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,27 +872,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>58000</v>
+        <v>142700</v>
       </c>
       <c r="F14" t="n">
-        <v>5.9271</v>
+        <v>64.8394</v>
       </c>
       <c r="G14" t="n">
-        <v>343773.9</v>
+        <v>9252589.1</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,29 +904,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>50300</v>
+        <v>12770</v>
       </c>
       <c r="F15" t="n">
-        <v>75.29649999999999</v>
+        <v>2752.925</v>
       </c>
       <c r="G15" t="n">
-        <v>3787415.1</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>35154852.03</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-12.11</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -930,27 +938,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>199600</v>
+        <v>36800</v>
       </c>
       <c r="F16" t="n">
-        <v>12.1097</v>
+        <v>1048.963</v>
       </c>
       <c r="G16" t="n">
-        <v>2417091.1</v>
+        <v>38601838.9</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -962,12 +970,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -976,13 +984,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>111400</v>
+        <v>46000</v>
       </c>
       <c r="F17" t="n">
-        <v>16.3438</v>
+        <v>8.958600000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>1820696.1</v>
+        <v>412095.1</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,27 +1002,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>137200</v>
+        <v>47650</v>
       </c>
       <c r="F18" t="n">
-        <v>25.5948</v>
+        <v>159.7361</v>
       </c>
       <c r="G18" t="n">
-        <v>3511613.1</v>
+        <v>7611423.9</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,12 +1034,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1040,13 +1048,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>32250</v>
+        <v>143600</v>
       </c>
       <c r="F19" t="n">
-        <v>73.12130000000001</v>
+        <v>18.9174</v>
       </c>
       <c r="G19" t="n">
-        <v>2358161.1</v>
+        <v>2716534.1</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,27 +1066,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>136900</v>
+        <v>216500</v>
       </c>
       <c r="F20" t="n">
-        <v>281.9711</v>
+        <v>21.1655</v>
       </c>
       <c r="G20" t="n">
-        <v>38601838.9</v>
+        <v>4582327.9</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1090,12 +1098,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1104,13 +1112,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>47450</v>
+        <v>166800</v>
       </c>
       <c r="F21" t="n">
-        <v>11.7985</v>
+        <v>41.8652</v>
       </c>
       <c r="G21" t="n">
-        <v>559838.1</v>
+        <v>6983122.1</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1122,27 +1130,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>243000</v>
+        <v>58000</v>
       </c>
       <c r="F22" t="n">
-        <v>5.7934</v>
+        <v>5.9271</v>
       </c>
       <c r="G22" t="n">
-        <v>1407799.1</v>
+        <v>343773.9</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1154,12 +1162,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1168,13 +1176,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>150200</v>
+        <v>50300</v>
       </c>
       <c r="F23" t="n">
-        <v>22.6436</v>
+        <v>75.29649999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>3401064.1</v>
+        <v>3787415.1</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1186,27 +1194,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53300</v>
+        <v>199600</v>
       </c>
       <c r="F24" t="n">
-        <v>148.0773</v>
+        <v>12.1097</v>
       </c>
       <c r="G24" t="n">
-        <v>7892520.9</v>
+        <v>2417091.1</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1218,12 +1226,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1232,13 +1240,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>280500</v>
+        <v>111400</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1361</v>
+        <v>16.3438</v>
       </c>
       <c r="G25" t="n">
-        <v>38166.1</v>
+        <v>1820696.1</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1250,27 +1258,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>327500</v>
+        <v>137200</v>
       </c>
       <c r="F26" t="n">
-        <v>17.7362</v>
+        <v>25.5948</v>
       </c>
       <c r="G26" t="n">
-        <v>5808609.9</v>
+        <v>3511613.1</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1282,27 +1290,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>129200</v>
+        <v>32250</v>
       </c>
       <c r="F27" t="n">
-        <v>35.7512</v>
+        <v>73.12130000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>4619059.9</v>
+        <v>2358161.1</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1314,31 +1322,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>136600</v>
+        <v>136900</v>
       </c>
       <c r="F28" t="n">
-        <v>274.9595</v>
+        <v>281.9711</v>
       </c>
       <c r="G28" t="n">
-        <v>37559466.34</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-0.51</v>
-      </c>
+        <v>38601838.9</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1348,12 +1354,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1362,13 +1368,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>16590</v>
+        <v>47450</v>
       </c>
       <c r="F29" t="n">
-        <v>513.0315000000001</v>
+        <v>11.7985</v>
       </c>
       <c r="G29" t="n">
-        <v>8511192.1</v>
+        <v>559838.1</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1380,27 +1386,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>42450</v>
+        <v>243000</v>
       </c>
       <c r="F30" t="n">
-        <v>909.3484</v>
+        <v>5.7934</v>
       </c>
       <c r="G30" t="n">
-        <v>38601838.9</v>
+        <v>1407799.1</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1412,174 +1418,172 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>49100</v>
+        <v>150200</v>
       </c>
       <c r="F31" t="n">
-        <v>714.2857</v>
+        <v>22.6436</v>
       </c>
       <c r="G31" t="n">
-        <v>35071428.57</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-12.32</v>
-      </c>
+        <v>3401064.1</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>265500</v>
+        <v>53300</v>
       </c>
       <c r="F32" t="n">
-        <v>123.2792</v>
+        <v>148.0773</v>
       </c>
       <c r="G32" t="n">
-        <v>32730640.59686133</v>
+        <v>7892520.9</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>116300</v>
+        <v>280500</v>
       </c>
       <c r="F33" t="n">
-        <v>332.3224</v>
+        <v>0.1361</v>
       </c>
       <c r="G33" t="n">
-        <v>38649096.95964394</v>
+        <v>38166.1</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>152400</v>
+        <v>327500</v>
       </c>
       <c r="F34" t="n">
-        <v>272.9638</v>
+        <v>17.7362</v>
       </c>
       <c r="G34" t="n">
-        <v>41599689.38070278</v>
+        <v>5808609.9</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>44950</v>
+        <v>129200</v>
       </c>
       <c r="F35" t="n">
-        <v>931.6319999999999</v>
+        <v>35.7512</v>
       </c>
       <c r="G35" t="n">
-        <v>41876856.8952711</v>
+        <v>4619059.9</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1588,100 +1592,96 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>48700</v>
+        <v>136600</v>
       </c>
       <c r="F36" t="n">
-        <v>854.2030999999999</v>
+        <v>274.9595</v>
       </c>
       <c r="G36" t="n">
-        <v>41599689.38070278</v>
+        <v>37559466.34</v>
       </c>
       <c r="H36" t="n">
-        <v>6.1</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>125000</v>
+        <v>16590</v>
       </c>
       <c r="F37" t="n">
-        <v>335.0149</v>
+        <v>513.0315000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>41876856.8952711</v>
-      </c>
-      <c r="H37" t="n">
-        <v>8.32</v>
-      </c>
+        <v>8511192.1</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>51300</v>
+        <v>42450</v>
       </c>
       <c r="F38" t="n">
-        <v>638.0242</v>
+        <v>909.3484</v>
       </c>
       <c r="G38" t="n">
-        <v>32730640.59686133</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-14.21</v>
-      </c>
+        <v>38601838.9</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>475150</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1690,66 +1690,64 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>145400</v>
+        <v>49100</v>
       </c>
       <c r="F39" t="n">
-        <v>265.8122</v>
+        <v>714.2857</v>
       </c>
       <c r="G39" t="n">
-        <v>38649096.95964394</v>
+        <v>35071428.57</v>
       </c>
       <c r="H39" t="n">
-        <v>2.83</v>
+        <v>-12.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>663000</v>
+        <v>265500</v>
       </c>
       <c r="F40" t="n">
-        <v>59.097</v>
+        <v>123.2792</v>
       </c>
       <c r="G40" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>32730640.59686133</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1758,30 +1756,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>236500</v>
+        <v>116300</v>
       </c>
       <c r="F41" t="n">
-        <v>165.6714</v>
+        <v>332.3224</v>
       </c>
       <c r="G41" t="n">
-        <v>39181280.69736513</v>
+        <v>38649096.95964394</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1790,96 +1788,96 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>117900</v>
+        <v>152400</v>
       </c>
       <c r="F42" t="n">
-        <v>268.003</v>
+        <v>272.9638</v>
       </c>
       <c r="G42" t="n">
-        <v>31597552.38168333</v>
+        <v>41599689.38070278</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>190600</v>
+        <v>44950</v>
       </c>
       <c r="F43" t="n">
-        <v>165.7794</v>
+        <v>931.6319999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>31597552.38168333</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-11.96</v>
-      </c>
+        <v>41876856.8952711</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>665000</v>
+        <v>48700</v>
       </c>
       <c r="F44" t="n">
-        <v>59.097</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>41599689.38070278</v>
+      </c>
+      <c r="H44" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1888,64 +1886,66 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>94200</v>
+        <v>125000</v>
       </c>
       <c r="F45" t="n">
-        <v>390.423</v>
+        <v>335.0149</v>
       </c>
       <c r="G45" t="n">
-        <v>36777850.25730231</v>
+        <v>41876856.8952711</v>
       </c>
       <c r="H45" t="n">
-        <v>-7.83</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>240000</v>
+        <v>51300</v>
       </c>
       <c r="F46" t="n">
-        <v>153.241</v>
+        <v>638.0242</v>
       </c>
       <c r="G46" t="n">
-        <v>36777850.25730231</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>32730640.59686133</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-14.21</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1954,32 +1954,32 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>78200</v>
+        <v>145400</v>
       </c>
       <c r="F47" t="n">
-        <v>502.5508</v>
+        <v>265.8122</v>
       </c>
       <c r="G47" t="n">
-        <v>39299474.60595447</v>
+        <v>38649096.95964394</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1988,198 +1988,196 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>10970</v>
+        <v>663000</v>
       </c>
       <c r="F48" t="n">
-        <v>3600.36</v>
+        <v>59.097</v>
       </c>
       <c r="G48" t="n">
-        <v>39495949.5949595</v>
+        <v>39181280.69736513</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.26</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>80800</v>
+        <v>236500</v>
       </c>
       <c r="F49" t="n">
-        <v>493.8272</v>
+        <v>165.6714</v>
       </c>
       <c r="G49" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-0.25</v>
-      </c>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>11880</v>
+        <v>117900</v>
       </c>
       <c r="F50" t="n">
-        <v>3021.148</v>
+        <v>268.003</v>
       </c>
       <c r="G50" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-10.27</v>
-      </c>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102200</v>
+        <v>190600</v>
       </c>
       <c r="F51" t="n">
-        <v>390.423</v>
+        <v>165.7794</v>
       </c>
       <c r="G51" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-11.96</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>45150</v>
+        <v>665000</v>
       </c>
       <c r="F52" t="n">
-        <v>832.4662</v>
+        <v>59.097</v>
       </c>
       <c r="G52" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-6.04</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>194500</v>
+        <v>94200</v>
       </c>
       <c r="F53" t="n">
-        <v>203.064</v>
+        <v>390.423</v>
       </c>
       <c r="G53" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-7.83</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2188,47 +2186,49 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>128800</v>
+        <v>240000</v>
       </c>
       <c r="F54" t="n">
-        <v>306.2796</v>
+        <v>153.241</v>
       </c>
       <c r="G54" t="n">
-        <v>39448818.8976378</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>45900</v>
+        <v>78200</v>
       </c>
       <c r="F55" t="n">
-        <v>854.2030999999999</v>
+        <v>502.5508</v>
       </c>
       <c r="G55" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2238,29 +2238,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>78200</v>
+        <v>10970</v>
       </c>
       <c r="F56" t="n">
-        <v>502.5508</v>
+        <v>3600.36</v>
       </c>
       <c r="G56" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>39495949.5949595</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-1.26</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2270,29 +2272,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>115400</v>
+        <v>80800</v>
       </c>
       <c r="F57" t="n">
-        <v>335.0149</v>
+        <v>493.8272</v>
       </c>
       <c r="G57" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2302,12 +2306,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2316,16 +2320,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>9740</v>
+        <v>11880</v>
       </c>
       <c r="F58" t="n">
-        <v>3875.969</v>
+        <v>3021.148</v>
       </c>
       <c r="G58" t="n">
-        <v>37751937.98449613</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H58" t="n">
-        <v>-5.62</v>
+        <v>-10.27</v>
       </c>
     </row>
     <row r="59">
@@ -2336,31 +2340,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>21650</v>
+        <v>102200</v>
       </c>
       <c r="F59" t="n">
-        <v>1785.7143</v>
+        <v>390.423</v>
       </c>
       <c r="G59" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2370,29 +2372,31 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>271000</v>
+        <v>45150</v>
       </c>
       <c r="F60" t="n">
-        <v>141.0219</v>
+        <v>832.4662</v>
       </c>
       <c r="G60" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-6.04</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2402,31 +2406,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>64300</v>
+        <v>194500</v>
       </c>
       <c r="F61" t="n">
-        <v>594.3536</v>
+        <v>203.064</v>
       </c>
       <c r="G61" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-4.46</v>
-      </c>
+        <v>39495949.5949595</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2436,31 +2438,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>56100</v>
+        <v>128800</v>
       </c>
       <c r="F62" t="n">
-        <v>700.5254</v>
+        <v>306.2796</v>
       </c>
       <c r="G62" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-1.75</v>
-      </c>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2484,13 +2484,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>137300</v>
+        <v>45900</v>
       </c>
       <c r="F63" t="n">
-        <v>274.9595</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>37751937.98449613</v>
+        <v>39207920.79207921</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2502,12 +2502,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2516,13 +2516,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>59800</v>
+        <v>78200</v>
       </c>
       <c r="F64" t="n">
-        <v>638.0242</v>
+        <v>502.5508</v>
       </c>
       <c r="G64" t="n">
-        <v>38153846.15384615</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2534,12 +2534,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2548,13 +2548,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>141400</v>
+        <v>115400</v>
       </c>
       <c r="F65" t="n">
-        <v>265.8122</v>
+        <v>335.0149</v>
       </c>
       <c r="G65" t="n">
-        <v>37585848.07492196</v>
+        <v>38660714.28571428</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2580,16 +2580,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>10020</v>
+        <v>9740</v>
       </c>
       <c r="F66" t="n">
-        <v>3937.0079</v>
+        <v>3875.969</v>
       </c>
       <c r="G66" t="n">
-        <v>39448818.8976378</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.38</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="67">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2614,16 +2614,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>29700</v>
+        <v>21650</v>
       </c>
       <c r="F67" t="n">
-        <v>1320.132</v>
+        <v>1785.7143</v>
       </c>
       <c r="G67" t="n">
-        <v>39207920.79207921</v>
+        <v>38660714.28571428</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.98</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="68">
@@ -2634,31 +2634,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6820</v>
+        <v>271000</v>
       </c>
       <c r="F68" t="n">
-        <v>5594.4056</v>
+        <v>141.0219</v>
       </c>
       <c r="G68" t="n">
-        <v>38153846.15384615</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-4.62</v>
-      </c>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2668,76 +2666,80 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>216500</v>
+        <v>64300</v>
       </c>
       <c r="F69" t="n">
-        <v>165.7794</v>
+        <v>594.3536</v>
       </c>
       <c r="G69" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>48850</v>
+        <v>56100</v>
       </c>
       <c r="F70" t="n">
-        <v>818.8332</v>
+        <v>700.5254</v>
       </c>
       <c r="G70" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-1.75</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2746,30 +2748,30 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>11110</v>
+        <v>137300</v>
       </c>
       <c r="F71" t="n">
-        <v>3600.36</v>
+        <v>274.9595</v>
       </c>
       <c r="G71" t="n">
-        <v>40000000</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2778,30 +2780,30 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>81000</v>
+        <v>59800</v>
       </c>
       <c r="F72" t="n">
-        <v>493.8272</v>
+        <v>638.0242</v>
       </c>
       <c r="G72" t="n">
-        <v>40000000</v>
+        <v>38153846.15384615</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2810,126 +2812,132 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>13240</v>
+        <v>141400</v>
       </c>
       <c r="F73" t="n">
-        <v>3021.148</v>
+        <v>265.8122</v>
       </c>
       <c r="G73" t="n">
-        <v>40000000</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>14530</v>
+        <v>10020</v>
       </c>
       <c r="F74" t="n">
-        <v>2752.925</v>
+        <v>3937.0079</v>
       </c>
       <c r="G74" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>46650</v>
+        <v>29700</v>
       </c>
       <c r="F75" t="n">
-        <v>857.4491</v>
+        <v>1320.132</v>
       </c>
       <c r="G75" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>62600</v>
+        <v>6820</v>
       </c>
       <c r="F76" t="n">
-        <v>638.9776000000001</v>
+        <v>5594.4056</v>
       </c>
       <c r="G76" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2938,13 +2946,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>142600</v>
+        <v>216500</v>
       </c>
       <c r="F77" t="n">
-        <v>280.5049</v>
+        <v>165.7794</v>
       </c>
       <c r="G77" t="n">
-        <v>40000000</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2956,12 +2964,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2970,10 +2978,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>48050</v>
+        <v>48850</v>
       </c>
       <c r="F78" t="n">
-        <v>832.4662</v>
+        <v>818.8332</v>
       </c>
       <c r="G78" t="n">
         <v>40000000</v>
@@ -2988,12 +2996,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3002,10 +3010,10 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>62000</v>
+        <v>11110</v>
       </c>
       <c r="F79" t="n">
-        <v>645.1613</v>
+        <v>3600.36</v>
       </c>
       <c r="G79" t="n">
         <v>40000000</v>
@@ -3020,12 +3028,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3034,10 +3042,10 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>113600</v>
+        <v>81000</v>
       </c>
       <c r="F80" t="n">
-        <v>352.1127</v>
+        <v>493.8272</v>
       </c>
       <c r="G80" t="n">
         <v>40000000</v>
@@ -3052,12 +3060,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3066,10 +3074,10 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>31250</v>
+        <v>13240</v>
       </c>
       <c r="F81" t="n">
-        <v>1280</v>
+        <v>3021.148</v>
       </c>
       <c r="G81" t="n">
         <v>40000000</v>
@@ -3084,12 +3092,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3098,10 +3106,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>50100</v>
+        <v>14530</v>
       </c>
       <c r="F82" t="n">
-        <v>798.4032</v>
+        <v>2752.925</v>
       </c>
       <c r="G82" t="n">
         <v>40000000</v>
@@ -3116,12 +3124,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3130,10 +3138,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>10320</v>
+        <v>46650</v>
       </c>
       <c r="F83" t="n">
-        <v>3875.969</v>
+        <v>857.4491</v>
       </c>
       <c r="G83" t="n">
         <v>40000000</v>
@@ -3148,12 +3156,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3162,10 +3170,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>22400</v>
+        <v>62600</v>
       </c>
       <c r="F84" t="n">
-        <v>1785.7143</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G84" t="n">
         <v>40000000</v>
@@ -3180,12 +3188,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3194,10 +3202,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>137800</v>
+        <v>142600</v>
       </c>
       <c r="F85" t="n">
-        <v>290.2758</v>
+        <v>280.5049</v>
       </c>
       <c r="G85" t="n">
         <v>40000000</v>
@@ -3212,12 +3220,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3226,10 +3234,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>71900</v>
+        <v>48050</v>
       </c>
       <c r="F86" t="n">
-        <v>556.3282</v>
+        <v>832.4662</v>
       </c>
       <c r="G86" t="n">
         <v>40000000</v>
@@ -3244,12 +3252,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3258,10 +3266,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>413500</v>
+        <v>62000</v>
       </c>
       <c r="F87" t="n">
-        <v>96.73520000000001</v>
+        <v>645.1613</v>
       </c>
       <c r="G87" t="n">
         <v>40000000</v>
@@ -3276,12 +3284,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3290,10 +3298,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>67300</v>
+        <v>113600</v>
       </c>
       <c r="F88" t="n">
-        <v>594.3536</v>
+        <v>352.1127</v>
       </c>
       <c r="G88" t="n">
         <v>40000000</v>
@@ -3308,12 +3316,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3322,10 +3330,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>57100</v>
+        <v>31250</v>
       </c>
       <c r="F89" t="n">
-        <v>700.5254</v>
+        <v>1280</v>
       </c>
       <c r="G89" t="n">
         <v>40000000</v>
@@ -3340,12 +3348,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3354,10 +3362,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>13890</v>
+        <v>50100</v>
       </c>
       <c r="F90" t="n">
-        <v>2879.7696</v>
+        <v>798.4032</v>
       </c>
       <c r="G90" t="n">
         <v>40000000</v>
@@ -3372,12 +3380,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3386,10 +3394,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>10160</v>
+        <v>10320</v>
       </c>
       <c r="F91" t="n">
-        <v>3937.0079</v>
+        <v>3875.969</v>
       </c>
       <c r="G91" t="n">
         <v>40000000</v>
@@ -3404,12 +3412,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3418,10 +3426,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>30300</v>
+        <v>22400</v>
       </c>
       <c r="F92" t="n">
-        <v>1320.132</v>
+        <v>1785.7143</v>
       </c>
       <c r="G92" t="n">
         <v>40000000</v>
@@ -3436,12 +3444,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3450,10 +3458,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>7150</v>
+        <v>137800</v>
       </c>
       <c r="F93" t="n">
-        <v>5594.4056</v>
+        <v>290.2758</v>
       </c>
       <c r="G93" t="n">
         <v>40000000</v>
@@ -3468,12 +3476,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3482,15 +3490,271 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>56000</v>
+        <v>71900</v>
       </c>
       <c r="F94" t="n">
-        <v>714.2857</v>
+        <v>556.3282</v>
       </c>
       <c r="G94" t="n">
         <v>40000000</v>
       </c>
       <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>413500</v>
+      </c>
+      <c r="F95" t="n">
+        <v>96.73520000000001</v>
+      </c>
+      <c r="G95" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>타이거일렉</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>219130</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>67300</v>
+      </c>
+      <c r="F96" t="n">
+        <v>594.3536</v>
+      </c>
+      <c r="G96" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>슈프리마</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>236200</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>57100</v>
+      </c>
+      <c r="F97" t="n">
+        <v>700.5254</v>
+      </c>
+      <c r="G97" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2879.7696</v>
+      </c>
+      <c r="G98" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>자이에스앤디</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>317400</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>10160</v>
+      </c>
+      <c r="F99" t="n">
+        <v>3937.0079</v>
+      </c>
+      <c r="G99" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G100" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F101" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G101" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>475150</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>56000</v>
+      </c>
+      <c r="F102" t="n">
+        <v>714.2857</v>
+      </c>
+      <c r="G102" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>DB손해보험</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>005830</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,30 +492,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>50600</v>
+        <v>192100</v>
       </c>
       <c r="F2" t="n">
-        <v>743.4666999999999</v>
+        <v>181.3286</v>
       </c>
       <c r="G2" t="n">
-        <v>37619415.7</v>
+        <v>34833230.8</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,32 +524,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>47100</v>
+        <v>53500</v>
       </c>
       <c r="F3" t="n">
-        <v>798.7137</v>
+        <v>651.0884</v>
       </c>
       <c r="G3" t="n">
-        <v>37619415.7</v>
+        <v>34833230.8</v>
       </c>
       <c r="H3" t="n">
-        <v>-20.99</v>
+        <v>-13.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,32 +558,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>225000</v>
+        <v>214000</v>
       </c>
       <c r="F4" t="n">
-        <v>174.4065</v>
+        <v>190.9543</v>
       </c>
       <c r="G4" t="n">
-        <v>39241469.2</v>
+        <v>40864227.3</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.12</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -592,81 +592,81 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>208500</v>
+        <v>13070</v>
       </c>
       <c r="F5" t="n">
-        <v>178.9817</v>
+        <v>2664.7317</v>
       </c>
       <c r="G5" t="n">
-        <v>37317676.7</v>
+        <v>34828043.1</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>135700</v>
+        <v>8280</v>
       </c>
       <c r="F6" t="n">
-        <v>280.6848</v>
+        <v>4935.2932</v>
       </c>
       <c r="G6" t="n">
-        <v>38088927.7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5.36</v>
-      </c>
+        <v>40864227.3</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>090430</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>144700</v>
+        <v>38300</v>
       </c>
       <c r="F7" t="n">
-        <v>263.2269</v>
+        <v>909.3484</v>
       </c>
       <c r="G7" t="n">
-        <v>38088927.7</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>34828043.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-9.779999999999999</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -676,31 +676,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>008930</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>269500</v>
+        <v>50600</v>
       </c>
       <c r="F8" t="n">
-        <v>159.878</v>
+        <v>743.4666999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>43087111.6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>13.95</v>
-      </c>
+        <v>37619415.7</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -710,29 +708,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>25300</v>
+        <v>47100</v>
       </c>
       <c r="F9" t="n">
-        <v>1703.0479</v>
+        <v>798.7137</v>
       </c>
       <c r="G9" t="n">
-        <v>43087111.6</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>37619415.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-20.99</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>326000</v>
+        <v>225000</v>
       </c>
       <c r="F10" t="n">
-        <v>114.4714</v>
+        <v>174.4065</v>
       </c>
       <c r="G10" t="n">
-        <v>37317676.7</v>
+        <v>39241469.2</v>
       </c>
       <c r="H10" t="n">
-        <v>-18.54</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="11">
@@ -776,12 +776,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -790,207 +790,211 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>59800</v>
+        <v>208500</v>
       </c>
       <c r="F11" t="n">
-        <v>656.2119</v>
+        <v>178.9817</v>
       </c>
       <c r="G11" t="n">
-        <v>39241469.2</v>
+        <v>37317676.7</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>247000</v>
+        <v>135700</v>
       </c>
       <c r="F12" t="n">
-        <v>33.5026</v>
+        <v>280.6848</v>
       </c>
       <c r="G12" t="n">
-        <v>8275143.9</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>38088927.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.36</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>48400</v>
+        <v>144700</v>
       </c>
       <c r="F13" t="n">
-        <v>31.4253</v>
+        <v>263.2269</v>
       </c>
       <c r="G13" t="n">
-        <v>1520986.1</v>
+        <v>38088927.7</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>142700</v>
+        <v>269500</v>
       </c>
       <c r="F14" t="n">
-        <v>64.8394</v>
+        <v>159.878</v>
       </c>
       <c r="G14" t="n">
-        <v>9252589.1</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>43087111.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>13.95</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12770</v>
+        <v>25300</v>
       </c>
       <c r="F15" t="n">
-        <v>2752.925</v>
+        <v>1703.0479</v>
       </c>
       <c r="G15" t="n">
-        <v>35154852.03</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-12.11</v>
-      </c>
+        <v>43087111.6</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>36800</v>
+        <v>326000</v>
       </c>
       <c r="F16" t="n">
-        <v>1048.963</v>
+        <v>114.4714</v>
       </c>
       <c r="G16" t="n">
-        <v>38601838.9</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>37317676.7</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-18.54</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>46000</v>
+        <v>59800</v>
       </c>
       <c r="F17" t="n">
-        <v>8.958600000000001</v>
+        <v>656.2119</v>
       </c>
       <c r="G17" t="n">
-        <v>412095.1</v>
+        <v>39241469.2</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1002,12 +1006,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1016,13 +1020,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>47650</v>
+        <v>247000</v>
       </c>
       <c r="F18" t="n">
-        <v>159.7361</v>
+        <v>33.5026</v>
       </c>
       <c r="G18" t="n">
-        <v>7611423.9</v>
+        <v>8275143.9</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1034,12 +1038,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1048,13 +1052,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>143600</v>
+        <v>48400</v>
       </c>
       <c r="F19" t="n">
-        <v>18.9174</v>
+        <v>31.4253</v>
       </c>
       <c r="G19" t="n">
-        <v>2716534.1</v>
+        <v>1520986.1</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1066,27 +1070,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>216500</v>
+        <v>142700</v>
       </c>
       <c r="F20" t="n">
-        <v>21.1655</v>
+        <v>64.8394</v>
       </c>
       <c r="G20" t="n">
-        <v>4582327.9</v>
+        <v>9252589.1</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1098,29 +1102,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>166800</v>
+        <v>12770</v>
       </c>
       <c r="F21" t="n">
-        <v>41.8652</v>
+        <v>2752.925</v>
       </c>
       <c r="G21" t="n">
-        <v>6983122.1</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>35154852.03</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-12.11</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1130,27 +1136,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>58000</v>
+        <v>36800</v>
       </c>
       <c r="F22" t="n">
-        <v>5.9271</v>
+        <v>1048.963</v>
       </c>
       <c r="G22" t="n">
-        <v>343773.9</v>
+        <v>38601838.9</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1162,12 +1168,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1176,13 +1182,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>50300</v>
+        <v>46000</v>
       </c>
       <c r="F23" t="n">
-        <v>75.29649999999999</v>
+        <v>8.958600000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>3787415.1</v>
+        <v>412095.1</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1194,27 +1200,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>199600</v>
+        <v>47650</v>
       </c>
       <c r="F24" t="n">
-        <v>12.1097</v>
+        <v>159.7361</v>
       </c>
       <c r="G24" t="n">
-        <v>2417091.1</v>
+        <v>7611423.9</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1226,12 +1232,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1240,13 +1246,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>111400</v>
+        <v>143600</v>
       </c>
       <c r="F25" t="n">
-        <v>16.3438</v>
+        <v>18.9174</v>
       </c>
       <c r="G25" t="n">
-        <v>1820696.1</v>
+        <v>2716534.1</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1258,27 +1264,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>137200</v>
+        <v>216500</v>
       </c>
       <c r="F26" t="n">
-        <v>25.5948</v>
+        <v>21.1655</v>
       </c>
       <c r="G26" t="n">
-        <v>3511613.1</v>
+        <v>4582327.9</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1290,12 +1296,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1304,13 +1310,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>32250</v>
+        <v>166800</v>
       </c>
       <c r="F27" t="n">
-        <v>73.12130000000001</v>
+        <v>41.8652</v>
       </c>
       <c r="G27" t="n">
-        <v>2358161.1</v>
+        <v>6983122.1</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1322,27 +1328,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>136900</v>
+        <v>58000</v>
       </c>
       <c r="F28" t="n">
-        <v>281.9711</v>
+        <v>5.9271</v>
       </c>
       <c r="G28" t="n">
-        <v>38601838.9</v>
+        <v>343773.9</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1354,12 +1360,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1368,13 +1374,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>47450</v>
+        <v>50300</v>
       </c>
       <c r="F29" t="n">
-        <v>11.7985</v>
+        <v>75.29649999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>559838.1</v>
+        <v>3787415.1</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1386,12 +1392,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1400,13 +1406,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>243000</v>
+        <v>199600</v>
       </c>
       <c r="F30" t="n">
-        <v>5.7934</v>
+        <v>12.1097</v>
       </c>
       <c r="G30" t="n">
-        <v>1407799.1</v>
+        <v>2417091.1</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1418,12 +1424,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1432,13 +1438,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>150200</v>
+        <v>111400</v>
       </c>
       <c r="F31" t="n">
-        <v>22.6436</v>
+        <v>16.3438</v>
       </c>
       <c r="G31" t="n">
-        <v>3401064.1</v>
+        <v>1820696.1</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1450,27 +1456,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>53300</v>
+        <v>137200</v>
       </c>
       <c r="F32" t="n">
-        <v>148.0773</v>
+        <v>25.5948</v>
       </c>
       <c r="G32" t="n">
-        <v>7892520.9</v>
+        <v>3511613.1</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1482,12 +1488,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1496,13 +1502,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>280500</v>
+        <v>32250</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1361</v>
+        <v>73.12130000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>38166.1</v>
+        <v>2358161.1</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1514,27 +1520,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>327500</v>
+        <v>136900</v>
       </c>
       <c r="F34" t="n">
-        <v>17.7362</v>
+        <v>281.9711</v>
       </c>
       <c r="G34" t="n">
-        <v>5808609.9</v>
+        <v>38601838.9</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1546,27 +1552,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>129200</v>
+        <v>47450</v>
       </c>
       <c r="F35" t="n">
-        <v>35.7512</v>
+        <v>11.7985</v>
       </c>
       <c r="G35" t="n">
-        <v>4619059.9</v>
+        <v>559838.1</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1578,31 +1584,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>136600</v>
+        <v>243000</v>
       </c>
       <c r="F36" t="n">
-        <v>274.9595</v>
+        <v>5.7934</v>
       </c>
       <c r="G36" t="n">
-        <v>37559466.34</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-0.51</v>
-      </c>
+        <v>1407799.1</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1612,12 +1616,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1626,13 +1630,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>16590</v>
+        <v>150200</v>
       </c>
       <c r="F37" t="n">
-        <v>513.0315000000001</v>
+        <v>22.6436</v>
       </c>
       <c r="G37" t="n">
-        <v>8511192.1</v>
+        <v>3401064.1</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1644,27 +1648,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>42450</v>
+        <v>53300</v>
       </c>
       <c r="F38" t="n">
-        <v>909.3484</v>
+        <v>148.0773</v>
       </c>
       <c r="G38" t="n">
-        <v>38601838.9</v>
+        <v>7892520.9</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1676,208 +1680,206 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>49100</v>
+        <v>280500</v>
       </c>
       <c r="F39" t="n">
-        <v>714.2857</v>
+        <v>0.1361</v>
       </c>
       <c r="G39" t="n">
-        <v>35071428.57</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-12.32</v>
-      </c>
+        <v>38166.1</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>265500</v>
+        <v>327500</v>
       </c>
       <c r="F40" t="n">
-        <v>123.2792</v>
+        <v>17.7362</v>
       </c>
       <c r="G40" t="n">
-        <v>32730640.59686133</v>
+        <v>5808609.9</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>116300</v>
+        <v>129200</v>
       </c>
       <c r="F41" t="n">
-        <v>332.3224</v>
+        <v>35.7512</v>
       </c>
       <c r="G41" t="n">
-        <v>38649096.95964394</v>
+        <v>4619059.9</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>152400</v>
+        <v>136600</v>
       </c>
       <c r="F42" t="n">
-        <v>272.9638</v>
+        <v>274.9595</v>
       </c>
       <c r="G42" t="n">
-        <v>41599689.38070278</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>37559466.34</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.51</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>44950</v>
+        <v>16590</v>
       </c>
       <c r="F43" t="n">
-        <v>931.6319999999999</v>
+        <v>513.0315000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>41876856.8952711</v>
+        <v>8511192.1</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>48700</v>
+        <v>42450</v>
       </c>
       <c r="F44" t="n">
-        <v>854.2030999999999</v>
+        <v>909.3484</v>
       </c>
       <c r="G44" t="n">
-        <v>41599689.38070278</v>
-      </c>
-      <c r="H44" t="n">
-        <v>6.1</v>
-      </c>
+        <v>38601838.9</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>475150</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1886,16 +1888,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>125000</v>
+        <v>49100</v>
       </c>
       <c r="F45" t="n">
-        <v>335.0149</v>
+        <v>714.2857</v>
       </c>
       <c r="G45" t="n">
-        <v>41876856.8952711</v>
+        <v>35071428.57</v>
       </c>
       <c r="H45" t="n">
-        <v>8.32</v>
+        <v>-12.32</v>
       </c>
     </row>
     <row r="46">
@@ -1906,31 +1908,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>51300</v>
+        <v>265500</v>
       </c>
       <c r="F46" t="n">
-        <v>638.0242</v>
+        <v>123.2792</v>
       </c>
       <c r="G46" t="n">
         <v>32730640.59686133</v>
       </c>
-      <c r="H46" t="n">
-        <v>-14.21</v>
-      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1940,80 +1940,76 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>145400</v>
+        <v>116300</v>
       </c>
       <c r="F47" t="n">
-        <v>265.8122</v>
+        <v>332.3224</v>
       </c>
       <c r="G47" t="n">
         <v>38649096.95964394</v>
       </c>
-      <c r="H47" t="n">
-        <v>2.83</v>
-      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>663000</v>
+        <v>152400</v>
       </c>
       <c r="F48" t="n">
-        <v>59.097</v>
+        <v>272.9638</v>
       </c>
       <c r="G48" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>41599689.38070278</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2022,62 +2018,64 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>236500</v>
+        <v>44950</v>
       </c>
       <c r="F49" t="n">
-        <v>165.6714</v>
+        <v>931.6319999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>39181280.69736513</v>
+        <v>41876856.8952711</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>117900</v>
+        <v>48700</v>
       </c>
       <c r="F50" t="n">
-        <v>268.003</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>31597552.38168333</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>41599689.38070278</v>
+      </c>
+      <c r="H50" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2086,64 +2084,66 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>190600</v>
+        <v>125000</v>
       </c>
       <c r="F51" t="n">
-        <v>165.7794</v>
+        <v>335.0149</v>
       </c>
       <c r="G51" t="n">
-        <v>31597552.38168333</v>
+        <v>41876856.8952711</v>
       </c>
       <c r="H51" t="n">
-        <v>-11.96</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>665000</v>
+        <v>51300</v>
       </c>
       <c r="F52" t="n">
-        <v>59.097</v>
+        <v>638.0242</v>
       </c>
       <c r="G52" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>32730640.59686133</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-14.21</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2152,132 +2152,130 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>94200</v>
+        <v>145400</v>
       </c>
       <c r="F53" t="n">
-        <v>390.423</v>
+        <v>265.8122</v>
       </c>
       <c r="G53" t="n">
-        <v>36777850.25730231</v>
+        <v>38649096.95964394</v>
       </c>
       <c r="H53" t="n">
-        <v>-7.83</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>240000</v>
+        <v>663000</v>
       </c>
       <c r="F54" t="n">
-        <v>153.241</v>
+        <v>59.097</v>
       </c>
       <c r="G54" t="n">
-        <v>36777850.25730231</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>78200</v>
+        <v>236500</v>
       </c>
       <c r="F55" t="n">
-        <v>502.5508</v>
+        <v>165.6714</v>
       </c>
       <c r="G55" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>10970</v>
+        <v>117900</v>
       </c>
       <c r="F56" t="n">
-        <v>3600.36</v>
+        <v>268.003</v>
       </c>
       <c r="G56" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-1.26</v>
-      </c>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2286,56 +2284,54 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>80800</v>
+        <v>190600</v>
       </c>
       <c r="F57" t="n">
-        <v>493.8272</v>
+        <v>165.7794</v>
       </c>
       <c r="G57" t="n">
-        <v>39901234.56790123</v>
+        <v>31597552.38168333</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.25</v>
+        <v>-11.96</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>11880</v>
+        <v>665000</v>
       </c>
       <c r="F58" t="n">
-        <v>3021.148</v>
+        <v>59.097</v>
       </c>
       <c r="G58" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-10.27</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2350,85 +2346,87 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>102200</v>
+        <v>94200</v>
       </c>
       <c r="F59" t="n">
         <v>390.423</v>
       </c>
       <c r="G59" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-7.83</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>45150</v>
+        <v>240000</v>
       </c>
       <c r="F60" t="n">
-        <v>832.4662</v>
+        <v>153.241</v>
       </c>
       <c r="G60" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-6.04</v>
-      </c>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>194500</v>
+        <v>78200</v>
       </c>
       <c r="F61" t="n">
-        <v>203.064</v>
+        <v>502.5508</v>
       </c>
       <c r="G61" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2438,29 +2436,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>128800</v>
+        <v>10970</v>
       </c>
       <c r="F62" t="n">
-        <v>306.2796</v>
+        <v>3600.36</v>
       </c>
       <c r="G62" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>39495949.5949595</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-1.26</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2470,29 +2470,31 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>45900</v>
+        <v>80800</v>
       </c>
       <c r="F63" t="n">
-        <v>854.2030999999999</v>
+        <v>493.8272</v>
       </c>
       <c r="G63" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2502,29 +2504,31 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>78200</v>
+        <v>11880</v>
       </c>
       <c r="F64" t="n">
-        <v>502.5508</v>
+        <v>3021.148</v>
       </c>
       <c r="G64" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>35891238.67069487</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-10.27</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2534,12 +2538,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2548,13 +2552,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>115400</v>
+        <v>102200</v>
       </c>
       <c r="F65" t="n">
-        <v>335.0149</v>
+        <v>390.423</v>
       </c>
       <c r="G65" t="n">
-        <v>38660714.28571428</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2566,12 +2570,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2580,16 +2584,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>9740</v>
+        <v>45150</v>
       </c>
       <c r="F66" t="n">
-        <v>3875.969</v>
+        <v>832.4662</v>
       </c>
       <c r="G66" t="n">
-        <v>37751937.98449613</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H66" t="n">
-        <v>-5.62</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="67">
@@ -2600,31 +2604,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>21650</v>
+        <v>194500</v>
       </c>
       <c r="F67" t="n">
-        <v>1785.7143</v>
+        <v>203.064</v>
       </c>
       <c r="G67" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>39495949.5949595</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2634,12 +2636,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2648,13 +2650,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>271000</v>
+        <v>128800</v>
       </c>
       <c r="F68" t="n">
-        <v>141.0219</v>
+        <v>306.2796</v>
       </c>
       <c r="G68" t="n">
-        <v>38216939.07875186</v>
+        <v>39448818.8976378</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2666,31 +2668,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>64300</v>
+        <v>45900</v>
       </c>
       <c r="F69" t="n">
-        <v>594.3536</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-4.46</v>
-      </c>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2700,31 +2700,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>56100</v>
+        <v>78200</v>
       </c>
       <c r="F70" t="n">
-        <v>700.5254</v>
+        <v>502.5508</v>
       </c>
       <c r="G70" t="n">
         <v>39299474.60595447</v>
       </c>
-      <c r="H70" t="n">
-        <v>-1.75</v>
-      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2734,12 +2732,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2748,13 +2746,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>137300</v>
+        <v>115400</v>
       </c>
       <c r="F71" t="n">
-        <v>274.9595</v>
+        <v>335.0149</v>
       </c>
       <c r="G71" t="n">
-        <v>37751937.98449613</v>
+        <v>38660714.28571428</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2766,29 +2764,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>59800</v>
+        <v>9740</v>
       </c>
       <c r="F72" t="n">
-        <v>638.0242</v>
+        <v>3875.969</v>
       </c>
       <c r="G72" t="n">
-        <v>38153846.15384615</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>37751937.98449613</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-5.62</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2798,29 +2798,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>141400</v>
+        <v>21650</v>
       </c>
       <c r="F73" t="n">
-        <v>265.8122</v>
+        <v>1785.7143</v>
       </c>
       <c r="G73" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-3.35</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2830,31 +2832,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>10020</v>
+        <v>271000</v>
       </c>
       <c r="F74" t="n">
-        <v>3937.0079</v>
+        <v>141.0219</v>
       </c>
       <c r="G74" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-1.38</v>
-      </c>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2878,16 +2878,16 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>29700</v>
+        <v>64300</v>
       </c>
       <c r="F75" t="n">
-        <v>1320.132</v>
+        <v>594.3536</v>
       </c>
       <c r="G75" t="n">
-        <v>39207920.79207921</v>
+        <v>38216939.07875186</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.98</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="76">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2912,16 +2912,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6820</v>
+        <v>56100</v>
       </c>
       <c r="F76" t="n">
-        <v>5594.4056</v>
+        <v>700.5254</v>
       </c>
       <c r="G76" t="n">
-        <v>38153846.15384615</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H76" t="n">
-        <v>-4.62</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="77">
@@ -2932,12 +2932,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2946,30 +2946,30 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>216500</v>
+        <v>137300</v>
       </c>
       <c r="F77" t="n">
-        <v>165.7794</v>
+        <v>274.9595</v>
       </c>
       <c r="G77" t="n">
-        <v>35891238.67069487</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2978,30 +2978,30 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>48850</v>
+        <v>59800</v>
       </c>
       <c r="F78" t="n">
-        <v>818.8332</v>
+        <v>638.0242</v>
       </c>
       <c r="G78" t="n">
-        <v>40000000</v>
+        <v>38153846.15384615</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3010,126 +3010,132 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>11110</v>
+        <v>141400</v>
       </c>
       <c r="F79" t="n">
-        <v>3600.36</v>
+        <v>265.8122</v>
       </c>
       <c r="G79" t="n">
-        <v>40000000</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>81000</v>
+        <v>10020</v>
       </c>
       <c r="F80" t="n">
-        <v>493.8272</v>
+        <v>3937.0079</v>
       </c>
       <c r="G80" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>13240</v>
+        <v>29700</v>
       </c>
       <c r="F81" t="n">
-        <v>3021.148</v>
+        <v>1320.132</v>
       </c>
       <c r="G81" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>14530</v>
+        <v>6820</v>
       </c>
       <c r="F82" t="n">
-        <v>2752.925</v>
+        <v>5594.4056</v>
       </c>
       <c r="G82" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3138,13 +3144,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>46650</v>
+        <v>216500</v>
       </c>
       <c r="F83" t="n">
-        <v>857.4491</v>
+        <v>165.7794</v>
       </c>
       <c r="G83" t="n">
-        <v>40000000</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3156,12 +3162,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3170,10 +3176,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>62600</v>
+        <v>48850</v>
       </c>
       <c r="F84" t="n">
-        <v>638.9776000000001</v>
+        <v>818.8332</v>
       </c>
       <c r="G84" t="n">
         <v>40000000</v>
@@ -3188,12 +3194,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3202,10 +3208,10 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>142600</v>
+        <v>11110</v>
       </c>
       <c r="F85" t="n">
-        <v>280.5049</v>
+        <v>3600.36</v>
       </c>
       <c r="G85" t="n">
         <v>40000000</v>
@@ -3220,12 +3226,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3234,10 +3240,10 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>48050</v>
+        <v>81000</v>
       </c>
       <c r="F86" t="n">
-        <v>832.4662</v>
+        <v>493.8272</v>
       </c>
       <c r="G86" t="n">
         <v>40000000</v>
@@ -3252,12 +3258,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3266,10 +3272,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>62000</v>
+        <v>13240</v>
       </c>
       <c r="F87" t="n">
-        <v>645.1613</v>
+        <v>3021.148</v>
       </c>
       <c r="G87" t="n">
         <v>40000000</v>
@@ -3284,12 +3290,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3298,10 +3304,10 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>113600</v>
+        <v>14530</v>
       </c>
       <c r="F88" t="n">
-        <v>352.1127</v>
+        <v>2752.925</v>
       </c>
       <c r="G88" t="n">
         <v>40000000</v>
@@ -3316,12 +3322,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3330,10 +3336,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>31250</v>
+        <v>46650</v>
       </c>
       <c r="F89" t="n">
-        <v>1280</v>
+        <v>857.4491</v>
       </c>
       <c r="G89" t="n">
         <v>40000000</v>
@@ -3348,12 +3354,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3362,10 +3368,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>50100</v>
+        <v>62600</v>
       </c>
       <c r="F90" t="n">
-        <v>798.4032</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G90" t="n">
         <v>40000000</v>
@@ -3380,12 +3386,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3394,10 +3400,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>10320</v>
+        <v>142600</v>
       </c>
       <c r="F91" t="n">
-        <v>3875.969</v>
+        <v>280.5049</v>
       </c>
       <c r="G91" t="n">
         <v>40000000</v>
@@ -3412,12 +3418,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3426,10 +3432,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>22400</v>
+        <v>48050</v>
       </c>
       <c r="F92" t="n">
-        <v>1785.7143</v>
+        <v>832.4662</v>
       </c>
       <c r="G92" t="n">
         <v>40000000</v>
@@ -3444,12 +3450,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3458,10 +3464,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>137800</v>
+        <v>62000</v>
       </c>
       <c r="F93" t="n">
-        <v>290.2758</v>
+        <v>645.1613</v>
       </c>
       <c r="G93" t="n">
         <v>40000000</v>
@@ -3476,12 +3482,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3490,10 +3496,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>71900</v>
+        <v>113600</v>
       </c>
       <c r="F94" t="n">
-        <v>556.3282</v>
+        <v>352.1127</v>
       </c>
       <c r="G94" t="n">
         <v>40000000</v>
@@ -3508,12 +3514,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3522,10 +3528,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>413500</v>
+        <v>31250</v>
       </c>
       <c r="F95" t="n">
-        <v>96.73520000000001</v>
+        <v>1280</v>
       </c>
       <c r="G95" t="n">
         <v>40000000</v>
@@ -3540,12 +3546,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3554,10 +3560,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>67300</v>
+        <v>50100</v>
       </c>
       <c r="F96" t="n">
-        <v>594.3536</v>
+        <v>798.4032</v>
       </c>
       <c r="G96" t="n">
         <v>40000000</v>
@@ -3572,12 +3578,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3586,10 +3592,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>57100</v>
+        <v>10320</v>
       </c>
       <c r="F97" t="n">
-        <v>700.5254</v>
+        <v>3875.969</v>
       </c>
       <c r="G97" t="n">
         <v>40000000</v>
@@ -3604,12 +3610,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3618,10 +3624,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>13890</v>
+        <v>22400</v>
       </c>
       <c r="F98" t="n">
-        <v>2879.7696</v>
+        <v>1785.7143</v>
       </c>
       <c r="G98" t="n">
         <v>40000000</v>
@@ -3636,12 +3642,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3650,10 +3656,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>10160</v>
+        <v>137800</v>
       </c>
       <c r="F99" t="n">
-        <v>3937.0079</v>
+        <v>290.2758</v>
       </c>
       <c r="G99" t="n">
         <v>40000000</v>
@@ -3668,12 +3674,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3682,10 +3688,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>30300</v>
+        <v>71900</v>
       </c>
       <c r="F100" t="n">
-        <v>1320.132</v>
+        <v>556.3282</v>
       </c>
       <c r="G100" t="n">
         <v>40000000</v>
@@ -3700,12 +3706,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3714,10 +3720,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>7150</v>
+        <v>413500</v>
       </c>
       <c r="F101" t="n">
-        <v>5594.4056</v>
+        <v>96.73520000000001</v>
       </c>
       <c r="G101" t="n">
         <v>40000000</v>
@@ -3732,12 +3738,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3746,15 +3752,207 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>56000</v>
+        <v>67300</v>
       </c>
       <c r="F102" t="n">
-        <v>714.2857</v>
+        <v>594.3536</v>
       </c>
       <c r="G102" t="n">
         <v>40000000</v>
       </c>
       <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>슈프리마</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>236200</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>57100</v>
+      </c>
+      <c r="F103" t="n">
+        <v>700.5254</v>
+      </c>
+      <c r="G103" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2879.7696</v>
+      </c>
+      <c r="G104" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>자이에스앤디</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>317400</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>10160</v>
+      </c>
+      <c r="F105" t="n">
+        <v>3937.0079</v>
+      </c>
+      <c r="G105" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G106" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F107" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G107" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>475150</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>56000</v>
+      </c>
+      <c r="F108" t="n">
+        <v>714.2857</v>
+      </c>
+      <c r="G108" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,83 +473,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DB손해보험</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>005830</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>192100</v>
+        <v>109800</v>
       </c>
       <c r="F2" t="n">
-        <v>181.3286</v>
+        <v>335.7689</v>
       </c>
       <c r="G2" t="n">
-        <v>34833230.8</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>36867425.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-3.35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>오킨스전자</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>080580</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53500</v>
+        <v>27700</v>
       </c>
       <c r="F3" t="n">
-        <v>651.0884</v>
+        <v>1434.2409</v>
       </c>
       <c r="G3" t="n">
-        <v>34833230.8</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-13.66</v>
-      </c>
+        <v>39728473</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,64 +558,66 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>214000</v>
+        <v>138300</v>
       </c>
       <c r="F4" t="n">
-        <v>190.9543</v>
+        <v>263.2269</v>
       </c>
       <c r="G4" t="n">
-        <v>40864227.3</v>
+        <v>36404275.7</v>
       </c>
       <c r="H4" t="n">
-        <v>10.03</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13070</v>
+        <v>56400</v>
       </c>
       <c r="F5" t="n">
-        <v>2664.7317</v>
+        <v>704.4055</v>
       </c>
       <c r="G5" t="n">
-        <v>34828043.1</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>39728473</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-17.05</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>SK케미칼</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>192650</t>
+          <t>285130</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,13 +626,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>8280</v>
+        <v>51000</v>
       </c>
       <c r="F6" t="n">
-        <v>4935.2932</v>
+        <v>722.8907</v>
       </c>
       <c r="G6" t="n">
-        <v>40864227.3</v>
+        <v>36867425.8</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -642,78 +644,78 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>DB손해보험</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>005830</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>38300</v>
+        <v>192100</v>
       </c>
       <c r="F7" t="n">
-        <v>909.3484</v>
+        <v>181.3286</v>
       </c>
       <c r="G7" t="n">
-        <v>34828043.1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-9.779999999999999</v>
-      </c>
+        <v>34833230.8</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>50600</v>
+        <v>53500</v>
       </c>
       <c r="F8" t="n">
-        <v>743.4666999999999</v>
+        <v>651.0884</v>
       </c>
       <c r="G8" t="n">
-        <v>37619415.7</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>34833230.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-13.66</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -722,66 +724,64 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47100</v>
+        <v>214000</v>
       </c>
       <c r="F9" t="n">
-        <v>798.7137</v>
+        <v>190.9543</v>
       </c>
       <c r="G9" t="n">
-        <v>37619415.7</v>
+        <v>40864227.3</v>
       </c>
       <c r="H9" t="n">
-        <v>-20.99</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>225000</v>
+        <v>13070</v>
       </c>
       <c r="F10" t="n">
-        <v>174.4065</v>
+        <v>2664.7317</v>
       </c>
       <c r="G10" t="n">
-        <v>39241469.2</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-5.12</v>
-      </c>
+        <v>34828043.1</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -790,30 +790,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208500</v>
+        <v>8280</v>
       </c>
       <c r="F11" t="n">
-        <v>178.9817</v>
+        <v>4935.2932</v>
       </c>
       <c r="G11" t="n">
-        <v>37317676.7</v>
+        <v>40864227.3</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>135700</v>
+        <v>38300</v>
       </c>
       <c r="F12" t="n">
-        <v>280.6848</v>
+        <v>909.3484</v>
       </c>
       <c r="G12" t="n">
-        <v>38088927.7</v>
+        <v>34828043.1</v>
       </c>
       <c r="H12" t="n">
-        <v>5.36</v>
+        <v>-9.779999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -842,12 +842,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>090430</t>
+          <t>008930</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -856,13 +856,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>144700</v>
+        <v>50600</v>
       </c>
       <c r="F13" t="n">
-        <v>263.2269</v>
+        <v>743.4666999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>38088927.7</v>
+        <v>37619415.7</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>269500</v>
+        <v>47100</v>
       </c>
       <c r="F14" t="n">
-        <v>159.878</v>
+        <v>798.7137</v>
       </c>
       <c r="G14" t="n">
-        <v>43087111.6</v>
+        <v>37619415.7</v>
       </c>
       <c r="H14" t="n">
-        <v>13.95</v>
+        <v>-20.99</v>
       </c>
     </row>
     <row r="15">
@@ -908,29 +908,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25300</v>
+        <v>225000</v>
       </c>
       <c r="F15" t="n">
-        <v>1703.0479</v>
+        <v>174.4065</v>
       </c>
       <c r="G15" t="n">
-        <v>43087111.6</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>39241469.2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-5.12</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -940,31 +942,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>326000</v>
+        <v>208500</v>
       </c>
       <c r="F16" t="n">
-        <v>114.4714</v>
+        <v>178.9817</v>
       </c>
       <c r="G16" t="n">
         <v>37317676.7</v>
       </c>
-      <c r="H16" t="n">
-        <v>-18.54</v>
-      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -974,140 +974,144 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>59800</v>
+        <v>135700</v>
       </c>
       <c r="F17" t="n">
-        <v>656.2119</v>
+        <v>280.6848</v>
       </c>
       <c r="G17" t="n">
-        <v>39241469.2</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>38088927.7</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5.36</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>247000</v>
+        <v>144700</v>
       </c>
       <c r="F18" t="n">
-        <v>33.5026</v>
+        <v>263.2269</v>
       </c>
       <c r="G18" t="n">
-        <v>8275143.9</v>
+        <v>38088927.7</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48400</v>
+        <v>269500</v>
       </c>
       <c r="F19" t="n">
-        <v>31.4253</v>
+        <v>159.878</v>
       </c>
       <c r="G19" t="n">
-        <v>1520986.1</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>43087111.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>13.95</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>142700</v>
+        <v>25300</v>
       </c>
       <c r="F20" t="n">
-        <v>64.8394</v>
+        <v>1703.0479</v>
       </c>
       <c r="G20" t="n">
-        <v>9252589.1</v>
+        <v>43087111.6</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1116,32 +1120,32 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>12770</v>
+        <v>326000</v>
       </c>
       <c r="F21" t="n">
-        <v>2752.925</v>
+        <v>114.4714</v>
       </c>
       <c r="G21" t="n">
-        <v>35154852.03</v>
+        <v>37317676.7</v>
       </c>
       <c r="H21" t="n">
-        <v>-12.11</v>
+        <v>-18.54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1150,13 +1154,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>36800</v>
+        <v>59800</v>
       </c>
       <c r="F22" t="n">
-        <v>1048.963</v>
+        <v>656.2119</v>
       </c>
       <c r="G22" t="n">
-        <v>38601838.9</v>
+        <v>39241469.2</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1168,27 +1172,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>46000</v>
+        <v>247000</v>
       </c>
       <c r="F23" t="n">
-        <v>8.958600000000001</v>
+        <v>33.5026</v>
       </c>
       <c r="G23" t="n">
-        <v>412095.1</v>
+        <v>8275143.9</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1200,27 +1204,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>47650</v>
+        <v>48400</v>
       </c>
       <c r="F24" t="n">
-        <v>159.7361</v>
+        <v>31.4253</v>
       </c>
       <c r="G24" t="n">
-        <v>7611423.9</v>
+        <v>1520986.1</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1232,12 +1236,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1246,13 +1250,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>143600</v>
+        <v>142700</v>
       </c>
       <c r="F25" t="n">
-        <v>18.9174</v>
+        <v>64.8394</v>
       </c>
       <c r="G25" t="n">
-        <v>2716534.1</v>
+        <v>9252589.1</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1264,29 +1268,31 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>216500</v>
+        <v>12770</v>
       </c>
       <c r="F26" t="n">
-        <v>21.1655</v>
+        <v>2752.925</v>
       </c>
       <c r="G26" t="n">
-        <v>4582327.9</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>35154852.03</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-12.11</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1296,27 +1302,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>166800</v>
+        <v>36800</v>
       </c>
       <c r="F27" t="n">
-        <v>41.8652</v>
+        <v>1048.963</v>
       </c>
       <c r="G27" t="n">
-        <v>6983122.1</v>
+        <v>38601838.9</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1328,27 +1334,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>58000</v>
+        <v>46000</v>
       </c>
       <c r="F28" t="n">
-        <v>5.9271</v>
+        <v>8.958600000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>343773.9</v>
+        <v>412095.1</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1360,27 +1366,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>50300</v>
+        <v>47650</v>
       </c>
       <c r="F29" t="n">
-        <v>75.29649999999999</v>
+        <v>159.7361</v>
       </c>
       <c r="G29" t="n">
-        <v>3787415.1</v>
+        <v>7611423.9</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1392,12 +1398,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1406,13 +1412,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>199600</v>
+        <v>143600</v>
       </c>
       <c r="F30" t="n">
-        <v>12.1097</v>
+        <v>18.9174</v>
       </c>
       <c r="G30" t="n">
-        <v>2417091.1</v>
+        <v>2716534.1</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1424,27 +1430,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>111400</v>
+        <v>216500</v>
       </c>
       <c r="F31" t="n">
-        <v>16.3438</v>
+        <v>21.1655</v>
       </c>
       <c r="G31" t="n">
-        <v>1820696.1</v>
+        <v>4582327.9</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1456,12 +1462,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1470,13 +1476,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>137200</v>
+        <v>166800</v>
       </c>
       <c r="F32" t="n">
-        <v>25.5948</v>
+        <v>41.8652</v>
       </c>
       <c r="G32" t="n">
-        <v>3511613.1</v>
+        <v>6983122.1</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1488,27 +1494,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>32250</v>
+        <v>58000</v>
       </c>
       <c r="F33" t="n">
-        <v>73.12130000000001</v>
+        <v>5.9271</v>
       </c>
       <c r="G33" t="n">
-        <v>2358161.1</v>
+        <v>343773.9</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1520,27 +1526,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>136900</v>
+        <v>50300</v>
       </c>
       <c r="F34" t="n">
-        <v>281.9711</v>
+        <v>75.29649999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>38601838.9</v>
+        <v>3787415.1</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1552,12 +1558,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1566,13 +1572,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>47450</v>
+        <v>199600</v>
       </c>
       <c r="F35" t="n">
-        <v>11.7985</v>
+        <v>12.1097</v>
       </c>
       <c r="G35" t="n">
-        <v>559838.1</v>
+        <v>2417091.1</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1584,12 +1590,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1598,13 +1604,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>243000</v>
+        <v>111400</v>
       </c>
       <c r="F36" t="n">
-        <v>5.7934</v>
+        <v>16.3438</v>
       </c>
       <c r="G36" t="n">
-        <v>1407799.1</v>
+        <v>1820696.1</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1616,12 +1622,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1630,13 +1636,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>150200</v>
+        <v>137200</v>
       </c>
       <c r="F37" t="n">
-        <v>22.6436</v>
+        <v>25.5948</v>
       </c>
       <c r="G37" t="n">
-        <v>3401064.1</v>
+        <v>3511613.1</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1648,27 +1654,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>53300</v>
+        <v>32250</v>
       </c>
       <c r="F38" t="n">
-        <v>148.0773</v>
+        <v>73.12130000000001</v>
       </c>
       <c r="G38" t="n">
-        <v>7892520.9</v>
+        <v>2358161.1</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1680,27 +1686,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>280500</v>
+        <v>136900</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1361</v>
+        <v>281.9711</v>
       </c>
       <c r="G39" t="n">
-        <v>38166.1</v>
+        <v>38601838.9</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1712,27 +1718,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>327500</v>
+        <v>47450</v>
       </c>
       <c r="F40" t="n">
-        <v>17.7362</v>
+        <v>11.7985</v>
       </c>
       <c r="G40" t="n">
-        <v>5808609.9</v>
+        <v>559838.1</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1744,27 +1750,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>129200</v>
+        <v>243000</v>
       </c>
       <c r="F41" t="n">
-        <v>35.7512</v>
+        <v>5.7934</v>
       </c>
       <c r="G41" t="n">
-        <v>4619059.9</v>
+        <v>1407799.1</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1776,31 +1782,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>136600</v>
+        <v>150200</v>
       </c>
       <c r="F42" t="n">
-        <v>274.9595</v>
+        <v>22.6436</v>
       </c>
       <c r="G42" t="n">
-        <v>37559466.34</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-0.51</v>
-      </c>
+        <v>3401064.1</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1810,27 +1814,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>16590</v>
+        <v>53300</v>
       </c>
       <c r="F43" t="n">
-        <v>513.0315000000001</v>
+        <v>148.0773</v>
       </c>
       <c r="G43" t="n">
-        <v>8511192.1</v>
+        <v>7892520.9</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1842,27 +1846,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>42450</v>
+        <v>280500</v>
       </c>
       <c r="F44" t="n">
-        <v>909.3484</v>
+        <v>0.1361</v>
       </c>
       <c r="G44" t="n">
-        <v>38601838.9</v>
+        <v>38166.1</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1874,142 +1878,142 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>49100</v>
+        <v>327500</v>
       </c>
       <c r="F45" t="n">
-        <v>714.2857</v>
+        <v>17.7362</v>
       </c>
       <c r="G45" t="n">
-        <v>35071428.57</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-12.32</v>
-      </c>
+        <v>5808609.9</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>265500</v>
+        <v>129200</v>
       </c>
       <c r="F46" t="n">
-        <v>123.2792</v>
+        <v>35.7512</v>
       </c>
       <c r="G46" t="n">
-        <v>32730640.59686133</v>
+        <v>4619059.9</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>116300</v>
+        <v>136600</v>
       </c>
       <c r="F47" t="n">
-        <v>332.3224</v>
+        <v>274.9595</v>
       </c>
       <c r="G47" t="n">
-        <v>38649096.95964394</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>37559466.34</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.51</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>152400</v>
+        <v>16590</v>
       </c>
       <c r="F48" t="n">
-        <v>272.9638</v>
+        <v>513.0315000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>41599689.38070278</v>
+        <v>8511192.1</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2018,30 +2022,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>44950</v>
+        <v>42450</v>
       </c>
       <c r="F49" t="n">
-        <v>931.6319999999999</v>
+        <v>909.3484</v>
       </c>
       <c r="G49" t="n">
-        <v>41876856.8952711</v>
+        <v>38601838.9</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>475150</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2050,16 +2054,16 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>48700</v>
+        <v>49100</v>
       </c>
       <c r="F50" t="n">
-        <v>854.2030999999999</v>
+        <v>714.2857</v>
       </c>
       <c r="G50" t="n">
-        <v>41599689.38070278</v>
+        <v>35071428.57</v>
       </c>
       <c r="H50" t="n">
-        <v>6.1</v>
+        <v>-12.32</v>
       </c>
     </row>
     <row r="51">
@@ -2070,31 +2074,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>125000</v>
+        <v>265500</v>
       </c>
       <c r="F51" t="n">
-        <v>335.0149</v>
+        <v>123.2792</v>
       </c>
       <c r="G51" t="n">
-        <v>41876856.8952711</v>
-      </c>
-      <c r="H51" t="n">
-        <v>8.32</v>
-      </c>
+        <v>32730640.59686133</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2104,31 +2106,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>51300</v>
+        <v>116300</v>
       </c>
       <c r="F52" t="n">
-        <v>638.0242</v>
+        <v>332.3224</v>
       </c>
       <c r="G52" t="n">
-        <v>32730640.59686133</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-14.21</v>
-      </c>
+        <v>38649096.95964394</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2138,144 +2138,144 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>145400</v>
+        <v>152400</v>
       </c>
       <c r="F53" t="n">
-        <v>265.8122</v>
+        <v>272.9638</v>
       </c>
       <c r="G53" t="n">
-        <v>38649096.95964394</v>
-      </c>
-      <c r="H53" t="n">
-        <v>2.83</v>
-      </c>
+        <v>41599689.38070278</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>663000</v>
+        <v>44950</v>
       </c>
       <c r="F54" t="n">
-        <v>59.097</v>
+        <v>931.6319999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>41876856.8952711</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>236500</v>
+        <v>48700</v>
       </c>
       <c r="F55" t="n">
-        <v>165.6714</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>41599689.38070278</v>
+      </c>
+      <c r="H55" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>117900</v>
+        <v>125000</v>
       </c>
       <c r="F56" t="n">
-        <v>268.003</v>
+        <v>335.0149</v>
       </c>
       <c r="G56" t="n">
-        <v>31597552.38168333</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>41876856.8952711</v>
+      </c>
+      <c r="H56" t="n">
+        <v>8.32</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2284,64 +2284,66 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>190600</v>
+        <v>51300</v>
       </c>
       <c r="F57" t="n">
-        <v>165.7794</v>
+        <v>638.0242</v>
       </c>
       <c r="G57" t="n">
-        <v>31597552.38168333</v>
+        <v>32730640.59686133</v>
       </c>
       <c r="H57" t="n">
-        <v>-11.96</v>
+        <v>-14.21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>665000</v>
+        <v>145400</v>
       </c>
       <c r="F58" t="n">
-        <v>59.097</v>
+        <v>265.8122</v>
       </c>
       <c r="G58" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>38649096.95964394</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2.83</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2350,32 +2352,32 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>94200</v>
+        <v>663000</v>
       </c>
       <c r="F59" t="n">
-        <v>390.423</v>
+        <v>59.097</v>
       </c>
       <c r="G59" t="n">
-        <v>36777850.25730231</v>
+        <v>39181280.69736513</v>
       </c>
       <c r="H59" t="n">
-        <v>-7.83</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2384,64 +2386,62 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>240000</v>
+        <v>236500</v>
       </c>
       <c r="F60" t="n">
-        <v>153.241</v>
+        <v>165.6714</v>
       </c>
       <c r="G60" t="n">
-        <v>36777850.25730231</v>
+        <v>39181280.69736513</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>78200</v>
+        <v>117900</v>
       </c>
       <c r="F61" t="n">
-        <v>502.5508</v>
+        <v>268.003</v>
       </c>
       <c r="G61" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2450,66 +2450,64 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>10970</v>
+        <v>190600</v>
       </c>
       <c r="F62" t="n">
-        <v>3600.36</v>
+        <v>165.7794</v>
       </c>
       <c r="G62" t="n">
-        <v>39495949.5949595</v>
+        <v>31597552.38168333</v>
       </c>
       <c r="H62" t="n">
-        <v>-1.26</v>
+        <v>-11.96</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>80800</v>
+        <v>665000</v>
       </c>
       <c r="F63" t="n">
-        <v>493.8272</v>
+        <v>59.097</v>
       </c>
       <c r="G63" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-0.25</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2518,32 +2516,32 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>11880</v>
+        <v>94200</v>
       </c>
       <c r="F64" t="n">
-        <v>3021.148</v>
+        <v>390.423</v>
       </c>
       <c r="G64" t="n">
-        <v>35891238.67069487</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H64" t="n">
-        <v>-10.27</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2552,30 +2550,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>102200</v>
+        <v>240000</v>
       </c>
       <c r="F65" t="n">
-        <v>390.423</v>
+        <v>153.241</v>
       </c>
       <c r="G65" t="n">
-        <v>39901234.56790123</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2584,16 +2582,16 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>45150</v>
+        <v>78200</v>
       </c>
       <c r="F66" t="n">
-        <v>832.4662</v>
+        <v>502.5508</v>
       </c>
       <c r="G66" t="n">
-        <v>37585848.07492196</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H66" t="n">
-        <v>-6.04</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2604,29 +2602,31 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>194500</v>
+        <v>10970</v>
       </c>
       <c r="F67" t="n">
-        <v>203.064</v>
+        <v>3600.36</v>
       </c>
       <c r="G67" t="n">
         <v>39495949.5949595</v>
       </c>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>-1.26</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2636,29 +2636,31 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>128800</v>
+        <v>80800</v>
       </c>
       <c r="F68" t="n">
-        <v>306.2796</v>
+        <v>493.8272</v>
       </c>
       <c r="G68" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2668,29 +2670,31 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>45900</v>
+        <v>11880</v>
       </c>
       <c r="F69" t="n">
-        <v>854.2030999999999</v>
+        <v>3021.148</v>
       </c>
       <c r="G69" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>35891238.67069487</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-10.27</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2700,12 +2704,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2714,13 +2718,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>78200</v>
+        <v>102200</v>
       </c>
       <c r="F70" t="n">
-        <v>502.5508</v>
+        <v>390.423</v>
       </c>
       <c r="G70" t="n">
-        <v>39299474.60595447</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2732,29 +2736,31 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>115400</v>
+        <v>45150</v>
       </c>
       <c r="F71" t="n">
-        <v>335.0149</v>
+        <v>832.4662</v>
       </c>
       <c r="G71" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H71" t="n">
+        <v>-6.04</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2764,31 +2770,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>9740</v>
+        <v>194500</v>
       </c>
       <c r="F72" t="n">
-        <v>3875.969</v>
+        <v>203.064</v>
       </c>
       <c r="G72" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-5.62</v>
-      </c>
+        <v>39495949.5949595</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2798,31 +2802,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>21650</v>
+        <v>128800</v>
       </c>
       <c r="F73" t="n">
-        <v>1785.7143</v>
+        <v>306.2796</v>
       </c>
       <c r="G73" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2832,12 +2834,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2846,13 +2848,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>271000</v>
+        <v>45900</v>
       </c>
       <c r="F74" t="n">
-        <v>141.0219</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>38216939.07875186</v>
+        <v>39207920.79207921</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2864,31 +2866,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>64300</v>
+        <v>78200</v>
       </c>
       <c r="F75" t="n">
-        <v>594.3536</v>
+        <v>502.5508</v>
       </c>
       <c r="G75" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-4.46</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2898,31 +2898,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>56100</v>
+        <v>115400</v>
       </c>
       <c r="F76" t="n">
-        <v>700.5254</v>
+        <v>335.0149</v>
       </c>
       <c r="G76" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-1.75</v>
-      </c>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2932,29 +2930,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>137300</v>
+        <v>9740</v>
       </c>
       <c r="F77" t="n">
-        <v>274.9595</v>
+        <v>3875.969</v>
       </c>
       <c r="G77" t="n">
         <v>37751937.98449613</v>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>-5.62</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2964,29 +2964,31 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>59800</v>
+        <v>21650</v>
       </c>
       <c r="F78" t="n">
-        <v>638.0242</v>
+        <v>1785.7143</v>
       </c>
       <c r="G78" t="n">
-        <v>38153846.15384615</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-3.35</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2996,12 +2998,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3010,13 +3012,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>141400</v>
+        <v>271000</v>
       </c>
       <c r="F79" t="n">
-        <v>265.8122</v>
+        <v>141.0219</v>
       </c>
       <c r="G79" t="n">
-        <v>37585848.07492196</v>
+        <v>38216939.07875186</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -3028,12 +3030,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3042,16 +3044,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>10020</v>
+        <v>64300</v>
       </c>
       <c r="F80" t="n">
-        <v>3937.0079</v>
+        <v>594.3536</v>
       </c>
       <c r="G80" t="n">
-        <v>39448818.8976378</v>
+        <v>38216939.07875186</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.38</v>
+        <v>-4.46</v>
       </c>
     </row>
     <row r="81">
@@ -3062,12 +3064,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3076,16 +3078,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>29700</v>
+        <v>56100</v>
       </c>
       <c r="F81" t="n">
-        <v>1320.132</v>
+        <v>700.5254</v>
       </c>
       <c r="G81" t="n">
-        <v>39207920.79207921</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.98</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="82">
@@ -3096,31 +3098,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6820</v>
+        <v>137300</v>
       </c>
       <c r="F82" t="n">
-        <v>5594.4056</v>
+        <v>274.9595</v>
       </c>
       <c r="G82" t="n">
-        <v>38153846.15384615</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-4.62</v>
-      </c>
+        <v>37751937.98449613</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3144,30 +3144,30 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>216500</v>
+        <v>59800</v>
       </c>
       <c r="F83" t="n">
-        <v>165.7794</v>
+        <v>638.0242</v>
       </c>
       <c r="G83" t="n">
-        <v>35891238.67069487</v>
+        <v>38153846.15384615</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3176,126 +3176,132 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>48850</v>
+        <v>141400</v>
       </c>
       <c r="F84" t="n">
-        <v>818.8332</v>
+        <v>265.8122</v>
       </c>
       <c r="G84" t="n">
-        <v>40000000</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>11110</v>
+        <v>10020</v>
       </c>
       <c r="F85" t="n">
-        <v>3600.36</v>
+        <v>3937.0079</v>
       </c>
       <c r="G85" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H85" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>81000</v>
+        <v>29700</v>
       </c>
       <c r="F86" t="n">
-        <v>493.8272</v>
+        <v>1320.132</v>
       </c>
       <c r="G86" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>13240</v>
+        <v>6820</v>
       </c>
       <c r="F87" t="n">
-        <v>3021.148</v>
+        <v>5594.4056</v>
       </c>
       <c r="G87" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3304,13 +3310,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>14530</v>
+        <v>216500</v>
       </c>
       <c r="F88" t="n">
-        <v>2752.925</v>
+        <v>165.7794</v>
       </c>
       <c r="G88" t="n">
-        <v>40000000</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3322,12 +3328,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3336,10 +3342,10 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>46650</v>
+        <v>48850</v>
       </c>
       <c r="F89" t="n">
-        <v>857.4491</v>
+        <v>818.8332</v>
       </c>
       <c r="G89" t="n">
         <v>40000000</v>
@@ -3354,12 +3360,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3368,10 +3374,10 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>62600</v>
+        <v>11110</v>
       </c>
       <c r="F90" t="n">
-        <v>638.9776000000001</v>
+        <v>3600.36</v>
       </c>
       <c r="G90" t="n">
         <v>40000000</v>
@@ -3386,12 +3392,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3400,10 +3406,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>142600</v>
+        <v>81000</v>
       </c>
       <c r="F91" t="n">
-        <v>280.5049</v>
+        <v>493.8272</v>
       </c>
       <c r="G91" t="n">
         <v>40000000</v>
@@ -3418,12 +3424,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3432,10 +3438,10 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>48050</v>
+        <v>13240</v>
       </c>
       <c r="F92" t="n">
-        <v>832.4662</v>
+        <v>3021.148</v>
       </c>
       <c r="G92" t="n">
         <v>40000000</v>
@@ -3450,12 +3456,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3464,10 +3470,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>62000</v>
+        <v>14530</v>
       </c>
       <c r="F93" t="n">
-        <v>645.1613</v>
+        <v>2752.925</v>
       </c>
       <c r="G93" t="n">
         <v>40000000</v>
@@ -3482,12 +3488,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3496,10 +3502,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>113600</v>
+        <v>46650</v>
       </c>
       <c r="F94" t="n">
-        <v>352.1127</v>
+        <v>857.4491</v>
       </c>
       <c r="G94" t="n">
         <v>40000000</v>
@@ -3514,12 +3520,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3528,10 +3534,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>31250</v>
+        <v>62600</v>
       </c>
       <c r="F95" t="n">
-        <v>1280</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G95" t="n">
         <v>40000000</v>
@@ -3546,12 +3552,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3560,10 +3566,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>50100</v>
+        <v>142600</v>
       </c>
       <c r="F96" t="n">
-        <v>798.4032</v>
+        <v>280.5049</v>
       </c>
       <c r="G96" t="n">
         <v>40000000</v>
@@ -3578,12 +3584,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3592,10 +3598,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>10320</v>
+        <v>48050</v>
       </c>
       <c r="F97" t="n">
-        <v>3875.969</v>
+        <v>832.4662</v>
       </c>
       <c r="G97" t="n">
         <v>40000000</v>
@@ -3610,12 +3616,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3624,10 +3630,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>22400</v>
+        <v>62000</v>
       </c>
       <c r="F98" t="n">
-        <v>1785.7143</v>
+        <v>645.1613</v>
       </c>
       <c r="G98" t="n">
         <v>40000000</v>
@@ -3642,12 +3648,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3656,10 +3662,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>137800</v>
+        <v>113600</v>
       </c>
       <c r="F99" t="n">
-        <v>290.2758</v>
+        <v>352.1127</v>
       </c>
       <c r="G99" t="n">
         <v>40000000</v>
@@ -3674,12 +3680,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3688,10 +3694,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>71900</v>
+        <v>31250</v>
       </c>
       <c r="F100" t="n">
-        <v>556.3282</v>
+        <v>1280</v>
       </c>
       <c r="G100" t="n">
         <v>40000000</v>
@@ -3706,12 +3712,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3720,10 +3726,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>413500</v>
+        <v>50100</v>
       </c>
       <c r="F101" t="n">
-        <v>96.73520000000001</v>
+        <v>798.4032</v>
       </c>
       <c r="G101" t="n">
         <v>40000000</v>
@@ -3738,12 +3744,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3752,10 +3758,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>67300</v>
+        <v>10320</v>
       </c>
       <c r="F102" t="n">
-        <v>594.3536</v>
+        <v>3875.969</v>
       </c>
       <c r="G102" t="n">
         <v>40000000</v>
@@ -3770,12 +3776,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3784,10 +3790,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>57100</v>
+        <v>22400</v>
       </c>
       <c r="F103" t="n">
-        <v>700.5254</v>
+        <v>1785.7143</v>
       </c>
       <c r="G103" t="n">
         <v>40000000</v>
@@ -3802,12 +3808,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3816,10 +3822,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>13890</v>
+        <v>137800</v>
       </c>
       <c r="F104" t="n">
-        <v>2879.7696</v>
+        <v>290.2758</v>
       </c>
       <c r="G104" t="n">
         <v>40000000</v>
@@ -3834,12 +3840,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3848,10 +3854,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>10160</v>
+        <v>71900</v>
       </c>
       <c r="F105" t="n">
-        <v>3937.0079</v>
+        <v>556.3282</v>
       </c>
       <c r="G105" t="n">
         <v>40000000</v>
@@ -3866,12 +3872,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3880,10 +3886,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>30300</v>
+        <v>413500</v>
       </c>
       <c r="F106" t="n">
-        <v>1320.132</v>
+        <v>96.73520000000001</v>
       </c>
       <c r="G106" t="n">
         <v>40000000</v>
@@ -3898,12 +3904,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3912,10 +3918,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>7150</v>
+        <v>67300</v>
       </c>
       <c r="F107" t="n">
-        <v>5594.4056</v>
+        <v>594.3536</v>
       </c>
       <c r="G107" t="n">
         <v>40000000</v>
@@ -3930,12 +3936,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3944,15 +3950,175 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>56000</v>
+        <v>57100</v>
       </c>
       <c r="F108" t="n">
-        <v>714.2857</v>
+        <v>700.5254</v>
       </c>
       <c r="G108" t="n">
         <v>40000000</v>
       </c>
       <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2879.7696</v>
+      </c>
+      <c r="G109" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>자이에스앤디</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>317400</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>10160</v>
+      </c>
+      <c r="F110" t="n">
+        <v>3937.0079</v>
+      </c>
+      <c r="G110" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G111" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F112" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G112" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>475150</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>56000</v>
+      </c>
+      <c r="F113" t="n">
+        <v>714.2857</v>
+      </c>
+      <c r="G113" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,83 +473,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>109800</v>
+        <v>43050</v>
       </c>
       <c r="F2" t="n">
-        <v>335.7689</v>
+        <v>720.0199</v>
       </c>
       <c r="G2" t="n">
-        <v>36867425.8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>30996857.1</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>오킨스전자</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>080580</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27700</v>
+        <v>29550</v>
       </c>
       <c r="F3" t="n">
-        <v>1434.2409</v>
+        <v>1048.963</v>
       </c>
       <c r="G3" t="n">
-        <v>39728473</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>30996857.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-19.7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>090430</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -558,51 +558,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>138300</v>
+        <v>39450</v>
       </c>
       <c r="F4" t="n">
-        <v>263.2269</v>
+        <v>848.4905</v>
       </c>
       <c r="G4" t="n">
-        <v>36404275.7</v>
+        <v>33472950.2</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.42</v>
+        <v>-15.43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>56400</v>
+        <v>57700</v>
       </c>
       <c r="F5" t="n">
-        <v>704.4055</v>
+        <v>580.1205</v>
       </c>
       <c r="G5" t="n">
-        <v>39728473</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-17.05</v>
-      </c>
+        <v>33472950.2</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -612,44 +610,46 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SK케미칼</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>285130</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>51000</v>
+        <v>109800</v>
       </c>
       <c r="F6" t="n">
-        <v>722.8907</v>
+        <v>335.7689</v>
       </c>
       <c r="G6" t="n">
         <v>36867425.8</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>-3.35</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DB손해보험</t>
+          <t>오킨스전자</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>005830</t>
+          <t>080580</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -658,30 +658,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>192100</v>
+        <v>27700</v>
       </c>
       <c r="F7" t="n">
-        <v>181.3286</v>
+        <v>1434.2409</v>
       </c>
       <c r="G7" t="n">
-        <v>34833230.8</v>
+        <v>39728473</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -690,32 +690,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53500</v>
+        <v>138300</v>
       </c>
       <c r="F8" t="n">
-        <v>651.0884</v>
+        <v>263.2269</v>
       </c>
       <c r="G8" t="n">
-        <v>34833230.8</v>
+        <v>36404275.7</v>
       </c>
       <c r="H8" t="n">
-        <v>-13.66</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -724,32 +724,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>214000</v>
+        <v>56400</v>
       </c>
       <c r="F9" t="n">
-        <v>190.9543</v>
+        <v>704.4055</v>
       </c>
       <c r="G9" t="n">
-        <v>40864227.3</v>
+        <v>39728473</v>
       </c>
       <c r="H9" t="n">
-        <v>10.03</v>
+        <v>-17.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>SK케미칼</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>285130</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -758,13 +758,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13070</v>
+        <v>51000</v>
       </c>
       <c r="F10" t="n">
-        <v>2664.7317</v>
+        <v>722.8907</v>
       </c>
       <c r="G10" t="n">
-        <v>34828043.1</v>
+        <v>36867425.8</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -776,12 +776,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>DB손해보험</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>192650</t>
+          <t>005830</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -790,13 +790,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8280</v>
+        <v>192100</v>
       </c>
       <c r="F11" t="n">
-        <v>4935.2932</v>
+        <v>181.3286</v>
       </c>
       <c r="G11" t="n">
-        <v>40864227.3</v>
+        <v>34833230.8</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -822,149 +822,149 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>38300</v>
+        <v>53500</v>
       </c>
       <c r="F12" t="n">
-        <v>909.3484</v>
+        <v>651.0884</v>
       </c>
       <c r="G12" t="n">
-        <v>34828043.1</v>
+        <v>34833230.8</v>
       </c>
       <c r="H12" t="n">
-        <v>-9.779999999999999</v>
+        <v>-13.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>50600</v>
+        <v>214000</v>
       </c>
       <c r="F13" t="n">
-        <v>743.4666999999999</v>
+        <v>190.9543</v>
       </c>
       <c r="G13" t="n">
-        <v>37619415.7</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>40864227.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10.03</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>47100</v>
+        <v>13070</v>
       </c>
       <c r="F14" t="n">
-        <v>798.7137</v>
+        <v>2664.7317</v>
       </c>
       <c r="G14" t="n">
-        <v>37619415.7</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-20.99</v>
-      </c>
+        <v>34828043.1</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>225000</v>
+        <v>8280</v>
       </c>
       <c r="F15" t="n">
-        <v>174.4065</v>
+        <v>4935.2932</v>
       </c>
       <c r="G15" t="n">
-        <v>39241469.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-5.12</v>
-      </c>
+        <v>40864227.3</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208500</v>
+        <v>38300</v>
       </c>
       <c r="F16" t="n">
-        <v>178.9817</v>
+        <v>909.3484</v>
       </c>
       <c r="G16" t="n">
-        <v>37317676.7</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>34828043.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-9.779999999999999</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -974,31 +974,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>008930</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>135700</v>
+        <v>50600</v>
       </c>
       <c r="F17" t="n">
-        <v>280.6848</v>
+        <v>743.4666999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>38088927.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>5.36</v>
-      </c>
+        <v>37619415.7</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1008,29 +1006,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>090430</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>144700</v>
+        <v>47100</v>
       </c>
       <c r="F18" t="n">
-        <v>263.2269</v>
+        <v>798.7137</v>
       </c>
       <c r="G18" t="n">
-        <v>38088927.7</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>37619415.7</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-20.99</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1054,16 +1054,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>269500</v>
+        <v>225000</v>
       </c>
       <c r="F19" t="n">
-        <v>159.878</v>
+        <v>174.4065</v>
       </c>
       <c r="G19" t="n">
-        <v>43087111.6</v>
+        <v>39241469.2</v>
       </c>
       <c r="H19" t="n">
-        <v>13.95</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="20">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>25300</v>
+        <v>208500</v>
       </c>
       <c r="F20" t="n">
-        <v>1703.0479</v>
+        <v>178.9817</v>
       </c>
       <c r="G20" t="n">
-        <v>43087111.6</v>
+        <v>37317676.7</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1120,16 +1120,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>326000</v>
+        <v>135700</v>
       </c>
       <c r="F21" t="n">
-        <v>114.4714</v>
+        <v>280.6848</v>
       </c>
       <c r="G21" t="n">
-        <v>37317676.7</v>
+        <v>38088927.7</v>
       </c>
       <c r="H21" t="n">
-        <v>-18.54</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="22">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1154,145 +1154,147 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>59800</v>
+        <v>144700</v>
       </c>
       <c r="F22" t="n">
-        <v>656.2119</v>
+        <v>263.2269</v>
       </c>
       <c r="G22" t="n">
-        <v>39241469.2</v>
+        <v>38088927.7</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>247000</v>
+        <v>269500</v>
       </c>
       <c r="F23" t="n">
-        <v>33.5026</v>
+        <v>159.878</v>
       </c>
       <c r="G23" t="n">
-        <v>8275143.9</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>43087111.6</v>
+      </c>
+      <c r="H23" t="n">
+        <v>13.95</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>48400</v>
+        <v>25300</v>
       </c>
       <c r="F24" t="n">
-        <v>31.4253</v>
+        <v>1703.0479</v>
       </c>
       <c r="G24" t="n">
-        <v>1520986.1</v>
+        <v>43087111.6</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>142700</v>
+        <v>326000</v>
       </c>
       <c r="F25" t="n">
-        <v>64.8394</v>
+        <v>114.4714</v>
       </c>
       <c r="G25" t="n">
-        <v>9252589.1</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>37317676.7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-18.54</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>12770</v>
+        <v>59800</v>
       </c>
       <c r="F26" t="n">
-        <v>2752.925</v>
+        <v>656.2119</v>
       </c>
       <c r="G26" t="n">
-        <v>35154852.03</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-12.11</v>
-      </c>
+        <v>39241469.2</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1302,27 +1304,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>36800</v>
+        <v>247000</v>
       </c>
       <c r="F27" t="n">
-        <v>1048.963</v>
+        <v>33.5026</v>
       </c>
       <c r="G27" t="n">
-        <v>38601838.9</v>
+        <v>8275143.9</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1334,12 +1336,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1348,13 +1350,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>46000</v>
+        <v>48400</v>
       </c>
       <c r="F28" t="n">
-        <v>8.958600000000001</v>
+        <v>31.4253</v>
       </c>
       <c r="G28" t="n">
-        <v>412095.1</v>
+        <v>1520986.1</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1366,27 +1368,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>47650</v>
+        <v>142700</v>
       </c>
       <c r="F29" t="n">
-        <v>159.7361</v>
+        <v>64.8394</v>
       </c>
       <c r="G29" t="n">
-        <v>7611423.9</v>
+        <v>9252589.1</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1398,29 +1400,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>143600</v>
+        <v>12770</v>
       </c>
       <c r="F30" t="n">
-        <v>18.9174</v>
+        <v>2752.925</v>
       </c>
       <c r="G30" t="n">
-        <v>2716534.1</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>35154852.03</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-12.11</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1430,27 +1434,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>216500</v>
+        <v>36800</v>
       </c>
       <c r="F31" t="n">
-        <v>21.1655</v>
+        <v>1048.963</v>
       </c>
       <c r="G31" t="n">
-        <v>4582327.9</v>
+        <v>38601838.9</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1462,12 +1466,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1476,13 +1480,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>166800</v>
+        <v>46000</v>
       </c>
       <c r="F32" t="n">
-        <v>41.8652</v>
+        <v>8.958600000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>6983122.1</v>
+        <v>412095.1</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1494,12 +1498,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1508,13 +1512,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>58000</v>
+        <v>47650</v>
       </c>
       <c r="F33" t="n">
-        <v>5.9271</v>
+        <v>159.7361</v>
       </c>
       <c r="G33" t="n">
-        <v>343773.9</v>
+        <v>7611423.9</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1526,12 +1530,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1540,13 +1544,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>50300</v>
+        <v>143600</v>
       </c>
       <c r="F34" t="n">
-        <v>75.29649999999999</v>
+        <v>18.9174</v>
       </c>
       <c r="G34" t="n">
-        <v>3787415.1</v>
+        <v>2716534.1</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1558,27 +1562,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>199600</v>
+        <v>216500</v>
       </c>
       <c r="F35" t="n">
-        <v>12.1097</v>
+        <v>21.1655</v>
       </c>
       <c r="G35" t="n">
-        <v>2417091.1</v>
+        <v>4582327.9</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1590,12 +1594,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1604,13 +1608,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>111400</v>
+        <v>166800</v>
       </c>
       <c r="F36" t="n">
-        <v>16.3438</v>
+        <v>41.8652</v>
       </c>
       <c r="G36" t="n">
-        <v>1820696.1</v>
+        <v>6983122.1</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1622,27 +1626,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>137200</v>
+        <v>58000</v>
       </c>
       <c r="F37" t="n">
-        <v>25.5948</v>
+        <v>5.9271</v>
       </c>
       <c r="G37" t="n">
-        <v>3511613.1</v>
+        <v>343773.9</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1654,12 +1658,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1668,13 +1672,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>32250</v>
+        <v>50300</v>
       </c>
       <c r="F38" t="n">
-        <v>73.12130000000001</v>
+        <v>75.29649999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>2358161.1</v>
+        <v>3787415.1</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1686,27 +1690,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>136900</v>
+        <v>199600</v>
       </c>
       <c r="F39" t="n">
-        <v>281.9711</v>
+        <v>12.1097</v>
       </c>
       <c r="G39" t="n">
-        <v>38601838.9</v>
+        <v>2417091.1</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1718,12 +1722,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1732,13 +1736,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>47450</v>
+        <v>111400</v>
       </c>
       <c r="F40" t="n">
-        <v>11.7985</v>
+        <v>16.3438</v>
       </c>
       <c r="G40" t="n">
-        <v>559838.1</v>
+        <v>1820696.1</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1750,12 +1754,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1764,13 +1768,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>243000</v>
+        <v>137200</v>
       </c>
       <c r="F41" t="n">
-        <v>5.7934</v>
+        <v>25.5948</v>
       </c>
       <c r="G41" t="n">
-        <v>1407799.1</v>
+        <v>3511613.1</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1782,12 +1786,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1796,13 +1800,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>150200</v>
+        <v>32250</v>
       </c>
       <c r="F42" t="n">
-        <v>22.6436</v>
+        <v>73.12130000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>3401064.1</v>
+        <v>2358161.1</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1814,27 +1818,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>53300</v>
+        <v>136900</v>
       </c>
       <c r="F43" t="n">
-        <v>148.0773</v>
+        <v>281.9711</v>
       </c>
       <c r="G43" t="n">
-        <v>7892520.9</v>
+        <v>38601838.9</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1846,12 +1850,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1860,13 +1864,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>280500</v>
+        <v>47450</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1361</v>
+        <v>11.7985</v>
       </c>
       <c r="G44" t="n">
-        <v>38166.1</v>
+        <v>559838.1</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1878,27 +1882,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>327500</v>
+        <v>243000</v>
       </c>
       <c r="F45" t="n">
-        <v>17.7362</v>
+        <v>5.7934</v>
       </c>
       <c r="G45" t="n">
-        <v>5808609.9</v>
+        <v>1407799.1</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1910,27 +1914,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>129200</v>
+        <v>150200</v>
       </c>
       <c r="F46" t="n">
-        <v>35.7512</v>
+        <v>22.6436</v>
       </c>
       <c r="G46" t="n">
-        <v>4619059.9</v>
+        <v>3401064.1</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1942,31 +1946,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>136600</v>
+        <v>53300</v>
       </c>
       <c r="F47" t="n">
-        <v>274.9595</v>
+        <v>148.0773</v>
       </c>
       <c r="G47" t="n">
-        <v>37559466.34</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-0.51</v>
-      </c>
+        <v>7892520.9</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1976,12 +1978,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1990,13 +1992,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>16590</v>
+        <v>280500</v>
       </c>
       <c r="F48" t="n">
-        <v>513.0315000000001</v>
+        <v>0.1361</v>
       </c>
       <c r="G48" t="n">
-        <v>8511192.1</v>
+        <v>38166.1</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -2008,27 +2010,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>42450</v>
+        <v>327500</v>
       </c>
       <c r="F49" t="n">
-        <v>909.3484</v>
+        <v>17.7362</v>
       </c>
       <c r="G49" t="n">
-        <v>38601838.9</v>
+        <v>5808609.9</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2040,110 +2042,110 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>49100</v>
+        <v>129200</v>
       </c>
       <c r="F50" t="n">
-        <v>714.2857</v>
+        <v>35.7512</v>
       </c>
       <c r="G50" t="n">
-        <v>35071428.57</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-12.32</v>
-      </c>
+        <v>4619059.9</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>265500</v>
+        <v>136600</v>
       </c>
       <c r="F51" t="n">
-        <v>123.2792</v>
+        <v>274.9595</v>
       </c>
       <c r="G51" t="n">
-        <v>32730640.59686133</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>37559466.34</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.51</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>116300</v>
+        <v>16590</v>
       </c>
       <c r="F52" t="n">
-        <v>332.3224</v>
+        <v>513.0315000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>38649096.95964394</v>
+        <v>8511192.1</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2152,47 +2154,49 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>152400</v>
+        <v>42450</v>
       </c>
       <c r="F53" t="n">
-        <v>272.9638</v>
+        <v>909.3484</v>
       </c>
       <c r="G53" t="n">
-        <v>41599689.38070278</v>
+        <v>38601838.9</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>475150</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>44950</v>
+        <v>49100</v>
       </c>
       <c r="F54" t="n">
-        <v>931.6319999999999</v>
+        <v>714.2857</v>
       </c>
       <c r="G54" t="n">
-        <v>41876856.8952711</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>35071428.57</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-12.32</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2202,31 +2206,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>48700</v>
+        <v>265500</v>
       </c>
       <c r="F55" t="n">
-        <v>854.2030999999999</v>
+        <v>123.2792</v>
       </c>
       <c r="G55" t="n">
-        <v>41599689.38070278</v>
-      </c>
-      <c r="H55" t="n">
-        <v>6.1</v>
-      </c>
+        <v>32730640.59686133</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2236,31 +2238,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>125000</v>
+        <v>116300</v>
       </c>
       <c r="F56" t="n">
-        <v>335.0149</v>
+        <v>332.3224</v>
       </c>
       <c r="G56" t="n">
-        <v>41876856.8952711</v>
-      </c>
-      <c r="H56" t="n">
-        <v>8.32</v>
-      </c>
+        <v>38649096.95964394</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2270,31 +2270,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>51300</v>
+        <v>152400</v>
       </c>
       <c r="F57" t="n">
-        <v>638.0242</v>
+        <v>272.9638</v>
       </c>
       <c r="G57" t="n">
-        <v>32730640.59686133</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-14.21</v>
-      </c>
+        <v>41599689.38070278</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2304,46 +2302,44 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>145400</v>
+        <v>44950</v>
       </c>
       <c r="F58" t="n">
-        <v>265.8122</v>
+        <v>931.6319999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>38649096.95964394</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2.83</v>
-      </c>
+        <v>41876856.8952711</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2352,96 +2348,100 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>663000</v>
+        <v>48700</v>
       </c>
       <c r="F59" t="n">
-        <v>59.097</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>39181280.69736513</v>
+        <v>41599689.38070278</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>236500</v>
+        <v>125000</v>
       </c>
       <c r="F60" t="n">
-        <v>165.6714</v>
+        <v>335.0149</v>
       </c>
       <c r="G60" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>41876856.8952711</v>
+      </c>
+      <c r="H60" t="n">
+        <v>8.32</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>117900</v>
+        <v>51300</v>
       </c>
       <c r="F61" t="n">
-        <v>268.003</v>
+        <v>638.0242</v>
       </c>
       <c r="G61" t="n">
-        <v>31597552.38168333</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>32730640.59686133</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-14.21</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2450,22 +2450,22 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>190600</v>
+        <v>145400</v>
       </c>
       <c r="F62" t="n">
-        <v>165.7794</v>
+        <v>265.8122</v>
       </c>
       <c r="G62" t="n">
-        <v>31597552.38168333</v>
+        <v>38649096.95964394</v>
       </c>
       <c r="H62" t="n">
-        <v>-11.96</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2480,68 +2480,68 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>665000</v>
+        <v>663000</v>
       </c>
       <c r="F63" t="n">
         <v>59.097</v>
       </c>
       <c r="G63" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0.3</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>94200</v>
+        <v>236500</v>
       </c>
       <c r="F64" t="n">
-        <v>390.423</v>
+        <v>165.6714</v>
       </c>
       <c r="G64" t="n">
-        <v>36777850.25730231</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-7.83</v>
-      </c>
+        <v>39181280.69736513</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2550,30 +2550,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>240000</v>
+        <v>117900</v>
       </c>
       <c r="F65" t="n">
-        <v>153.241</v>
+        <v>268.003</v>
       </c>
       <c r="G65" t="n">
-        <v>36777850.25730231</v>
+        <v>31597552.38168333</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2582,66 +2582,64 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>78200</v>
+        <v>190600</v>
       </c>
       <c r="F66" t="n">
-        <v>502.5508</v>
+        <v>165.7794</v>
       </c>
       <c r="G66" t="n">
-        <v>39299474.60595447</v>
+        <v>31597552.38168333</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>-11.96</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>10970</v>
+        <v>665000</v>
       </c>
       <c r="F67" t="n">
-        <v>3600.36</v>
+        <v>59.097</v>
       </c>
       <c r="G67" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-1.26</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2650,83 +2648,83 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>80800</v>
+        <v>94200</v>
       </c>
       <c r="F68" t="n">
-        <v>493.8272</v>
+        <v>390.423</v>
       </c>
       <c r="G68" t="n">
-        <v>39901234.56790123</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.25</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>11880</v>
+        <v>240000</v>
       </c>
       <c r="F69" t="n">
-        <v>3021.148</v>
+        <v>153.241</v>
       </c>
       <c r="G69" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-10.27</v>
-      </c>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102200</v>
+        <v>78200</v>
       </c>
       <c r="F70" t="n">
-        <v>390.423</v>
+        <v>502.5508</v>
       </c>
       <c r="G70" t="n">
-        <v>39901234.56790123</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2736,12 +2734,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2750,16 +2748,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>45150</v>
+        <v>10970</v>
       </c>
       <c r="F71" t="n">
-        <v>832.4662</v>
+        <v>3600.36</v>
       </c>
       <c r="G71" t="n">
-        <v>37585848.07492196</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H71" t="n">
-        <v>-6.04</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="72">
@@ -2770,29 +2768,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>194500</v>
+        <v>80800</v>
       </c>
       <c r="F72" t="n">
-        <v>203.064</v>
+        <v>493.8272</v>
       </c>
       <c r="G72" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-0.25</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2802,29 +2802,31 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>128800</v>
+        <v>11880</v>
       </c>
       <c r="F73" t="n">
-        <v>306.2796</v>
+        <v>3021.148</v>
       </c>
       <c r="G73" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>35891238.67069487</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-10.27</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2834,12 +2836,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2848,13 +2850,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>45900</v>
+        <v>102200</v>
       </c>
       <c r="F74" t="n">
-        <v>854.2030999999999</v>
+        <v>390.423</v>
       </c>
       <c r="G74" t="n">
-        <v>39207920.79207921</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2866,29 +2868,31 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>78200</v>
+        <v>45150</v>
       </c>
       <c r="F75" t="n">
-        <v>502.5508</v>
+        <v>832.4662</v>
       </c>
       <c r="G75" t="n">
-        <v>39299474.60595447</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>37585848.07492196</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-6.04</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2898,12 +2902,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2912,13 +2916,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>115400</v>
+        <v>194500</v>
       </c>
       <c r="F76" t="n">
-        <v>335.0149</v>
+        <v>203.064</v>
       </c>
       <c r="G76" t="n">
-        <v>38660714.28571428</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2930,31 +2934,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>9740</v>
+        <v>128800</v>
       </c>
       <c r="F77" t="n">
-        <v>3875.969</v>
+        <v>306.2796</v>
       </c>
       <c r="G77" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-5.62</v>
-      </c>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2964,31 +2966,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>21650</v>
+        <v>45900</v>
       </c>
       <c r="F78" t="n">
-        <v>1785.7143</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-3.35</v>
-      </c>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3012,13 +3012,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>271000</v>
+        <v>78200</v>
       </c>
       <c r="F79" t="n">
-        <v>141.0219</v>
+        <v>502.5508</v>
       </c>
       <c r="G79" t="n">
-        <v>38216939.07875186</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -3030,31 +3030,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>64300</v>
+        <v>115400</v>
       </c>
       <c r="F80" t="n">
-        <v>594.3536</v>
+        <v>335.0149</v>
       </c>
       <c r="G80" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-4.46</v>
-      </c>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3064,12 +3062,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3078,16 +3076,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>56100</v>
+        <v>9740</v>
       </c>
       <c r="F81" t="n">
-        <v>700.5254</v>
+        <v>3875.969</v>
       </c>
       <c r="G81" t="n">
-        <v>39299474.60595447</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.75</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="82">
@@ -3098,29 +3096,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>137300</v>
+        <v>21650</v>
       </c>
       <c r="F82" t="n">
-        <v>274.9595</v>
+        <v>1785.7143</v>
       </c>
       <c r="G82" t="n">
-        <v>37751937.98449613</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-3.35</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>59800</v>
+        <v>271000</v>
       </c>
       <c r="F83" t="n">
-        <v>638.0242</v>
+        <v>141.0219</v>
       </c>
       <c r="G83" t="n">
-        <v>38153846.15384615</v>
+        <v>38216939.07875186</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3162,29 +3162,31 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>141400</v>
+        <v>64300</v>
       </c>
       <c r="F84" t="n">
-        <v>265.8122</v>
+        <v>594.3536</v>
       </c>
       <c r="G84" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3194,12 +3196,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3208,16 +3210,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>10020</v>
+        <v>56100</v>
       </c>
       <c r="F85" t="n">
-        <v>3937.0079</v>
+        <v>700.5254</v>
       </c>
       <c r="G85" t="n">
-        <v>39448818.8976378</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.38</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="86">
@@ -3228,31 +3230,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>29700</v>
+        <v>137300</v>
       </c>
       <c r="F86" t="n">
-        <v>1320.132</v>
+        <v>274.9595</v>
       </c>
       <c r="G86" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-1.98</v>
-      </c>
+        <v>37751937.98449613</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3262,31 +3262,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6820</v>
+        <v>59800</v>
       </c>
       <c r="F87" t="n">
-        <v>5594.4056</v>
+        <v>638.0242</v>
       </c>
       <c r="G87" t="n">
         <v>38153846.15384615</v>
       </c>
-      <c r="H87" t="n">
-        <v>-4.62</v>
-      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3296,12 +3294,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3310,126 +3308,132 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>216500</v>
+        <v>141400</v>
       </c>
       <c r="F88" t="n">
-        <v>165.7794</v>
+        <v>265.8122</v>
       </c>
       <c r="G88" t="n">
-        <v>35891238.67069487</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>48850</v>
+        <v>10020</v>
       </c>
       <c r="F89" t="n">
-        <v>818.8332</v>
+        <v>3937.0079</v>
       </c>
       <c r="G89" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>11110</v>
+        <v>29700</v>
       </c>
       <c r="F90" t="n">
-        <v>3600.36</v>
+        <v>1320.132</v>
       </c>
       <c r="G90" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H90" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>81000</v>
+        <v>6820</v>
       </c>
       <c r="F91" t="n">
-        <v>493.8272</v>
+        <v>5594.4056</v>
       </c>
       <c r="G91" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H91" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3438,13 +3442,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>13240</v>
+        <v>216500</v>
       </c>
       <c r="F92" t="n">
-        <v>3021.148</v>
+        <v>165.7794</v>
       </c>
       <c r="G92" t="n">
-        <v>40000000</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3456,12 +3460,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3470,10 +3474,10 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>14530</v>
+        <v>48850</v>
       </c>
       <c r="F93" t="n">
-        <v>2752.925</v>
+        <v>818.8332</v>
       </c>
       <c r="G93" t="n">
         <v>40000000</v>
@@ -3488,12 +3492,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3502,10 +3506,10 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>46650</v>
+        <v>11110</v>
       </c>
       <c r="F94" t="n">
-        <v>857.4491</v>
+        <v>3600.36</v>
       </c>
       <c r="G94" t="n">
         <v>40000000</v>
@@ -3520,12 +3524,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3534,10 +3538,10 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>62600</v>
+        <v>81000</v>
       </c>
       <c r="F95" t="n">
-        <v>638.9776000000001</v>
+        <v>493.8272</v>
       </c>
       <c r="G95" t="n">
         <v>40000000</v>
@@ -3552,12 +3556,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3566,10 +3570,10 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>142600</v>
+        <v>13240</v>
       </c>
       <c r="F96" t="n">
-        <v>280.5049</v>
+        <v>3021.148</v>
       </c>
       <c r="G96" t="n">
         <v>40000000</v>
@@ -3584,12 +3588,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3598,10 +3602,10 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>48050</v>
+        <v>14530</v>
       </c>
       <c r="F97" t="n">
-        <v>832.4662</v>
+        <v>2752.925</v>
       </c>
       <c r="G97" t="n">
         <v>40000000</v>
@@ -3616,12 +3620,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3630,10 +3634,10 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>62000</v>
+        <v>46650</v>
       </c>
       <c r="F98" t="n">
-        <v>645.1613</v>
+        <v>857.4491</v>
       </c>
       <c r="G98" t="n">
         <v>40000000</v>
@@ -3648,12 +3652,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3662,10 +3666,10 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>113600</v>
+        <v>62600</v>
       </c>
       <c r="F99" t="n">
-        <v>352.1127</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G99" t="n">
         <v>40000000</v>
@@ -3680,12 +3684,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3694,10 +3698,10 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>31250</v>
+        <v>142600</v>
       </c>
       <c r="F100" t="n">
-        <v>1280</v>
+        <v>280.5049</v>
       </c>
       <c r="G100" t="n">
         <v>40000000</v>
@@ -3712,12 +3716,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3726,10 +3730,10 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>50100</v>
+        <v>48050</v>
       </c>
       <c r="F101" t="n">
-        <v>798.4032</v>
+        <v>832.4662</v>
       </c>
       <c r="G101" t="n">
         <v>40000000</v>
@@ -3744,12 +3748,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3758,10 +3762,10 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>10320</v>
+        <v>62000</v>
       </c>
       <c r="F102" t="n">
-        <v>3875.969</v>
+        <v>645.1613</v>
       </c>
       <c r="G102" t="n">
         <v>40000000</v>
@@ -3776,12 +3780,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3790,10 +3794,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>22400</v>
+        <v>113600</v>
       </c>
       <c r="F103" t="n">
-        <v>1785.7143</v>
+        <v>352.1127</v>
       </c>
       <c r="G103" t="n">
         <v>40000000</v>
@@ -3808,12 +3812,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3822,10 +3826,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>137800</v>
+        <v>31250</v>
       </c>
       <c r="F104" t="n">
-        <v>290.2758</v>
+        <v>1280</v>
       </c>
       <c r="G104" t="n">
         <v>40000000</v>
@@ -3840,12 +3844,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3854,10 +3858,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>71900</v>
+        <v>50100</v>
       </c>
       <c r="F105" t="n">
-        <v>556.3282</v>
+        <v>798.4032</v>
       </c>
       <c r="G105" t="n">
         <v>40000000</v>
@@ -3872,12 +3876,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3886,10 +3890,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>413500</v>
+        <v>10320</v>
       </c>
       <c r="F106" t="n">
-        <v>96.73520000000001</v>
+        <v>3875.969</v>
       </c>
       <c r="G106" t="n">
         <v>40000000</v>
@@ -3904,12 +3908,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3918,10 +3922,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>67300</v>
+        <v>22400</v>
       </c>
       <c r="F107" t="n">
-        <v>594.3536</v>
+        <v>1785.7143</v>
       </c>
       <c r="G107" t="n">
         <v>40000000</v>
@@ -3936,12 +3940,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3950,10 +3954,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>57100</v>
+        <v>137800</v>
       </c>
       <c r="F108" t="n">
-        <v>700.5254</v>
+        <v>290.2758</v>
       </c>
       <c r="G108" t="n">
         <v>40000000</v>
@@ -3968,12 +3972,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3982,10 +3986,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>13890</v>
+        <v>71900</v>
       </c>
       <c r="F109" t="n">
-        <v>2879.7696</v>
+        <v>556.3282</v>
       </c>
       <c r="G109" t="n">
         <v>40000000</v>
@@ -4000,12 +4004,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4014,10 +4018,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>10160</v>
+        <v>413500</v>
       </c>
       <c r="F110" t="n">
-        <v>3937.0079</v>
+        <v>96.73520000000001</v>
       </c>
       <c r="G110" t="n">
         <v>40000000</v>
@@ -4032,12 +4036,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4046,10 +4050,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>30300</v>
+        <v>67300</v>
       </c>
       <c r="F111" t="n">
-        <v>1320.132</v>
+        <v>594.3536</v>
       </c>
       <c r="G111" t="n">
         <v>40000000</v>
@@ -4064,12 +4068,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4078,10 +4082,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>7150</v>
+        <v>57100</v>
       </c>
       <c r="F112" t="n">
-        <v>5594.4056</v>
+        <v>700.5254</v>
       </c>
       <c r="G112" t="n">
         <v>40000000</v>
@@ -4096,12 +4100,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4110,15 +4114,143 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>56000</v>
+        <v>13890</v>
       </c>
       <c r="F113" t="n">
-        <v>714.2857</v>
+        <v>2879.7696</v>
       </c>
       <c r="G113" t="n">
         <v>40000000</v>
       </c>
       <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>자이에스앤디</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>317400</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>10160</v>
+      </c>
+      <c r="F114" t="n">
+        <v>3937.0079</v>
+      </c>
+      <c r="G114" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G115" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F116" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G116" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>475150</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>56000</v>
+      </c>
+      <c r="F117" t="n">
+        <v>714.2857</v>
+      </c>
+      <c r="G117" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/momentum_mp_history.xlsx
+++ b/docs/downloads/momentum_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,117 +473,115 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>003160</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>43050</v>
+        <v>42650</v>
       </c>
       <c r="F2" t="n">
-        <v>720.0199</v>
+        <v>787.4078</v>
       </c>
       <c r="G2" t="n">
-        <v>30996857.1</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>33582944</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-12.69</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>미코</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>059090</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29550</v>
+        <v>22500</v>
       </c>
       <c r="F3" t="n">
-        <v>1048.963</v>
+        <v>1489.3049</v>
       </c>
       <c r="G3" t="n">
-        <v>30996857.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-19.7</v>
-      </c>
+        <v>33509360.6</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>39450</v>
+        <v>32400</v>
       </c>
       <c r="F4" t="n">
-        <v>848.4905</v>
+        <v>1070.8368</v>
       </c>
       <c r="G4" t="n">
-        <v>33472950.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-15.43</v>
-      </c>
+        <v>34695110.9</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>엑시콘</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>092870</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -592,30 +590,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57700</v>
+        <v>23550</v>
       </c>
       <c r="F5" t="n">
-        <v>580.1205</v>
+        <v>1255.4662</v>
       </c>
       <c r="G5" t="n">
-        <v>33472950.2</v>
+        <v>29566229.7</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,32 +622,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>109800</v>
+        <v>42600</v>
       </c>
       <c r="F6" t="n">
-        <v>335.7689</v>
+        <v>786.6047</v>
       </c>
       <c r="G6" t="n">
-        <v>36867425.8</v>
+        <v>33509360.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-3.35</v>
+        <v>-14.97</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오킨스전자</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>080580</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -658,30 +656,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>27700</v>
+        <v>130700</v>
       </c>
       <c r="F7" t="n">
-        <v>1434.2409</v>
+        <v>256.9468</v>
       </c>
       <c r="G7" t="n">
-        <v>39728473</v>
+        <v>33582944</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>090430</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -690,32 +688,32 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>138300</v>
+        <v>124500</v>
       </c>
       <c r="F8" t="n">
-        <v>263.2269</v>
+        <v>267.6322</v>
       </c>
       <c r="G8" t="n">
-        <v>36404275.7</v>
+        <v>33320208</v>
       </c>
       <c r="H8" t="n">
-        <v>-4.42</v>
+        <v>-9.65</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -724,22 +722,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>56400</v>
+        <v>7030</v>
       </c>
       <c r="F9" t="n">
-        <v>704.4055</v>
+        <v>4935.2932</v>
       </c>
       <c r="G9" t="n">
-        <v>39728473</v>
+        <v>34695110.9</v>
       </c>
       <c r="H9" t="n">
-        <v>-17.05</v>
+        <v>-15.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -754,34 +752,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>51000</v>
+        <v>40900</v>
       </c>
       <c r="F10" t="n">
         <v>722.8907</v>
       </c>
       <c r="G10" t="n">
-        <v>36867425.8</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>29566229.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-19.8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DB손해보험</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005830</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -790,64 +790,62 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>192100</v>
+        <v>41900</v>
       </c>
       <c r="F11" t="n">
-        <v>181.3286</v>
+        <v>795.2317</v>
       </c>
       <c r="G11" t="n">
-        <v>34833230.8</v>
+        <v>33320208</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>003160</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53500</v>
+        <v>43050</v>
       </c>
       <c r="F12" t="n">
-        <v>651.0884</v>
+        <v>720.0199</v>
       </c>
       <c r="G12" t="n">
-        <v>34833230.8</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-13.66</v>
-      </c>
+        <v>30996857.1</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -856,64 +854,66 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>214000</v>
+        <v>29550</v>
       </c>
       <c r="F13" t="n">
-        <v>190.9543</v>
+        <v>1048.963</v>
       </c>
       <c r="G13" t="n">
-        <v>40864227.3</v>
+        <v>30996857.1</v>
       </c>
       <c r="H13" t="n">
-        <v>10.03</v>
+        <v>-19.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13070</v>
+        <v>39450</v>
       </c>
       <c r="F14" t="n">
-        <v>2664.7317</v>
+        <v>848.4905</v>
       </c>
       <c r="G14" t="n">
-        <v>34828043.1</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>33472950.2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-15.43</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>엑시콘</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>192650</t>
+          <t>092870</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -922,30 +922,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8280</v>
+        <v>57700</v>
       </c>
       <c r="F15" t="n">
-        <v>4935.2932</v>
+        <v>580.1205</v>
       </c>
       <c r="G15" t="n">
-        <v>40864227.3</v>
+        <v>33472950.2</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -954,32 +954,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>38300</v>
+        <v>109800</v>
       </c>
       <c r="F16" t="n">
-        <v>909.3484</v>
+        <v>335.7689</v>
       </c>
       <c r="G16" t="n">
-        <v>34828043.1</v>
+        <v>36867425.8</v>
       </c>
       <c r="H16" t="n">
-        <v>-9.779999999999999</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한미사이언스</t>
+          <t>오킨스전자</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>008930</t>
+          <t>080580</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -988,30 +988,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>50600</v>
+        <v>27700</v>
       </c>
       <c r="F17" t="n">
-        <v>743.4666999999999</v>
+        <v>1434.2409</v>
       </c>
       <c r="G17" t="n">
-        <v>37619415.7</v>
+        <v>39728473</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1020,32 +1020,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>47100</v>
+        <v>138300</v>
       </c>
       <c r="F18" t="n">
-        <v>798.7137</v>
+        <v>263.2269</v>
       </c>
       <c r="G18" t="n">
-        <v>37619415.7</v>
+        <v>36404275.7</v>
       </c>
       <c r="H18" t="n">
-        <v>-20.99</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1054,32 +1054,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>225000</v>
+        <v>56400</v>
       </c>
       <c r="F19" t="n">
-        <v>174.4065</v>
+        <v>704.4055</v>
       </c>
       <c r="G19" t="n">
-        <v>39241469.2</v>
+        <v>39728473</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.12</v>
+        <v>-17.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>주성엔지니어링</t>
+          <t>SK케미칼</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>036930</t>
+          <t>285130</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1088,96 +1088,96 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208500</v>
+        <v>51000</v>
       </c>
       <c r="F20" t="n">
-        <v>178.9817</v>
+        <v>722.8907</v>
       </c>
       <c r="G20" t="n">
-        <v>37317676.7</v>
+        <v>36867425.8</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>DB손해보험</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>005830</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>135700</v>
+        <v>192100</v>
       </c>
       <c r="F21" t="n">
-        <v>280.6848</v>
+        <v>181.3286</v>
       </c>
       <c r="G21" t="n">
-        <v>38088927.7</v>
-      </c>
-      <c r="H21" t="n">
-        <v>5.36</v>
-      </c>
+        <v>34833230.8</v>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>090430</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>144700</v>
+        <v>53500</v>
       </c>
       <c r="F22" t="n">
-        <v>263.2269</v>
+        <v>651.0884</v>
       </c>
       <c r="G22" t="n">
-        <v>38088927.7</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>34833230.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-13.66</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1186,32 +1186,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>269500</v>
+        <v>214000</v>
       </c>
       <c r="F23" t="n">
-        <v>159.878</v>
+        <v>190.9543</v>
       </c>
       <c r="G23" t="n">
-        <v>43087111.6</v>
+        <v>40864227.3</v>
       </c>
       <c r="H23" t="n">
-        <v>13.95</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>제이앤티씨</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>204270</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1220,401 +1220,409 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>25300</v>
+        <v>13070</v>
       </c>
       <c r="F24" t="n">
-        <v>1703.0479</v>
+        <v>2664.7317</v>
       </c>
       <c r="G24" t="n">
-        <v>43087111.6</v>
+        <v>34828043.1</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192650</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>326000</v>
+        <v>8280</v>
       </c>
       <c r="F25" t="n">
-        <v>114.4714</v>
+        <v>4935.2932</v>
       </c>
       <c r="G25" t="n">
-        <v>37317676.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-18.54</v>
-      </c>
+        <v>40864227.3</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>59800</v>
+        <v>38300</v>
       </c>
       <c r="F26" t="n">
-        <v>656.2119</v>
+        <v>909.3484</v>
       </c>
       <c r="G26" t="n">
-        <v>39241469.2</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>34828043.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-9.779999999999999</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>한미사이언스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>008930</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>247000</v>
+        <v>50600</v>
       </c>
       <c r="F27" t="n">
-        <v>33.5026</v>
+        <v>743.4666999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>8275143.9</v>
+        <v>37619415.7</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>48400</v>
+        <v>47100</v>
       </c>
       <c r="F28" t="n">
-        <v>31.4253</v>
+        <v>798.7137</v>
       </c>
       <c r="G28" t="n">
-        <v>1520986.1</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>37619415.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-20.99</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>142700</v>
+        <v>225000</v>
       </c>
       <c r="F29" t="n">
-        <v>64.8394</v>
+        <v>174.4065</v>
       </c>
       <c r="G29" t="n">
-        <v>9252589.1</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>39241469.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-5.12</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>주성엔지니어링</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>036930</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>12770</v>
+        <v>208500</v>
       </c>
       <c r="F30" t="n">
-        <v>2752.925</v>
+        <v>178.9817</v>
       </c>
       <c r="G30" t="n">
-        <v>35154852.03</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-12.11</v>
-      </c>
+        <v>37317676.7</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>36800</v>
+        <v>135700</v>
       </c>
       <c r="F31" t="n">
-        <v>1048.963</v>
+        <v>280.6848</v>
       </c>
       <c r="G31" t="n">
-        <v>38601838.9</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>38088927.7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5.36</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>아모레퍼시픽</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>090430</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>46000</v>
+        <v>144700</v>
       </c>
       <c r="F32" t="n">
-        <v>8.958600000000001</v>
+        <v>263.2269</v>
       </c>
       <c r="G32" t="n">
-        <v>412095.1</v>
+        <v>38088927.7</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>47650</v>
+        <v>269500</v>
       </c>
       <c r="F33" t="n">
-        <v>159.7361</v>
+        <v>159.878</v>
       </c>
       <c r="G33" t="n">
-        <v>7611423.9</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>43087111.6</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13.95</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>제이앤티씨</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>204270</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>143600</v>
+        <v>25300</v>
       </c>
       <c r="F34" t="n">
-        <v>18.9174</v>
+        <v>1703.0479</v>
       </c>
       <c r="G34" t="n">
-        <v>2716534.1</v>
+        <v>43087111.6</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>216500</v>
+        <v>326000</v>
       </c>
       <c r="F35" t="n">
-        <v>21.1655</v>
+        <v>114.4714</v>
       </c>
       <c r="G35" t="n">
-        <v>4582327.9</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>37317676.7</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-18.54</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>166800</v>
+        <v>59800</v>
       </c>
       <c r="F36" t="n">
-        <v>41.8652</v>
+        <v>656.2119</v>
       </c>
       <c r="G36" t="n">
-        <v>6983122.1</v>
+        <v>39241469.2</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1626,12 +1634,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1640,13 +1648,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>58000</v>
+        <v>247000</v>
       </c>
       <c r="F37" t="n">
-        <v>5.9271</v>
+        <v>33.5026</v>
       </c>
       <c r="G37" t="n">
-        <v>343773.9</v>
+        <v>8275143.9</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1658,12 +1666,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1672,13 +1680,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>50300</v>
+        <v>48400</v>
       </c>
       <c r="F38" t="n">
-        <v>75.29649999999999</v>
+        <v>31.4253</v>
       </c>
       <c r="G38" t="n">
-        <v>3787415.1</v>
+        <v>1520986.1</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1690,12 +1698,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1704,13 +1712,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>199600</v>
+        <v>142700</v>
       </c>
       <c r="F39" t="n">
-        <v>12.1097</v>
+        <v>64.8394</v>
       </c>
       <c r="G39" t="n">
-        <v>2417091.1</v>
+        <v>9252589.1</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1722,29 +1730,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>111400</v>
+        <v>12770</v>
       </c>
       <c r="F40" t="n">
-        <v>16.3438</v>
+        <v>2752.925</v>
       </c>
       <c r="G40" t="n">
-        <v>1820696.1</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>35154852.03</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-12.11</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1754,27 +1764,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>137200</v>
+        <v>36800</v>
       </c>
       <c r="F41" t="n">
-        <v>25.5948</v>
+        <v>1048.963</v>
       </c>
       <c r="G41" t="n">
-        <v>3511613.1</v>
+        <v>38601838.9</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1786,12 +1796,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1800,13 +1810,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>32250</v>
+        <v>46000</v>
       </c>
       <c r="F42" t="n">
-        <v>73.12130000000001</v>
+        <v>8.958600000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>2358161.1</v>
+        <v>412095.1</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1818,27 +1828,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>136900</v>
+        <v>47650</v>
       </c>
       <c r="F43" t="n">
-        <v>281.9711</v>
+        <v>159.7361</v>
       </c>
       <c r="G43" t="n">
-        <v>38601838.9</v>
+        <v>7611423.9</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1850,12 +1860,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1864,13 +1874,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>47450</v>
+        <v>143600</v>
       </c>
       <c r="F44" t="n">
-        <v>11.7985</v>
+        <v>18.9174</v>
       </c>
       <c r="G44" t="n">
-        <v>559838.1</v>
+        <v>2716534.1</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1882,27 +1892,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>243000</v>
+        <v>216500</v>
       </c>
       <c r="F45" t="n">
-        <v>5.7934</v>
+        <v>21.1655</v>
       </c>
       <c r="G45" t="n">
-        <v>1407799.1</v>
+        <v>4582327.9</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1914,12 +1924,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1928,13 +1938,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>150200</v>
+        <v>166800</v>
       </c>
       <c r="F46" t="n">
-        <v>22.6436</v>
+        <v>41.8652</v>
       </c>
       <c r="G46" t="n">
-        <v>3401064.1</v>
+        <v>6983122.1</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1946,12 +1956,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1960,13 +1970,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53300</v>
+        <v>58000</v>
       </c>
       <c r="F47" t="n">
-        <v>148.0773</v>
+        <v>5.9271</v>
       </c>
       <c r="G47" t="n">
-        <v>7892520.9</v>
+        <v>343773.9</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1978,12 +1988,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1992,13 +2002,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>280500</v>
+        <v>50300</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1361</v>
+        <v>75.29649999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>38166.1</v>
+        <v>3787415.1</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -2010,27 +2020,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>327500</v>
+        <v>199600</v>
       </c>
       <c r="F49" t="n">
-        <v>17.7362</v>
+        <v>12.1097</v>
       </c>
       <c r="G49" t="n">
-        <v>5808609.9</v>
+        <v>2417091.1</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2042,27 +2052,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>129200</v>
+        <v>111400</v>
       </c>
       <c r="F50" t="n">
-        <v>35.7512</v>
+        <v>16.3438</v>
       </c>
       <c r="G50" t="n">
-        <v>4619059.9</v>
+        <v>1820696.1</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2074,31 +2084,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>136600</v>
+        <v>137200</v>
       </c>
       <c r="F51" t="n">
-        <v>274.9595</v>
+        <v>25.5948</v>
       </c>
       <c r="G51" t="n">
-        <v>37559466.34</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-0.51</v>
-      </c>
+        <v>3511613.1</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2108,12 +2116,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2122,13 +2130,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>16590</v>
+        <v>32250</v>
       </c>
       <c r="F52" t="n">
-        <v>513.0315000000001</v>
+        <v>73.12130000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>8511192.1</v>
+        <v>2358161.1</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2140,12 +2148,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2154,10 +2162,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>42450</v>
+        <v>136900</v>
       </c>
       <c r="F53" t="n">
-        <v>909.3484</v>
+        <v>281.9711</v>
       </c>
       <c r="G53" t="n">
         <v>38601838.9</v>
@@ -2172,242 +2180,236 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>49100</v>
+        <v>47450</v>
       </c>
       <c r="F54" t="n">
-        <v>714.2857</v>
+        <v>11.7985</v>
       </c>
       <c r="G54" t="n">
-        <v>35071428.57</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-12.32</v>
-      </c>
+        <v>559838.1</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>265500</v>
+        <v>243000</v>
       </c>
       <c r="F55" t="n">
-        <v>123.2792</v>
+        <v>5.7934</v>
       </c>
       <c r="G55" t="n">
-        <v>32730640.59686133</v>
+        <v>1407799.1</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>삼화콘덴서</t>
+          <t>한국콜마</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>001820</t>
+          <t>161890</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>116300</v>
+        <v>150200</v>
       </c>
       <c r="F56" t="n">
-        <v>332.3224</v>
+        <v>22.6436</v>
       </c>
       <c r="G56" t="n">
-        <v>38649096.95964394</v>
+        <v>3401064.1</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>NHN</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>031980</t>
+          <t>181710</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>152400</v>
+        <v>53300</v>
       </c>
       <c r="F57" t="n">
-        <v>272.9638</v>
+        <v>148.0773</v>
       </c>
       <c r="G57" t="n">
-        <v>41599689.38070278</v>
+        <v>7892520.9</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>064290</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>44950</v>
+        <v>280500</v>
       </c>
       <c r="F58" t="n">
-        <v>931.6319999999999</v>
+        <v>0.1361</v>
       </c>
       <c r="G58" t="n">
-        <v>41876856.8952711</v>
+        <v>38166.1</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>48700</v>
+        <v>327500</v>
       </c>
       <c r="F59" t="n">
-        <v>854.2030999999999</v>
+        <v>17.7362</v>
       </c>
       <c r="G59" t="n">
-        <v>41599689.38070278</v>
-      </c>
-      <c r="H59" t="n">
-        <v>6.1</v>
-      </c>
+        <v>5808609.9</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>125000</v>
+        <v>129200</v>
       </c>
       <c r="F60" t="n">
-        <v>335.0149</v>
+        <v>35.7512</v>
       </c>
       <c r="G60" t="n">
-        <v>41876856.8952711</v>
-      </c>
-      <c r="H60" t="n">
-        <v>8.32</v>
-      </c>
+        <v>4619059.9</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2416,132 +2418,130 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>51300</v>
+        <v>136600</v>
       </c>
       <c r="F61" t="n">
-        <v>638.0242</v>
+        <v>274.9595</v>
       </c>
       <c r="G61" t="n">
-        <v>32730640.59686133</v>
+        <v>37559466.34</v>
       </c>
       <c r="H61" t="n">
-        <v>-14.21</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>252990</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>145400</v>
+        <v>16590</v>
       </c>
       <c r="F62" t="n">
-        <v>265.8122</v>
+        <v>513.0315000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>38649096.95964394</v>
-      </c>
-      <c r="H62" t="n">
-        <v>2.83</v>
-      </c>
+        <v>8511192.1</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>663000</v>
+        <v>42450</v>
       </c>
       <c r="F63" t="n">
-        <v>59.097</v>
+        <v>909.3484</v>
       </c>
       <c r="G63" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-0.3</v>
-      </c>
+        <v>38601838.9</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>SK이터닉스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>131290</t>
+          <t>475150</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>236500</v>
+        <v>49100</v>
       </c>
       <c r="F64" t="n">
-        <v>165.6714</v>
+        <v>714.2857</v>
       </c>
       <c r="G64" t="n">
-        <v>39181280.69736513</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>35071428.57</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-12.32</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>000500</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2550,64 +2550,62 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>117900</v>
+        <v>265500</v>
       </c>
       <c r="F65" t="n">
-        <v>268.003</v>
+        <v>123.2792</v>
       </c>
       <c r="G65" t="n">
-        <v>31597552.38168333</v>
+        <v>32730640.59686133</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>삼화콘덴서</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>001820</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>190600</v>
+        <v>116300</v>
       </c>
       <c r="F66" t="n">
-        <v>165.7794</v>
+        <v>332.3224</v>
       </c>
       <c r="G66" t="n">
-        <v>31597552.38168333</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-11.96</v>
-      </c>
+        <v>38649096.95964394</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>000810</t>
+          <t>031980</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2616,96 +2614,96 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>665000</v>
+        <v>152400</v>
       </c>
       <c r="F67" t="n">
-        <v>59.097</v>
+        <v>272.9638</v>
       </c>
       <c r="G67" t="n">
-        <v>39299474.60595447</v>
+        <v>41599689.38070278</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>064290</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>94200</v>
+        <v>44950</v>
       </c>
       <c r="F68" t="n">
-        <v>390.423</v>
+        <v>931.6319999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>36777850.25730231</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-7.83</v>
-      </c>
+        <v>41876856.8952711</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>240000</v>
+        <v>48700</v>
       </c>
       <c r="F69" t="n">
-        <v>153.241</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>36777850.25730231</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>41599689.38070278</v>
+      </c>
+      <c r="H69" t="n">
+        <v>6.1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2714,32 +2712,32 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>78200</v>
+        <v>125000</v>
       </c>
       <c r="F70" t="n">
-        <v>502.5508</v>
+        <v>335.0149</v>
       </c>
       <c r="G70" t="n">
-        <v>39299474.60595447</v>
+        <v>41876856.8952711</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>8.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2748,32 +2746,32 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>10970</v>
+        <v>51300</v>
       </c>
       <c r="F71" t="n">
-        <v>3600.36</v>
+        <v>638.0242</v>
       </c>
       <c r="G71" t="n">
-        <v>39495949.5949595</v>
+        <v>32730640.59686133</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.26</v>
+        <v>-14.21</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2782,32 +2780,32 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>80800</v>
+        <v>145400</v>
       </c>
       <c r="F72" t="n">
-        <v>493.8272</v>
+        <v>265.8122</v>
       </c>
       <c r="G72" t="n">
-        <v>39901234.56790123</v>
+        <v>38649096.95964394</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.25</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2816,32 +2814,32 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>11880</v>
+        <v>663000</v>
       </c>
       <c r="F73" t="n">
-        <v>3021.148</v>
+        <v>59.097</v>
       </c>
       <c r="G73" t="n">
-        <v>35891238.67069487</v>
+        <v>39181280.69736513</v>
       </c>
       <c r="H73" t="n">
-        <v>-10.27</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>131290</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2850,96 +2848,96 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>102200</v>
+        <v>236500</v>
       </c>
       <c r="F74" t="n">
-        <v>390.423</v>
+        <v>165.6714</v>
       </c>
       <c r="G74" t="n">
-        <v>39901234.56790123</v>
+        <v>39181280.69736513</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>45150</v>
+        <v>117900</v>
       </c>
       <c r="F75" t="n">
-        <v>832.4662</v>
+        <v>268.003</v>
       </c>
       <c r="G75" t="n">
-        <v>37585848.07492196</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-6.04</v>
-      </c>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>194500</v>
+        <v>190600</v>
       </c>
       <c r="F76" t="n">
-        <v>203.064</v>
+        <v>165.7794</v>
       </c>
       <c r="G76" t="n">
-        <v>39495949.5949595</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>31597552.38168333</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-11.96</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>삼성화재</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>086790</t>
+          <t>000810</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2948,62 +2946,64 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>128800</v>
+        <v>665000</v>
       </c>
       <c r="F77" t="n">
-        <v>306.2796</v>
+        <v>59.097</v>
       </c>
       <c r="G77" t="n">
-        <v>39448818.8976378</v>
+        <v>39299474.60595447</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>롯데렌탈</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>089860</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>45900</v>
+        <v>94200</v>
       </c>
       <c r="F78" t="n">
-        <v>854.2030999999999</v>
+        <v>390.423</v>
       </c>
       <c r="G78" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
+        <v>36777850.25730231</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-7.83</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>로보스타</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>090360</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -3012,47 +3012,49 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>78200</v>
+        <v>240000</v>
       </c>
       <c r="F79" t="n">
-        <v>502.5508</v>
+        <v>153.241</v>
       </c>
       <c r="G79" t="n">
-        <v>39299474.60595447</v>
+        <v>36777850.25730231</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>메리츠금융지주</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>138040</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>115400</v>
+        <v>78200</v>
       </c>
       <c r="F80" t="n">
-        <v>335.0149</v>
+        <v>502.5508</v>
       </c>
       <c r="G80" t="n">
-        <v>38660714.28571428</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3062,12 +3064,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3076,16 +3078,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>9740</v>
+        <v>10970</v>
       </c>
       <c r="F81" t="n">
-        <v>3875.969</v>
+        <v>3600.36</v>
       </c>
       <c r="G81" t="n">
-        <v>37751937.98449613</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H81" t="n">
-        <v>-5.62</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="82">
@@ -3096,12 +3098,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3110,16 +3112,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>21650</v>
+        <v>80800</v>
       </c>
       <c r="F82" t="n">
-        <v>1785.7143</v>
+        <v>493.8272</v>
       </c>
       <c r="G82" t="n">
-        <v>38660714.28571428</v>
+        <v>39901234.56790123</v>
       </c>
       <c r="H82" t="n">
-        <v>-3.35</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="83">
@@ -3130,29 +3132,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>271000</v>
+        <v>11880</v>
       </c>
       <c r="F83" t="n">
-        <v>141.0219</v>
+        <v>3021.148</v>
       </c>
       <c r="G83" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H83" t="inlineStr"/>
+        <v>35891238.67069487</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-10.27</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3162,31 +3166,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>64300</v>
+        <v>102200</v>
       </c>
       <c r="F84" t="n">
-        <v>594.3536</v>
+        <v>390.423</v>
       </c>
       <c r="G84" t="n">
-        <v>38216939.07875186</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-4.46</v>
-      </c>
+        <v>39901234.56790123</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3196,12 +3198,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3210,16 +3212,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>56100</v>
+        <v>45150</v>
       </c>
       <c r="F85" t="n">
-        <v>700.5254</v>
+        <v>832.4662</v>
       </c>
       <c r="G85" t="n">
-        <v>39299474.60595447</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H85" t="n">
-        <v>-1.75</v>
+        <v>-6.04</v>
       </c>
     </row>
     <row r="86">
@@ -3230,12 +3232,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>코스메카코리아</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>241710</t>
+          <t>066570</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3244,13 +3246,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>137300</v>
+        <v>194500</v>
       </c>
       <c r="F86" t="n">
-        <v>274.9595</v>
+        <v>203.064</v>
       </c>
       <c r="G86" t="n">
-        <v>37751937.98449613</v>
+        <v>39495949.5949595</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3262,12 +3264,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>251970</t>
+          <t>086790</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3276,13 +3278,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>59800</v>
+        <v>128800</v>
       </c>
       <c r="F87" t="n">
-        <v>638.0242</v>
+        <v>306.2796</v>
       </c>
       <c r="G87" t="n">
-        <v>38153846.15384615</v>
+        <v>39448818.8976378</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3294,12 +3296,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BGF리테일</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>282330</t>
+          <t>089860</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3308,13 +3310,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>141400</v>
+        <v>45900</v>
       </c>
       <c r="F88" t="n">
-        <v>265.8122</v>
+        <v>854.2030999999999</v>
       </c>
       <c r="G88" t="n">
-        <v>37585848.07492196</v>
+        <v>39207920.79207921</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3326,31 +3328,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>로보스타</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>090360</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>10020</v>
+        <v>78200</v>
       </c>
       <c r="F89" t="n">
-        <v>3937.0079</v>
+        <v>502.5508</v>
       </c>
       <c r="G89" t="n">
-        <v>39448818.8976378</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-1.38</v>
-      </c>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3360,31 +3360,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>138040</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>29700</v>
+        <v>115400</v>
       </c>
       <c r="F90" t="n">
-        <v>1320.132</v>
+        <v>335.0149</v>
       </c>
       <c r="G90" t="n">
-        <v>39207920.79207921</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-1.98</v>
-      </c>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3394,12 +3392,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3408,16 +3406,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6820</v>
+        <v>9740</v>
       </c>
       <c r="F91" t="n">
-        <v>5594.4056</v>
+        <v>3875.969</v>
       </c>
       <c r="G91" t="n">
-        <v>38153846.15384615</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H91" t="n">
-        <v>-4.62</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="92">
@@ -3428,44 +3426,46 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>216500</v>
+        <v>21650</v>
       </c>
       <c r="F92" t="n">
-        <v>165.7794</v>
+        <v>1785.7143</v>
       </c>
       <c r="G92" t="n">
-        <v>35891238.67069487</v>
-      </c>
-      <c r="H92" t="inlineStr"/>
+        <v>38660714.28571428</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-3.35</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3474,94 +3474,98 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>48850</v>
+        <v>271000</v>
       </c>
       <c r="F93" t="n">
-        <v>818.8332</v>
+        <v>141.0219</v>
       </c>
       <c r="G93" t="n">
-        <v>40000000</v>
+        <v>38216939.07875186</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>송원산업</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>004430</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>11110</v>
+        <v>64300</v>
       </c>
       <c r="F94" t="n">
-        <v>3600.36</v>
+        <v>594.3536</v>
       </c>
       <c r="G94" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>38216939.07875186</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-4.46</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>한국공항</t>
+          <t>슈프리마</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>005430</t>
+          <t>236200</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>81000</v>
+        <v>56100</v>
       </c>
       <c r="F95" t="n">
-        <v>493.8272</v>
+        <v>700.5254</v>
       </c>
       <c r="G95" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
+        <v>39299474.60595447</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-1.75</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>코스메카코리아</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>241710</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3570,30 +3574,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>13240</v>
+        <v>137300</v>
       </c>
       <c r="F96" t="n">
-        <v>3021.148</v>
+        <v>274.9595</v>
       </c>
       <c r="G96" t="n">
-        <v>40000000</v>
+        <v>37751937.98449613</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>251970</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3602,30 +3606,30 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>14530</v>
+        <v>59800</v>
       </c>
       <c r="F97" t="n">
-        <v>2752.925</v>
+        <v>638.0242</v>
       </c>
       <c r="G97" t="n">
-        <v>40000000</v>
+        <v>38153846.15384615</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DN오토모티브</t>
+          <t>BGF리테일</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>007340</t>
+          <t>282330</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3634,126 +3638,132 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>46650</v>
+        <v>141400</v>
       </c>
       <c r="F98" t="n">
-        <v>857.4491</v>
+        <v>265.8122</v>
       </c>
       <c r="G98" t="n">
-        <v>40000000</v>
+        <v>37585848.07492196</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>한올바이오파마</t>
+          <t>자이에스앤디</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>009420</t>
+          <t>317400</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>62600</v>
+        <v>10020</v>
       </c>
       <c r="F99" t="n">
-        <v>638.9776000000001</v>
+        <v>3937.0079</v>
       </c>
       <c r="G99" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H99" t="inlineStr"/>
+        <v>39448818.8976378</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-1.38</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>티앤엘</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>340570</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>142600</v>
+        <v>29700</v>
       </c>
       <c r="F100" t="n">
-        <v>280.5049</v>
+        <v>1320.132</v>
       </c>
       <c r="G100" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
+        <v>39207920.79207921</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-1.98</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>446540</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>48050</v>
+        <v>6820</v>
       </c>
       <c r="F101" t="n">
-        <v>832.4662</v>
+        <v>5594.4056</v>
       </c>
       <c r="G101" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>38153846.15384615</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-4.62</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>인바디</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>041830</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3762,13 +3772,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>62000</v>
+        <v>216500</v>
       </c>
       <c r="F102" t="n">
-        <v>645.1613</v>
+        <v>165.7794</v>
       </c>
       <c r="G102" t="n">
-        <v>40000000</v>
+        <v>35891238.67069487</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3780,12 +3790,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>078930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3794,10 +3804,10 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>113600</v>
+        <v>48850</v>
       </c>
       <c r="F103" t="n">
-        <v>352.1127</v>
+        <v>818.8332</v>
       </c>
       <c r="G103" t="n">
         <v>40000000</v>
@@ -3812,12 +3822,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>송원산업</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>096530</t>
+          <t>004430</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3826,10 +3836,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>31250</v>
+        <v>11110</v>
       </c>
       <c r="F104" t="n">
-        <v>1280</v>
+        <v>3600.36</v>
       </c>
       <c r="G104" t="n">
         <v>40000000</v>
@@ -3844,12 +3854,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>한국공항</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>119850</t>
+          <t>005430</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3858,10 +3868,10 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>50100</v>
+        <v>81000</v>
       </c>
       <c r="F105" t="n">
-        <v>798.4032</v>
+        <v>493.8272</v>
       </c>
       <c r="G105" t="n">
         <v>40000000</v>
@@ -3876,12 +3886,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3890,10 +3900,10 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>10320</v>
+        <v>13240</v>
       </c>
       <c r="F106" t="n">
-        <v>3875.969</v>
+        <v>3021.148</v>
       </c>
       <c r="G106" t="n">
         <v>40000000</v>
@@ -3908,12 +3918,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>006340</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3922,10 +3932,10 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>22400</v>
+        <v>14530</v>
       </c>
       <c r="F107" t="n">
-        <v>1785.7143</v>
+        <v>2752.925</v>
       </c>
       <c r="G107" t="n">
         <v>40000000</v>
@@ -3940,12 +3950,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>한국콜마</t>
+          <t>DN오토모티브</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>161890</t>
+          <t>007340</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3954,10 +3964,10 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>137800</v>
+        <v>46650</v>
       </c>
       <c r="F108" t="n">
-        <v>290.2758</v>
+        <v>857.4491</v>
       </c>
       <c r="G108" t="n">
         <v>40000000</v>
@@ -3972,12 +3982,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NHN</t>
+          <t>한올바이오파마</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>181710</t>
+          <t>009420</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3986,10 +3996,10 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>71900</v>
+        <v>62600</v>
       </c>
       <c r="F109" t="n">
-        <v>556.3282</v>
+        <v>638.9776000000001</v>
       </c>
       <c r="G109" t="n">
         <v>40000000</v>
@@ -4004,12 +4014,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -4018,10 +4028,10 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>413500</v>
+        <v>142600</v>
       </c>
       <c r="F110" t="n">
-        <v>96.73520000000001</v>
+        <v>280.5049</v>
       </c>
       <c r="G110" t="n">
         <v>40000000</v>
@@ -4036,12 +4046,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>028050</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4050,10 +4060,10 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>67300</v>
+        <v>48050</v>
       </c>
       <c r="F111" t="n">
-        <v>594.3536</v>
+        <v>832.4662</v>
       </c>
       <c r="G111" t="n">
         <v>40000000</v>
@@ -4068,12 +4078,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>슈프리마</t>
+          <t>인바디</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>236200</t>
+          <t>041830</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4082,10 +4092,10 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>57100</v>
+        <v>62000</v>
       </c>
       <c r="F112" t="n">
-        <v>700.5254</v>
+        <v>645.1613</v>
       </c>
       <c r="G112" t="n">
         <v>40000000</v>
@@ -4100,12 +4110,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>252990</t>
+          <t>078930</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4114,10 +4124,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>13890</v>
+        <v>113600</v>
       </c>
       <c r="F113" t="n">
-        <v>2879.7696</v>
+        <v>352.1127</v>
       </c>
       <c r="G113" t="n">
         <v>40000000</v>
@@ -4132,12 +4142,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>자이에스앤디</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>317400</t>
+          <t>096530</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4146,10 +4156,10 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>10160</v>
+        <v>31250</v>
       </c>
       <c r="F114" t="n">
-        <v>3937.0079</v>
+        <v>1280</v>
       </c>
       <c r="G114" t="n">
         <v>40000000</v>
@@ -4164,12 +4174,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>티앤엘</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>340570</t>
+          <t>119850</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4178,10 +4188,10 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>30300</v>
+        <v>50100</v>
       </c>
       <c r="F115" t="n">
-        <v>1320.132</v>
+        <v>798.4032</v>
       </c>
       <c r="G115" t="n">
         <v>40000000</v>
@@ -4196,12 +4206,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>446540</t>
+          <t>144960</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4210,10 +4220,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>7150</v>
+        <v>10320</v>
       </c>
       <c r="F116" t="n">
-        <v>5594.4056</v>
+        <v>3875.969</v>
       </c>
       <c r="G116" t="n">
         <v>40000000</v>
@@ -4228,12 +4238,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SK이터닉스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>475150</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4242,15 +4252,335 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>56000</v>
+        <v>22400</v>
       </c>
       <c r="F117" t="n">
-        <v>714.2857</v>
+        <v>1785.7143</v>
       </c>
       <c r="G117" t="n">
         <v>40000000</v>
       </c>
       <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>한국콜마</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>161890</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>137800</v>
+      </c>
+      <c r="F118" t="n">
+        <v>290.2758</v>
+      </c>
+      <c r="G118" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NHN</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>181710</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>71900</v>
+      </c>
+      <c r="F119" t="n">
+        <v>556.3282</v>
+      </c>
+      <c r="G119" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>413500</v>
+      </c>
+      <c r="F120" t="n">
+        <v>96.73520000000001</v>
+      </c>
+      <c r="G120" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>타이거일렉</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>219130</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>67300</v>
+      </c>
+      <c r="F121" t="n">
+        <v>594.3536</v>
+      </c>
+      <c r="G121" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>슈프리마</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>236200</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>57100</v>
+      </c>
+      <c r="F122" t="n">
+        <v>700.5254</v>
+      </c>
+      <c r="G122" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>252990</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>13890</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2879.7696</v>
+      </c>
+      <c r="G123" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>자이에스앤디</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>317400</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>10160</v>
+      </c>
+      <c r="F124" t="n">
+        <v>3937.0079</v>
+      </c>
+      <c r="G124" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>티앤엘</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>340570</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>30300</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1320.132</v>
+      </c>
+      <c r="G125" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>메가터치</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>446540</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>7150</v>
+      </c>
+      <c r="F126" t="n">
+        <v>5594.4056</v>
+      </c>
+      <c r="G126" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SK이터닉스</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>475150</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>56000</v>
+      </c>
+      <c r="F127" t="n">
+        <v>714.2857</v>
+      </c>
+      <c r="G127" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
